--- a/src/exports/M250285 input voor coderen - met Q18Q19_Q18Q19_code_assignments.xlsx
+++ b/src/exports/M250285 input voor coderen - met Q18Q19_Q18Q19_code_assignments.xlsx
@@ -70,12 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -447,16 +448,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,7 +567,7 @@
           <t>De uitspraak 'Ouders moeten meewerken' sluit direct aan bij het concept van 'Ouderlijke betrokkenheid', dat gaat over het informeren en betrekken van ouders bij gezondheidsthema's ter ondersteuning van schoolinterventies. Dit is een duidelijke en directe match met de codeomschrijving.</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -623,7 +625,7 @@
           <t>De uitdrukking 'De gezonde school aanpak is de norm' duidt op een blijvende en vanzelfsprekende uitvoering van de Gezonde School-aanpak binnen de school, wat precies aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -681,7 +683,7 @@
           <t>De uitdrukking 'leeft niet op onze school' duidt op een zwakke of ontbrekende verankering van de Gezonde School-aanpak in de schoolpraktijk, wat precies aansluit bij de code 'Onvoldoende verankering' die spreekt over lage herkenning, prioriteit, tijd of handhaving.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -739,7 +741,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak niet duidelijk of expliciet aanwezig is op de school, wat duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit goed aan bij de definitie van 'Onvoldoende verankering'.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -797,7 +799,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak geen prioriteit heeft, wat direct aansluit bij de code 'Onvoldoende verankering', die verwijst naar een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk, zichtbaar in lage herkenning, prioriteit, tijd of handhaving.</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -855,7 +857,7 @@
           <t>De reactie geeft aan dat het voedingsbeleid is aangepakt, wat direct aansluit bij de code 'Structureel voedingsbeleid' die verwijst naar blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -913,7 +915,7 @@
           <t>De uitspraak geeft aan dat er een waargenomen toename is in gezond gedrag bij leerlingen, namelijk gezonder eten op school. Dit sluit direct aan bij de code 'Verbeterd gezondheidsgedrag', die verwijst naar een toename van gezonde gedragingen bij leerlingen.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -971,7 +973,7 @@
           <t>De reactie benadrukt specifiek het aanbod van gezonde producten in de kantine, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1029,7 +1031,7 @@
           <t>De uiting 'goede contacten' duidt op een positieve samenwerking of ondersteuning, wat het beste past bij de code 'Ondersteunende samenwerking GGD' die verwijst naar ondersteuning door externe partijen zoals de GGD bij de uitvoering van Gezonde School-activiteiten.</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1087,7 +1089,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak is duidelijk' duidt op heldere en eenduidige communicatie over de aanpak, wat direct aansluit bij de code 'Consistente heldere communicatie' die regelmatige, eenduidige en verzorgde informatievoorziening beschrijft.</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1145,7 +1147,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak geïntegreerd is in het dagelijkse leven op school, wat overeenkomt met het concept van blijvende uitvoering door bestuurlijke steun en brede betrokkenheid, zoals beschreven bij 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1203,7 +1205,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak op meerdere terreinen tegelijk wordt uitgevoerd, wat aansluit bij de definitie van 'Brede implementatie van gezondheidsthema's' als zichtbare invoering van initiatieven over verschillende gezondheidsthema's op school.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1261,7 +1263,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak de gemaakte afspraken volgt, wat duidt op een blijvende uitvoering en verankering van de aanpak binnen de school. Dit sluit goed aan bij de definitie van 'Duurzame verankering', die gaat over blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1319,7 +1321,7 @@
           <t>De uitspraak 'moet aandacht krijgen' duidt op het belang van blijvende aandacht en betrokkenheid bij de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering, namelijk de blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1377,7 +1379,7 @@
           <t>De uitspraak 'Er wordt meer op gelet' duidt op een blijvende aandacht en betrokkenheid bij de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering, namelijk de blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1435,7 +1437,7 @@
           <t>De uitspraak 'heeft mooie dingen mogelijk gemaakt' duidt op een positieve waardering van de blijvende uitvoering en impact van de Gezonde School-aanpak, wat aansluit bij het concept van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n">
+      <c r="J17" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1493,7 +1495,7 @@
           <t>De uitspraak geeft aan dat de school bewust bezig is met de Gezonde School-aanpak, wat duidt op een blijvende en bewuste betrokkenheid. Dit sluit aan bij 'Duurzame verankering', dat gaat over blijvende uitvoering door brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1551,7 +1553,7 @@
           <t>De uitspraak suggereert een zorg dat de aanpak niet te ver moet gaan, wat kan wijzen op onduidelijkheid of weerstand tegen te strikte regels of maatregelen. Hoewel de code 'Onvoldoende beleidsduidelijkheid traktaties' specifiek over traktatieregels gaat, is dit de dichtstbijzijnde code die een gevoel van terughoudendheid of kritiek op de aanpak weerspiegelt binnen de gegeven opties.</t>
         </is>
       </c>
-      <c r="J19" s="2" t="n">
+      <c r="J19" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1609,7 +1611,7 @@
           <t>De idee benadrukt dat de Gezonde School-aanpak onder de aandacht wordt gebracht door de sportfunctionaris, wat direct aansluit bij de code 'Actieve sportfunctionaris' die verwijst naar een interne functionaris die actief sportactiviteiten binnen de school promoot.</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J20" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1667,7 +1669,7 @@
           <t>De tekst benoemt expliciet een interne functionaris die actief sportactiviteiten binnen de school promoot, wat precies overeenkomt met de definitie van de code 'Actieve sportfunctionaris'.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n">
+      <c r="J21" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1725,7 +1727,7 @@
           <t>De uitdrukking 'werkt cyclisch' verwijst direct naar een periodieke integratie en geplande cycli, wat precies overeenkomt met de definitie van 'Cyclische verankering in dagelijkse schoolpraktijk'.</t>
         </is>
       </c>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1783,7 +1785,7 @@
           <t>De uitspraak 'Ieder jaar staat een ander onderdeel centraal' duidt op een vaste programmaopzet met jaarlijkse themawissel, wat precies past bij de code 'Programmastructuur voor continuïteit' die verwijst naar een vaste programmaopzet met jaarlijkse themawissel die uitvoering en voortgang faciliteert.</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n">
+      <c r="J23" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1841,7 +1843,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak werkt' geeft aan dat de aanpak zichtbaar positieve resultaten of verbeteringen oplevert, wat aansluit bij het code label 'Effectief ingebed kader' dat verwijst naar een raamwerk dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert.</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1899,7 +1901,7 @@
           <t>De uitspraak 'kan soms sterker zijn' duidt op een zwakke of onvoldoende verankering van de Gezonde School-aanpak in de schoolpraktijk, wat aansluit bij de code 'Onvoldoende verankering' die verwijst naar een zwakke of ontbrekende verankering zichtbaar in lage herkenning, prioriteit, tijd of handhaving.</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1957,7 +1959,7 @@
           <t>De opmerking benadrukt dat de Gezonde School-aanpak bewustzijn creëert bij medewerkers, wat aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n">
+      <c r="J26" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2015,7 +2017,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak bewustzijn bij leerlingen creëert, wat aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n">
+      <c r="J27" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2073,7 +2075,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak een gezonde levensstijl ondersteunt, wat direct aansluit bij het code label 'Handvatten voor gezonde leefstijl' dat gaat over concrete maatregelen en hulpmiddelen die gezond gedrag stimuleren.</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n">
+      <c r="J28" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2131,7 +2133,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak bijdraagt aan het versterken van een gezonde levensstijl, wat direct aansluit bij het concept van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J29" s="2" t="n">
+      <c r="J29" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2189,7 +2191,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak mensen bewust maakt en alert houdt op een gezonde leefstijl, wat aansluit bij het bieden van concrete maatregelen en hulpmiddelen die gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n">
+      <c r="J30" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2247,7 +2249,7 @@
           <t>De opmerking geeft aan dat de Gezonde School-aanpak meerdere gezondheidsthema's omvat, wat direct aansluit bij de code 'Brede implementatie van gezondheidsthema's' die verwijst naar de invoering van diverse leefstijl- en gezondheidsthema's op school.</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n">
+      <c r="J31" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2305,7 +2307,7 @@
           <t>De uitspraak 'De aanpak is belangrijk' duidt op het belang van het blijvend uitvoeren en verankeren van de Gezonde School-aanpak, wat aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2363,7 +2365,7 @@
           <t>De term 'organisatie' duidt op het belang van een gestructureerde en blijvende aanpak binnen de school, wat aansluit bij 'Duurzame verankering' die staat voor blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n">
+      <c r="J33" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2421,7 +2423,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak leidt tot een verandering in het gedrag van leerlingen, wat direct aansluit bij de code 'Verbeterd gezondheidsgedrag' die verwijst naar een waargenomen toename van gezonde gedragingen bij leerlingen.</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n">
+      <c r="J34" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2479,7 +2481,7 @@
           <t>De reactie benadrukt het aanbod van gezonde voeding via de schoolcatering, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J35" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2537,7 +2539,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak een duidelijke structuur biedt, wat direct aansluit bij de code 'Programmastructuur voor continuïteit' die verwijst naar een vaste programmaopzet die uitvoering en voortgang faciliteert.</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J36" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2595,7 +2597,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak geïntegreerd wordt in het curriculum, wat aansluit bij de brede implementatie van gezondheidsthema's binnen de school. Dit betekent dat gezondheidsthema's zichtbaar en concreet worden ingevoerd in het onderwijs, wat precies past bij de code 'Brede implementatie van gezondheidsthema's'.</t>
         </is>
       </c>
-      <c r="J37" s="2" t="n">
+      <c r="J37" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2653,7 +2655,7 @@
           <t>De term 'prettige begeleiding bij de uitvoering van het project' sluit goed aan bij de code 'Ondersteunende samenwerking GGD', die beschrijft dat GGD-regisseurs de school ondersteunen bij de uitvoering van Gezonde School-activiteiten. Dit is een sterke match omdat het gaat om begeleiding en ondersteuning tijdens de uitvoering.</t>
         </is>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J38" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2711,7 +2713,7 @@
           <t>De reactie benadrukt de ondersteunende rol van de gezondheidsbevorderaar vanuit de GGD bij de uitvoering van Gezonde School-activiteiten, wat precies aansluit bij de code 'Ondersteunende samenwerking GGD'.</t>
         </is>
       </c>
-      <c r="J39" s="2" t="n">
+      <c r="J39" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2769,7 +2771,7 @@
           <t>De uitspraak 'Gezonde voeding moet gestimuleerd worden' sluit het beste aan bij de code 'Toegankelijkheid gezond voedingsaanbod', omdat het gaat over het bevorderen van de beschikbaarheid en het gemakkelijk verkrijgen van gezond eten binnen of nabij de school.</t>
         </is>
       </c>
-      <c r="J40" s="2" t="n">
+      <c r="J40" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2827,7 +2829,7 @@
           <t>De uitspraak 'Gezonde voeding sluit aan bij de populatie' duidt erop dat het gezonde voedingsaanbod afgestemd is op de behoeften of voorkeuren van de populatie, wat aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is (Toegankelijkheid gezond voedingsaanbod).</t>
         </is>
       </c>
-      <c r="J41" s="2" t="n">
+      <c r="J41" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2885,7 +2887,7 @@
           <t>De idee benadrukt dat gezonde voeding aansluit bij de leefstijl van medewerkers, wat inhoudt dat gezond eten binnen de schoolomgeving goed beschikbaar en passend is. Dit sluit het beste aan bij de code 'Toegankelijkheid gezond voedingsaanbod', die gaat over de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is.</t>
         </is>
       </c>
-      <c r="J42" s="2" t="n">
+      <c r="J42" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2943,7 +2945,7 @@
           <t>De uitspraak benadrukt het belang van het overbrengen (uitdragen) van de Gezonde School-aanpak naar leerlingen, wat aansluit bij het concept van consistente en heldere communicatie over de aanpak en voortgang aan betrokkenen.</t>
         </is>
       </c>
-      <c r="J43" s="2" t="n">
+      <c r="J43" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3001,7 +3003,7 @@
           <t>De uitspraak benadrukt het belang van het informeren en betrekken van ouders bij de Gezonde School-aanpak, wat precies aansluit bij de code 'Ouderlijke betrokkenheid' die gaat over het informeren van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J44" s="2" t="n">
+      <c r="J44" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3059,7 +3061,7 @@
           <t>De idee benadrukt het leren van leerlingen over het belang van de Gezonde School, wat aansluit bij het stimuleren van bewustwording en gezond gedrag via concrete maatregelen en hulpmiddelen, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J45" s="2" t="n">
+      <c r="J45" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3117,7 +3119,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak gezond eten en leven stimuleert, wat direct aansluit bij het concept van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J46" s="2" t="n">
+      <c r="J46" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3175,7 +3177,7 @@
           <t>De opmerking dat de Gezonde School-aanpak niet rigide regels hanteert, sluit aan bij het concept van 'Certificaten als vrijwillige erkenning', waarbij erkenning optioneel is en zonder verplichte opvolging, wat wijst op een flexibele, niet dwingende aanpak.</t>
         </is>
       </c>
-      <c r="J47" s="2" t="n">
+      <c r="J47" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3233,7 +3235,7 @@
           <t>De uitspraak 'Bijna iedereen kan zich vinden in de Gezonde School-aanpak' duidt op brede betrokkenheid en acceptatie binnen de school, wat aansluit bij het concept van 'Duurzame verankering' waarbij de aanpak blijvend wordt uitgevoerd door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J48" s="2" t="n">
+      <c r="J48" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3291,7 +3293,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak is helder' duidt op duidelijke en eenduidige communicatie over de aanpak, wat aansluit bij de code 'Consistente heldere communicatie' die regelmatige, eenduidige en verzorgde informatievoorziening beschrijft.</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n">
+      <c r="J49" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3349,7 +3351,7 @@
           <t>De term 'continuïteit' in de idee verwijst naar de blijvende uitvoering van de Gezonde School-aanpak, wat precies aansluit bij de code 'Duurzame verankering' die gaat over blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J50" s="2" t="n">
+      <c r="J50" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3407,7 +3409,7 @@
           <t>De opmerking dat de Gezonde School-aanpak discussie tussen kinderen vermindert, duidt op een positieve invloed op de schoolcultuur en het welzijn van leerlingen. Dit sluit aan bij het code label 'Effectief ingebed kader', dat verwijst naar een raamwerk dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert.</t>
         </is>
       </c>
-      <c r="J51" s="2" t="n">
+      <c r="J51" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3465,7 +3467,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak bijdraagt aan het verminderen van verschillen in eetgedrag, wat aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is. Dit duidt op een verbeterde toegankelijkheid van gezond voedingsaanbod.</t>
         </is>
       </c>
-      <c r="J52" s="2" t="n">
+      <c r="J52" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3523,7 +3525,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak heeft geleid tot aandacht voor meerdere onderwerpen, wat aansluit bij de definitie van 'Brede implementatie van gezondheidsthema's' die verwijst naar de invoering van diverse initiatieven rond leefstijl, voeding, gewicht en rookpreventie op school.</t>
         </is>
       </c>
-      <c r="J53" s="2" t="n">
+      <c r="J53" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3581,7 +3583,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak meer aandacht krijgt dan voorheen, wat duidt op een blijvende en versterkte betrokkenheid binnen de school. Dit sluit aan bij het concept van 'Duurzame verankering', waarbij de aanpak blijvend wordt uitgevoerd door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J54" s="2" t="n">
+      <c r="J54" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3639,7 +3641,7 @@
           <t>De uitspraak 'moet aandacht hebben' duidt op het belang van blijvende aandacht en betrokkenheid bij de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering, namelijk de blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J55" s="2" t="n">
+      <c r="J55" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3697,7 +3699,7 @@
           <t>De uitspraak benadrukt het creëren van groeiend bewustzijn, wat aansluit bij het stimuleren van gezond gedrag en bewustwording, zoals beschreven in 'Handvatten voor gezonde leefstijl'. Andere codes richten zich meer op specifieke beleidsaspecten of structuren, terwijl deze code het beste de intentie van bewustwording en gedragsstimulering vangt.</t>
         </is>
       </c>
-      <c r="J56" s="2" t="n">
+      <c r="J56" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3755,7 +3757,7 @@
           <t>De term 'vliegwiel' suggereert een kracht die iets in beweging houdt en voortzet, wat aansluit bij het concept van 'Duurzame verankering' waarbij de Gezonde School-aanpak blijvend wordt uitgevoerd door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J57" s="2" t="n">
+      <c r="J57" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3813,7 +3815,7 @@
           <t>De uitspraak geeft aan dat de uitvoering van de Gezonde School-aanpak niet optimaal is, wat wijst op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit goed aan bij de code 'Onvoldoende verankering', die verwijst naar een lage herkenning, prioriteit of tijd voor de aanpak.</t>
         </is>
       </c>
-      <c r="J58" s="2" t="n">
+      <c r="J58" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3871,7 +3873,7 @@
           <t>De vermelding dat de GGD betrokken is bij de Gezonde School-aanpak sluit direct aan bij de code 'Ondersteunende samenwerking GGD', die beschrijft dat GGD-regisseurs de school ondersteunen bij de uitvoering van Gezonde School-activiteiten. Dit is een directe en duidelijke match.</t>
         </is>
       </c>
-      <c r="J59" s="2" t="n">
+      <c r="J59" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3929,7 +3931,7 @@
           <t>De vermelding van een financiële bijdrage sluit direct aan bij het concept van beschikbare geldmiddelen en subsidieopties die de uitvoering en continuïteit van de Gezonde School-aanpak mogelijk maken, wat precies wordt beschreven onder 'Financieringsmogelijkheden'.</t>
         </is>
       </c>
-      <c r="J60" s="2" t="n">
+      <c r="J60" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3987,7 +3989,7 @@
           <t>De respondent geeft aan tevreden te zijn met de resultaten van de Gezonde School-aanpak, wat duidt op een positieve waarneming van effecten. De code 'Verbeterd gezondheidsgedrag' sluit hier het beste op aan omdat het gaat om waargenomen toename van gezonde gedragingen, wat een directe interpretatie is van 'mooie resultaten'.</t>
         </is>
       </c>
-      <c r="J61" s="2" t="n">
+      <c r="J61" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4045,7 +4047,7 @@
           <t>De term 'werkwijze' verwijst naar de manier waarop de Gezonde School-aanpak wordt uitgevoerd en ervaren. 'Fijn' duidt op tevredenheid over deze uitvoering, wat aansluit bij het concept van duurzame verankering, namelijk de blijvende uitvoering van de aanpak door bestuurlijke steun en brede betrokkenheid. Andere codes zijn minder relevant omdat ze meer specifieke aspecten behandelen, terwijl deze reactie een algemene positieve waardering van de aanpak betreft.</t>
         </is>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J62" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4103,7 +4105,7 @@
           <t>De uiting 'De Gezonde School-aanpak is prima' geeft een positieve waardering van de aanpak, wat kan duiden op tevredenheid over de blijvende uitvoering en verankering van de aanpak binnen de school. Dit sluit het beste aan bij 'Duurzame verankering', omdat het aangeeft dat de aanpak goed functioneert en mogelijk goed ingebed is.</t>
         </is>
       </c>
-      <c r="J63" s="2" t="n">
+      <c r="J63" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -4161,7 +4163,7 @@
           <t>De uitdrukking 'goede vibe in de school' duidt op een positieve verandering in de schoolcultuur of het welzijn, wat aansluit bij het code label 'Effectief ingebed kader' dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert.</t>
         </is>
       </c>
-      <c r="J64" s="2" t="n">
+      <c r="J64" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -4219,7 +4221,7 @@
           <t>De term 'kettingreactie' suggereert een doorlopende, blijvende impact van de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering waarbij de aanpak blijvend wordt uitgevoerd door brede betrokkenheid en bestuurlijke steun.</t>
         </is>
       </c>
-      <c r="J65" s="2" t="n">
+      <c r="J65" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -4277,7 +4279,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak gezonde voeding bevordert, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J66" s="2" t="n">
+      <c r="J66" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -4335,7 +4337,7 @@
           <t>De uitspraak benadrukt het belang van het organiseren van een goed aanbod binnen de Gezonde School-aanpak. Hoewel het niet expliciet over sport of beweging gaat, sluit 'Ruim bewegingsaanbod' het beste aan omdat het verwijst naar het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten en materialen, wat een kernaspect is van een goed georganiseerd aanbod binnen de aanpak.</t>
         </is>
       </c>
-      <c r="J67" s="2" t="n">
+      <c r="J67" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -4393,7 +4395,7 @@
           <t>De opmerking dat de Gezonde School-aanpak moet passen bij de kernwaarden duidt op het belang van blijvende uitvoering en brede betrokkenheid, wat aansluit bij de definitie van 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J68" s="2" t="n">
+      <c r="J68" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -4451,7 +4453,7 @@
           <t>De reactie verwijst expliciet naar het verkrijgen van financiële middelen voor de Gezonde School-aanpak, wat direct aansluit bij de code 'Financieringsmogelijkheden' die gaat over beschikbare geldmiddelen en subsidieopties voor uitvoering en continuïteit.</t>
         </is>
       </c>
-      <c r="J69" s="2" t="n">
+      <c r="J69" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4509,7 +4511,7 @@
           <t>De reactie benadrukt de noodzaak van een beleid gericht op gezond eten binnen de Gezonde School-aanpak, wat direct aansluit bij de definitie van 'Structureel voedingsbeleid' als blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J70" s="2" t="n">
+      <c r="J70" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4567,7 +4569,7 @@
           <t>De reactie benadrukt de noodzaak van voldoende bewegingsmogelijkheden binnen de Gezonde School-aanpak, wat direct aansluit bij de definitie van 'Ruim bewegingsaanbod' als het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J71" s="2" t="n">
+      <c r="J71" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4625,7 +4627,7 @@
           <t>De opmerking over het waarborgen van veiligheid kan gezien worden als een aspect van de blijvende uitvoering en borging van de Gezonde School-aanpak binnen de school, wat aansluit bij het concept van duurzame verankering. Hoewel veiligheid niet expliciet genoemd wordt in de definitie, past het binnen het bredere kader van een stabiele en gedragen aanpak.</t>
         </is>
       </c>
-      <c r="J72" s="2" t="n">
+      <c r="J72" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4683,7 +4685,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak kinderen leert over gezondheid, wat aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J73" s="2" t="n">
+      <c r="J73" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4741,7 +4743,7 @@
           <t>De uiting geeft aan dat de Gezonde School-aanpak onvoldoende effect heeft, wat direct aansluit bij de code 'Onmeetbare effectiviteit' die bezorgdheid uit over het niet aantoonbaar of zichtbaar zijn van resultaten met bestaande meetinstrumenten.</t>
         </is>
       </c>
-      <c r="J74" s="2" t="n">
+      <c r="J74" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4799,7 +4801,7 @@
           <t>De reactie benadrukt de noodzaak van veel aandacht voor bewegen op school, wat direct aansluit bij het concept van een ruim bewegingsaanbod, namelijk frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J75" s="2" t="n">
+      <c r="J75" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -4857,7 +4859,7 @@
           <t>De opmerking dat de Gezonde School-aanpak veel inspanning kost, wijst op mogelijke problemen met de verankering in de schoolpraktijk, zoals lage herkenning, prioriteit of tijdsbesteding, wat aansluit bij de code 'Onvoldoende verankering'.</t>
         </is>
       </c>
-      <c r="J76" s="2" t="n">
+      <c r="J76" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4915,7 +4917,7 @@
           <t>De uitdrukking 'De Gezonde School-aanpak loopt' suggereert dat de aanpak wordt uitgevoerd en voortgezet, wat aansluit bij het concept van duurzame verankering, namelijk de blijvende uitvoering van de aanpak door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J77" s="2" t="n">
+      <c r="J77" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4973,7 +4975,7 @@
           <t>De opmerking 'te dwingend' duidt op een gevoel van weerstand of onvrede over de manier waarop regels of richtlijnen worden opgelegd, wat het meest aansluit bij 'Onvoldoende beleidsduidelijkheid traktaties' waar sprake is van weerstand of problemen bij handhaving door onduidelijke regels. Hoewel het niet specifiek over traktaties gaat, is dit de beste beschikbare code die het concept van dwingendheid en weerstand benadert.</t>
         </is>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J78" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -5031,7 +5033,7 @@
           <t>De uitspraak suggereert dat leerkrachten actiever betrokken moeten zijn bij de Gezonde School-aanpak, wat wijst op een behoefte aan blijvende uitvoering en betrokkenheid binnen de school. Dit sluit aan bij het concept van 'Duurzame verankering', dat draait om blijvende uitvoering door brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="J79" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -5089,7 +5091,7 @@
           <t>De uitspraak 'moet breder uitgedragen worden' duidt op de wens om de Gezonde School-aanpak zichtbaarder en op meerdere terreinen binnen de school te implementeren, wat aansluit bij de code 'Brede implementatie van gezondheidsthema's' die gaat over zichtbare en terreinoverstijgende invoering van gezondheidsthema's.</t>
         </is>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J80" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5147,7 +5149,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak duidelijke en stapsgewijze aanwijzingen geeft, wat overeenkomt met het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J81" s="2" t="n">
+      <c r="J81" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -5205,7 +5207,7 @@
           <t>De uitspraak 'Scholen kunnen zich verantwoorden over de gemaakte stappen' duidt op het blijvend uitvoeren en verantwoorden van de Gezonde School-aanpak, wat aansluit bij het concept van 'Duurzame verankering' waarbij bestuurlijke steun en brede betrokkenheid zorgen voor continuïteit.</t>
         </is>
       </c>
-      <c r="J82" s="2" t="n">
+      <c r="J82" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -5263,7 +5265,7 @@
           <t>De vermelding van mediawijsheid duidt op een bredere invulling van gezondheidsthema's binnen de Gezonde School-aanpak, wat aansluit bij de code 'Aandacht voor brede gezondheidsthema's' die integratie van diverse thema's zoals milieu, seksuele relaties en sociaal-emotionele onderwerpen beschrijft.</t>
         </is>
       </c>
-      <c r="J83" s="2" t="n">
+      <c r="J83" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5321,7 +5323,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak gezonde voeding omvat, wat direct aansluit bij het code label 'Structureel voedingsbeleid', dat verwijst naar blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J84" s="2" t="n">
+      <c r="J84" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -5379,7 +5381,7 @@
           <t>De uitspraak gaat over het voldoende aanbieden van gezonde producten in de kantine, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J85" s="2" t="n">
+      <c r="J85" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -5437,7 +5439,7 @@
           <t>De uitspraak benadrukt het belang van gezonde producten, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J86" s="2" t="n">
+      <c r="J86" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -5495,7 +5497,7 @@
           <t>De uitdrukking 'Leerlingen leren voor het leven' impliceert het aanreiken van concrete, uitvoerbare maatregelen en hulpmiddelen die leerlingen bewust maken en stimuleren tot gezond gedrag, wat aansluit bij de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J87" s="2" t="n">
+      <c r="J87" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -5553,7 +5555,7 @@
           <t>De uitspraak benadrukt het belang van een gezonde leefstijl voor ouders en leerlingen, wat aansluit bij het informeren van ouders over gezondheidsthema's ter ondersteuning van schoolinterventies, zoals beschreven bij 'Ouderlijke betrokkenheid'.</t>
         </is>
       </c>
-      <c r="J88" s="2" t="n">
+      <c r="J88" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -5611,7 +5613,7 @@
           <t>De idee beschrijft expliciet een toename in fruitconsumptie bij kinderen, wat direct overeenkomt met de code 'Toegenomen fruitconsumptie' die aangeeft dat er een toename is van fruitconsumptie tijdens schooltijd.</t>
         </is>
       </c>
-      <c r="J89" s="2" t="n">
+      <c r="J89" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -5669,7 +5671,7 @@
           <t>De idee beschrijft dat ouders gezondere lunches meegeven, wat direct aansluit bij het concept van 'Ouderlijke betrokkenheid', namelijk het informeren en betrekken van ouders bij gezondheidsthema's ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J90" s="2" t="n">
+      <c r="J90" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5727,7 +5729,7 @@
           <t>De uitspraak 'Kinderen bewegen meer' sluit direct aan bij het concept van een 'Ruim bewegingsaanbod', dat verwijst naar frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag. Dit is een duidelijke en directe match met de codeomschrijving.</t>
         </is>
       </c>
-      <c r="J91" s="2" t="n">
+      <c r="J91" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5785,7 +5787,7 @@
           <t>De uitspraak 'Kinderen drinken water in plaats van frisdrank' geeft een duidelijke toename van gezond gedrag aan, namelijk het kiezen voor water boven frisdrank. Dit sluit direct aan bij de code 'Verbeterd gezondheidsgedrag', die verwijst naar waargenomen toename van gezonde gedragingen bij leerlingen.</t>
         </is>
       </c>
-      <c r="J92" s="2" t="n">
+      <c r="J92" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -5843,7 +5845,7 @@
           <t>De respondent geeft aan dat de resultaten van de Gezonde School-aanpak positief zijn ('prachtig'), wat duidt op een waargenomen verbetering. De code 'Verbeterd gezondheidsgedrag' sluit hier het beste op aan omdat het gaat om een waargenomen toename van gezonde gedragingen, wat een positieve uitkomst van de aanpak weerspiegelt.</t>
         </is>
       </c>
-      <c r="J93" s="2" t="n">
+      <c r="J93" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -5901,7 +5903,7 @@
           <t>De opmerking dat de aanpak veel tijd kost voor een kleine school duidt op een zwakke of ontbrekende verankering in de schoolpraktijk, waarbij tijd en prioriteit mogelijk onvoldoende zijn afgestemd op de capaciteit van de school.</t>
         </is>
       </c>
-      <c r="J94" s="2" t="n">
+      <c r="J94" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -5959,7 +5961,7 @@
           <t>De opmerking gaat over de haalbaarheid van eisen voor een gezonde kantine, wat direct verband houdt met de mate waarin gezond eten binnen of nabij de school gemakkelijk te verkrijgen is. Dit sluit het beste aan bij de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J95" s="2" t="n">
+      <c r="J95" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -6017,7 +6019,7 @@
           <t>De opmerking gaat over de haalbaarheid van de eisen voor een gezonde kantine, wat direct verband houdt met de mate waarin gezond eten binnen de school gemakkelijk te verkrijgen is. Dit sluit het beste aan bij 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J96" s="2" t="n">
+      <c r="J96" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -6075,7 +6077,7 @@
           <t>De uitspraak benadrukt het belang van de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering, namelijk de blijvende uitvoering en brede betrokkenheid bij de aanpak.</t>
         </is>
       </c>
-      <c r="J97" s="2" t="n">
+      <c r="J97" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -6133,7 +6135,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak is goed' duidt op tevredenheid over de aanpak, wat het beste past bij 'Duurzame verankering' omdat dit verwijst naar blijvende uitvoering en brede betrokkenheid, wat een positieve waardering van de aanpak impliceert.</t>
         </is>
       </c>
-      <c r="J98" s="2" t="n">
+      <c r="J98" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -6191,7 +6193,7 @@
           <t>De uitspraak 'kan altijd beter' duidt op ontevredenheid over de huidige uitvoering en mogelijk een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk, wat aansluit bij de code 'Onvoldoende verankering'.</t>
         </is>
       </c>
-      <c r="J99" s="2" t="n">
+      <c r="J99" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -6249,7 +6251,7 @@
           <t>De opmerking verwijst naar de invloed van supermarkten in de buurt op de dagelijkse praktijk, wat direct verband houdt met de mate waarin gezond eten gemakkelijk verkrijgbaar is in of nabij de schoolomgeving. Dit sluit aan bij de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J100" s="2" t="n">
+      <c r="J100" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -6307,7 +6309,7 @@
           <t>De uiting 'De Gezonde School-aanpak is goed bezig' duidt op tevredenheid over de voortgang en continuïteit van de aanpak, wat aansluit bij het concept van duurzame verankering, namelijk blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J101" s="2" t="n">
+      <c r="J101" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -6365,7 +6367,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak op een goed niveau is, wat duidt op een blijvende en goed ingebedde uitvoering. Dit sluit aan bij 'Duurzame verankering', dat gaat over blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J102" s="2" t="n">
+      <c r="J102" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -6423,7 +6425,7 @@
           <t>De uitspraak 'kan nog beter worden' duidt op een tekortkoming of ruimte voor verbetering in de uitvoering of verankering van de Gezonde School-aanpak. De code 'Onvoldoende verankering' sluit hier goed op aan omdat deze verwijst naar een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk, wat een reden kan zijn voor ontevredenheid en de wens tot verbetering.</t>
         </is>
       </c>
-      <c r="J103" s="2" t="n">
+      <c r="J103" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -6481,7 +6483,7 @@
           <t>De uitspraak geeft aan dat het effect van de Gezonde School-aanpak niet duidelijk of aantoonbaar is, wat precies aansluit bij de code 'Onmeetbare effectiviteit' die bezorgdheid over niet zichtbare of meetbare resultaten beschrijft.</t>
         </is>
       </c>
-      <c r="J104" s="2" t="n">
+      <c r="J104" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -6539,7 +6541,7 @@
           <t>De opmerking gaat over de mate van belangstelling voor gezondheidsthema's binnen een specifieke sector, wat aansluit bij de zichtbare invoering van gezondheidsthema's op school. Hoewel het niet expliciet over implementatie gaat, raakt het wel aan het thema van brede invoering en acceptatie van gezondheidsthema's.</t>
         </is>
       </c>
-      <c r="J105" s="2" t="n">
+      <c r="J105" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -6597,7 +6599,7 @@
           <t>De uitspraak benadrukt dat het voor kinderen vanzelfsprekend is om gezonde tussendoortjes mee te nemen, wat duidt op een gemakkelijk verkrijgbare en geaccepteerde gezonde voedingsoptie binnen de schoolomgeving. Dit sluit goed aan bij de code 'Toegankelijkheid gezond voedingsaanbod', die gaat over de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is.</t>
         </is>
       </c>
-      <c r="J106" s="2" t="n">
+      <c r="J106" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -6655,7 +6657,7 @@
           <t>De uitdrukking 'staat op de agenda' duidt op een blijvende en structurele aandacht voor de Gezonde School-aanpak binnen de school, wat aansluit bij het concept van duurzame verankering zoals omschreven in de code.</t>
         </is>
       </c>
-      <c r="J107" s="2" t="n">
+      <c r="J107" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -6713,7 +6715,7 @@
           <t>De term 'vignetten' verwijst waarschijnlijk naar certificaten of erkenningen die behaald zijn, wat aansluit bij de code 'Certificaten als vrijwillige erkenning' die optionele erkenningen zonder verplichte opvolging beschrijft.</t>
         </is>
       </c>
-      <c r="J108" s="2" t="n">
+      <c r="J108" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -6771,7 +6773,7 @@
           <t>De opmerking 'De kantine is te duur' verwijst naar de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, waarbij de prijs een barrière vormt voor toegankelijkheid. Dit sluit goed aan bij de code 'Toegankelijkheid gezond voedingsaanbod' die gaat over de bereikbaarheid en beschikbaarheid van gezond eten op school.</t>
         </is>
       </c>
-      <c r="J109" s="2" t="n">
+      <c r="J109" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -6829,7 +6831,7 @@
           <t>De reactie geeft duidelijk aan dat de lestijd voor lichamelijke opvoeding verminderd wordt, wat precies overeenkomt met de definitie van de code 'Ingekorte sporturen' die verwijst naar vermindering van lestijd voor lichamelijke opvoeding die uitvoering van activiteiten beperkt.</t>
         </is>
       </c>
-      <c r="J110" s="2" t="n">
+      <c r="J110" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -6887,7 +6889,7 @@
           <t>De uitdrukking 'leeft niet echt' duidt op een zwakke of ontbrekende verankering van de Gezonde School-aanpak in de schoolpraktijk, wat precies aansluit bij de code 'Onvoldoende verankering' die spreekt over lage herkenning, prioriteit, tijd of handhaving.</t>
         </is>
       </c>
-      <c r="J111" s="2" t="n">
+      <c r="J111" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -6945,7 +6947,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak niet goed ingebed of betrokken is binnen de organisatie van de school, wat overeenkomt met het concept van 'Onvoldoende verankering' waarbij er een zwakke of ontbrekende verankering is in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J112" s="2" t="n">
+      <c r="J112" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -7003,7 +7005,7 @@
           <t>De uitspraak geeft aan dat collega's de verantwoordelijkheid voor de Gezonde School-aanpak hebben overgenomen, wat duidt op blijvende uitvoering en brede betrokkenheid binnen de school, passend bij 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J113" s="2" t="n">
+      <c r="J113" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -7061,7 +7063,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak het gewenste resultaat bereikt, wat duidt op een blijvende en succesvolle uitvoering van de aanpak. Dit sluit het beste aan bij 'Duurzame verankering', dat verwijst naar de blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J114" s="2" t="n">
+      <c r="J114" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -7119,7 +7121,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak leidt tot gezonder leven van leerlingen, wat direct aansluit bij de code 'Verbeterd gezondheidsgedrag' die verwijst naar een waargenomen toename van gezonde gedragingen bij leerlingen.</t>
         </is>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J115" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -7177,7 +7179,7 @@
           <t>De uitspraak 'Leerlingen bewegen meer' sluit direct aan bij het concept van een 'Ruim bewegingsaanbod', dat verwijst naar het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag. Dit is een duidelijke en directe match met de codeomschrijving.</t>
         </is>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J116" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -7235,7 +7237,7 @@
           <t>De uitspraak 'Leerlingen drinken minder alcohol' geeft direct een waargenomen toename van gezond gedrag aan, namelijk minder alcoholgebruik. Dit sluit nauw aan bij de code 'Verbeterd gezondheidsgedrag', die verwijst naar een toename van gezonde gedragingen bij leerlingen.</t>
         </is>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J117" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -7293,7 +7295,7 @@
           <t>De uitspraak 'Leerlingen roken minder' duidt op een concreet resultaat van een gezondheidsthema, namelijk rookpreventie, dat zichtbaar is binnen de school. De code 'Brede implementatie van gezondheidsthema's' omvat de invoering van initiatieven rond leefstijl en rookpreventie, wat hier direct van toepassing is.</t>
         </is>
       </c>
-      <c r="J118" s="2" t="n">
+      <c r="J118" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -7351,7 +7353,7 @@
           <t>De uitspraak benadrukt het belang van blijvende betrokkenheid van docenten bij de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering, namelijk de blijvende uitvoering door brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J119" s="2" t="n">
+      <c r="J119" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -7409,7 +7411,7 @@
           <t>De opmerking gaat over het moeilijk betrekken van alle docenten, wat duidt op een uitdaging in de blijvende uitvoering en brede betrokkenheid binnen de Gezonde School-aanpak, wat past bij 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J120" s="2" t="n">
+      <c r="J120" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -7467,7 +7469,7 @@
           <t>De uitspraak benadrukt het ophalen van informatie door de coördinator, wat aansluit bij het concept van regelmatige, eenduidige en verzorgde informatievoorziening binnen de school, zoals beschreven bij 'Consistente heldere communicatie'. Dit is de beste match binnen de gegeven opties.</t>
         </is>
       </c>
-      <c r="J121" s="2" t="n">
+      <c r="J121" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -7525,7 +7527,7 @@
           <t>De vermelding dat de school subsidie heeft ontvangen sluit direct aan bij het code label 'Financieringsmogelijkheden', dat gaat over beschikbare geldmiddelen en subsidieopties die de uitvoering en continuïteit van de Gezonde School-aanpak mogelijk maken. Dit is een directe en duidelijke match.</t>
         </is>
       </c>
-      <c r="J122" s="2" t="n">
+      <c r="J122" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -7583,7 +7585,7 @@
           <t>De uitspraak 'De school heeft ideeën opgedaan' duidt op het verkrijgen van inzichten of plannen die kunnen bijdragen aan de blijvende uitvoering van de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering.</t>
         </is>
       </c>
-      <c r="J123" s="2" t="n">
+      <c r="J123" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -7641,7 +7643,7 @@
           <t>De uitdrukking 'gezonde trommel' verwijst naar het aanbieden of meenemen van gezond voedsel, wat direct aansluit bij de code 'Toegankelijkheid gezond voedingsaanbod', die gaat over de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is.</t>
         </is>
       </c>
-      <c r="J124" s="2" t="n">
+      <c r="J124" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -7699,7 +7701,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak moet beter worden' duidt op ontevredenheid over de huidige uitvoering en verankering van de aanpak. Dit sluit aan bij 'Onvoldoende verankering', wat verwijst naar een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J125" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -7757,7 +7759,7 @@
           <t>De suggestie om structureel ontbijt aan te bieden valt direct onder het beleid en de voorzieningen gericht op gezond eten op school, wat precies wordt beschreven in 'Structureel voedingsbeleid'.</t>
         </is>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J126" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -7815,7 +7817,7 @@
           <t>De suggestie om meer sporten na schooltijd aan te bieden sluit direct aan bij het concept van een ruim bewegingsaanbod, dat staat voor frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag, inclusief na schooltijd.</t>
         </is>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J127" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -7873,7 +7875,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak gezonde keuzes in de kantine mogelijk maakt, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J128" s="2" t="n">
+      <c r="J128" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -7931,7 +7933,7 @@
           <t>De uitspraak geeft aan dat het criterium (gezonde keuzes kopen) voor het predicaat 'gezonde school' niet als belangrijk wordt gezien, wat duidt op onduidelijkheid of gebrek aan duidelijke beleidsregels of criteria rondom gezonde keuzes en erkenning. Dit sluit het beste aan bij 'Onvoldoende beleidsduidelijkheid traktaties', omdat het gaat om onduidelijkheid in beleid en regels, hoewel het niet specifiek over traktaties gaat, is dit de meest passende code binnen de gegeven opties.</t>
         </is>
       </c>
-      <c r="J129" s="2" t="n">
+      <c r="J129" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -7989,7 +7991,7 @@
           <t>De uitspraak benadrukt het belang van het welbevinden van leerlingen, wat aansluit bij een raamwerk dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert. Dit sluit het beste aan bij 'Effectief ingebed kader' omdat het idee gaat over het belang van welzijn als onderdeel van de Gezonde School-aanpak.</t>
         </is>
       </c>
-      <c r="J130" s="2" t="n">
+      <c r="J130" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -8047,7 +8049,7 @@
           <t>De uitspraak benadrukt het belang van het welbevinden van leerlingen, wat aansluit bij het betrekken van leerlingen bij besluitvorming en activiteiten om hun welbevinden te verbeteren, zoals beschreven bij 'Leerlinginspraak'.</t>
         </is>
       </c>
-      <c r="J131" s="2" t="n">
+      <c r="J131" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -8105,7 +8107,7 @@
           <t>De uitspraak benadrukt het belang van financiële haalbaarheid van de Gezonde School-aanpak, wat direct aansluit bij de code 'Financieringsmogelijkheden' die gaat over beschikbare geldmiddelen en subsidieopties voor uitvoering en continuïteit.</t>
         </is>
       </c>
-      <c r="J132" s="2" t="n">
+      <c r="J132" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -8163,7 +8165,7 @@
           <t>Het idee benadrukt het belang van enthousiasme binnen het team, wat duidt op betrokkenheid en brede steun. Dit sluit aan bij 'Duurzame verankering', dat gaat over blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J133" s="2" t="n">
+      <c r="J133" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -8221,7 +8223,7 @@
           <t>De term 'specifiek' suggereert dat de aanpak gericht en duidelijk afgebakend is, wat aansluit bij het concept van een brede en zichtbare implementatie van concrete gezondheidsthema's op school. Hoewel de formulering vaag is, past het het beste bij de code die verwijst naar een duidelijke en brede invoering van gezondheidsthema's.</t>
         </is>
       </c>
-      <c r="J134" s="2" t="n">
+      <c r="J134" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -8279,7 +8281,7 @@
           <t>De aanwezigheid van een programma-eigenaar duidt op een structurele en blijvende uitvoering van de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering door bestuurlijke steun en betrokkenheid.</t>
         </is>
       </c>
-      <c r="J135" s="2" t="n">
+      <c r="J135" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -8337,7 +8339,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak zichtbare acties heeft, wat aansluit bij de definitie van 'Brede implementatie van gezondheidsthema's' waarin concrete initiatieven rond leefstijl en gezondheid zichtbaar zijn op school.</t>
         </is>
       </c>
-      <c r="J136" s="2" t="n">
+      <c r="J136" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -8395,7 +8397,7 @@
           <t>De uitspraak 'Kinderen zijn zich bewuster' duidt op een toegenomen bewustwording bij kinderen, wat aansluit bij het code-label 'Handvatten voor gezonde leefstijl'. Deze code omvat concrete maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, wat hier het beste past.</t>
         </is>
       </c>
-      <c r="J137" s="2" t="n">
+      <c r="J137" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -8453,7 +8455,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak al lange tijd op de school wordt uitgevoerd, wat duidt op blijvende uitvoering en daarmee duurzame verankering volgens de definitie.</t>
         </is>
       </c>
-      <c r="J138" s="2" t="n">
+      <c r="J138" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -8511,7 +8513,7 @@
           <t>De uitspraak benadrukt dat gezond gedrag gemakkelijk te stimuleren is, wat direct aansluit bij het concept van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J139" s="2" t="n">
+      <c r="J139" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -8569,7 +8571,7 @@
           <t>De uitspraak benadrukt het stimuleren van gezond gedrag bij ouders, wat aansluit bij het code label 'Ouderlijke betrokkenheid' dat gaat over het informeren van ouders over gezondheidsthema's ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J140" s="2" t="n">
+      <c r="J140" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -8627,7 +8629,7 @@
           <t>De uitspraak geeft aan dat de uitvoering van de Gezonde School-aanpak niet goed genoeg is, wat wijst op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit goed aan bij de code 'Onvoldoende verankering' die verwijst naar lage herkenning, prioriteit, tijd of handhaving van de aanpak.</t>
         </is>
       </c>
-      <c r="J141" s="2" t="n">
+      <c r="J141" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -8685,7 +8687,7 @@
           <t>De opmerking dat leerkrachten moeten wennen aan de Gezonde School-aanpak duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk, wat aansluit bij de code 'Onvoldoende verankering'.</t>
         </is>
       </c>
-      <c r="J142" s="2" t="n">
+      <c r="J142" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -8743,7 +8745,7 @@
           <t>De opmerking dat oudere leerlingen moeten wennen aan de Gezonde School-aanpak duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk, wat aansluit bij de definitie van 'Onvoldoende verankering'.</t>
         </is>
       </c>
-      <c r="J143" s="2" t="n">
+      <c r="J143" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -8801,7 +8803,7 @@
           <t>De reactie benadrukt het informeren van ouders over de Gezonde School-aanpak, wat direct aansluit bij de code 'Ouderlijke betrokkenheid' die gaat over het informeren van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J144" s="2" t="n">
+      <c r="J144" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -8859,7 +8861,7 @@
           <t>De respondent geeft aan dat er controle moet zijn na het verkrijgen van het certificaat, wat direct verband houdt met de aard van certificaten als erkenning en de wens voor opvolging of controle na toekenning. Dit sluit aan bij de code 'Certificaten als vrijwillige erkenning', die certificaten beschrijft als optionele erkenning zonder verplichte opvolging, terwijl hier juist een wens voor controle wordt geuit.</t>
         </is>
       </c>
-      <c r="J145" s="2" t="n">
+      <c r="J145" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -8917,7 +8919,7 @@
           <t>De opmerking gaat over het feit dat het gezonde eten in de kantine niet altijd beschikbaar of gemakkelijk te verkrijgen is voor leerlingen, wat direct aansluit bij de code 'Toegankelijkheid gezond voedingsaanbod' die de mate van beschikbaarheid van gezond eten binnen of nabij school beschrijft.</t>
         </is>
       </c>
-      <c r="J146" s="2" t="n">
+      <c r="J146" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -8975,7 +8977,7 @@
           <t>De reactie geeft aan dat de Gezonde School-aanpak zich beperkt tot gezonde voeding, wat direct aansluit bij het concept van structureel voedingsbeleid, namelijk het aanwezig zijn van blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J147" s="2" t="n">
+      <c r="J147" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -9033,7 +9035,7 @@
           <t>De vermelding van 'leefstijl training' sluit aan bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, wat precies past bij de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J148" s="2" t="n">
+      <c r="J148" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -9091,7 +9093,7 @@
           <t>De vermelding van sportlessen binnen de Gezonde School-aanpak sluit direct aan bij het concept van een ruim bewegingsaanbod, dat staat voor frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J149" s="2" t="n">
+      <c r="J149" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -9149,7 +9151,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak is begonnen' duidt op het starten en mogelijk blijvend uitvoeren van de aanpak, wat aansluit bij het concept van duurzame verankering, namelijk de blijvende uitvoering van de Gezonde School-aanpak door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J150" s="2" t="n">
+      <c r="J150" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -9207,7 +9209,7 @@
           <t>De uitspraak 'Leerkrachten weten waar ze aan toe zijn' duidt op duidelijke en eenduidige informatievoorziening aan leerkrachten over de aanpak, wat aansluit bij de code 'Consistente heldere communicatie' die regelmatige, eenduidige en verzorgde informatievoorziening beschrijft.</t>
         </is>
       </c>
-      <c r="J151" s="2" t="n">
+      <c r="J151" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -9265,7 +9267,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak moet voortgezet worden' duidt op het belang van blijvende uitvoering en continuïteit van de aanpak, wat precies aansluit bij de code 'Duurzame verankering' die verwijst naar blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J152" s="2" t="n">
+      <c r="J152" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -9323,7 +9325,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak vooruitgang boekt en daarmee een positieve ontwikkeling doormaakt, wat aansluit bij het concept van blijvende uitvoering en brede betrokkenheid zoals beschreven bij 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J153" s="2" t="n">
+      <c r="J153" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -9381,7 +9383,7 @@
           <t>De idee benadrukt het bevorderen van betrokkenheid van verschillende groepen (leerkrachten, ouders, leerlingen), wat aansluit bij het concept van duurzame verankering waarbij brede betrokkenheid en blijvende uitvoering centraal staan.</t>
         </is>
       </c>
-      <c r="J154" s="2" t="n">
+      <c r="J154" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -9439,7 +9441,7 @@
           <t>De reactie benadrukt het belang van tijd en aandacht voor het werken aan een gezonde leefstijl, wat aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J155" s="2" t="n">
+      <c r="J155" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -9497,7 +9499,7 @@
           <t>De reactie benadrukt de invloed van ouders op het gedrag van kinderen, specifiek het kopen van vapes, wat direct aansluit bij het code-label 'Ouderlijke betrokkenheid' dat gaat over het informeren en betrekken van ouders bij gezondheidsthema's ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J156" s="2" t="n">
+      <c r="J156" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -9555,7 +9557,7 @@
           <t>De kern van de uitspraak is dat de Gezonde School-aanpak weinig invloed heeft op het gedrag van ouders die ongezond eten kopen. Dit sluit direct aan bij de code 'Ouderlijke betrokkenheid', die gaat over het informeren van ouders en hun rol in het ondersteunen van schoolinterventies op het gebied van gezondheid.</t>
         </is>
       </c>
-      <c r="J157" s="2" t="n">
+      <c r="J157" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -9613,7 +9615,7 @@
           <t>De uitspraak 'lastig te handhaven' duidt op problemen met de verankering van de aanpak in de schoolpraktijk, wat overeenkomt met de code 'Onvoldoende verankering' die verwijst naar zwakke of ontbrekende verankering zichtbaar in lage herkenning, prioriteit, tijd of handhaving.</t>
         </is>
       </c>
-      <c r="J158" s="2" t="n">
+      <c r="J158" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -9671,7 +9673,7 @@
           <t>De fusie met een school die niet meedeed aan het traject kan duiden op een zwakke of ontbrekende verankering van de Gezonde School-aanpak in de nieuwe schoolpraktijk, wat aansluit bij de code 'Onvoldoende verankering'.</t>
         </is>
       </c>
-      <c r="J159" s="2" t="n">
+      <c r="J159" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -9729,7 +9731,7 @@
           <t>De reactie geeft duidelijk aan dat er weerstand is tegen het traktatiebeleid, wat wijst op een gebrek aan duidelijke regels en communicatie rondom traktaties, precies wat de code 'Onvoldoende beleidsduidelijkheid traktaties' beschrijft.</t>
         </is>
       </c>
-      <c r="J160" s="2" t="n">
+      <c r="J160" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -9787,7 +9789,7 @@
           <t>De weerstand tegen het letten op de gezonde lunch duidt op problemen met duidelijke regels en communicatie rondom gezonde voeding, wat aansluit bij 'Onvoldoende beleidsduidelijkheid traktaties' die verwijst naar afwezigheid van duidelijke traktatieregels en zichtbare weerstand bij handhaving.</t>
         </is>
       </c>
-      <c r="J161" s="2" t="n">
+      <c r="J161" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -9845,7 +9847,7 @@
           <t>De uitspraak 'geeft goed richting aan de school' duidt op een blijvende en duidelijke verankering van de Gezonde School-aanpak binnen de school, wat aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J162" s="2" t="n">
+      <c r="J162" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -9903,7 +9905,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak werkt voor onze school' duidt op een positieve, blijvende uitvoering van de aanpak, wat aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J163" s="2" t="n">
+      <c r="J163" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -9961,7 +9963,7 @@
           <t>De uitspraak 'zet aan tot actie' duidt op het stimuleren van concrete maatregelen en gedragsverandering, wat aansluit bij de code 'Handvatten voor gezonde leefstijl' die gaat over uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren.</t>
         </is>
       </c>
-      <c r="J164" s="2" t="n">
+      <c r="J164" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -10019,7 +10021,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak een stimulerende werking heeft op leerlingen, wat het beste aansluit bij het concept van een 'Ruim bewegingsaanbod' dat frequente en gevarieerde bewegingsmomenten stimuleert. Hoewel het niet expliciet over sportfunctionarissen gaat, past het idee van stimulering van leerlingen het beste bij het stimuleren van beweging binnen de schoolcontext.</t>
         </is>
       </c>
-      <c r="J165" s="2" t="n">
+      <c r="J165" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -10077,7 +10079,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak bijdraagt aan bewustwording bij ouders, wat direct aansluit bij het code label 'Ouderlijke betrokkenheid' dat gaat over het informeren van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J166" s="2" t="n">
+      <c r="J166" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -10135,7 +10137,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak helpt bij het bewustwordingsproces van collega's, wat aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J167" s="2" t="n">
+      <c r="J167" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -10193,7 +10195,7 @@
           <t>De idee beschrijft het aanbieden van een gezonde lunch, wat direct aansluit bij het code label 'Structureel voedingsbeleid' dat verwijst naar blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J168" s="2" t="n">
+      <c r="J168" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -10251,7 +10253,7 @@
           <t>De idee benadrukt de aanwezigheid van een vakdocent die aandacht besteedt aan sport, wat overeenkomt met de definitie van 'Actieve sportfunctionaris' als een interne functionaris die actief sportactiviteiten binnen de school promoot.</t>
         </is>
       </c>
-      <c r="J169" s="2" t="n">
+      <c r="J169" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -10309,7 +10311,7 @@
           <t>De idee benadrukt de aanwezigheid van aandacht voor sociaal emotionele ontwikkeling, wat valt onder de integratie van brede gezondheidsthema's zoals sociaal-emotionele onderwerpen in schoolbeleid en onderwijs. Dit sluit goed aan bij de code 'Aandacht voor brede gezondheidsthema's'.</t>
         </is>
       </c>
-      <c r="J170" s="2" t="n">
+      <c r="J170" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -10367,7 +10369,7 @@
           <t>De reactie benadrukt het creëren van bewustwording over het belang van de gezonde school, wat aansluit bij het bieden van concrete maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J171" s="2" t="n">
+      <c r="J171" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -10425,7 +10427,7 @@
           <t>De uitspraak geeft aan dat een belangrijke doelgroep (leerlingen die het meest nodig hebben) moeilijk te bereiken is, wat wijst op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit aan bij de definitie van 'Onvoldoende verankering', waar lage herkenning, prioriteit of tijd een rol spelen.</t>
         </is>
       </c>
-      <c r="J172" s="2" t="n">
+      <c r="J172" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -10483,7 +10485,7 @@
           <t>De uitspraak benadrukt dat de gezonde schoolweek belangrijke onderwerpen bevat, wat aansluit bij de brede invoering van gezondheidsthema's op school zoals leefstijl, voeding, gewicht en rookpreventie.</t>
         </is>
       </c>
-      <c r="J173" s="2" t="n">
+      <c r="J173" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -10541,7 +10543,7 @@
           <t>De opmerking geeft aan dat de onderwerpen van de gezonde schoolweek niet altijd goed worden gegeven, wat kan duiden op een gebrek aan duidelijke richtlijnen of beleid. Hoewel de code 'Onvoldoende beleidsduidelijkheid traktaties' specifiek over traktatieregels gaat, is dit de dichtstbijzijnde code die wijst op onduidelijkheid of problemen in de uitvoering van onderdelen van de Gezonde School-aanpak. Andere codes zijn minder relevant voor het aspect van onvoldoende goede uitvoering van onderwerpen.</t>
         </is>
       </c>
-      <c r="J174" s="2" t="n">
+      <c r="J174" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -10599,7 +10601,7 @@
           <t>De opmerking dat de onderwerpen van de gezonde schoolweek niet altijd beklijven duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk, wat overeenkomt met de definitie van 'Onvoldoende verankering'.</t>
         </is>
       </c>
-      <c r="J175" s="2" t="n">
+      <c r="J175" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -10657,7 +10659,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak bewustwording geeft, wat aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J176" s="2" t="n">
+      <c r="J176" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -10715,7 +10717,7 @@
           <t>De uitspraak 'biedt gerichte aandacht' suggereert een gerichte en zichtbare invoering van initiatieven rond gezondheidsthema's, wat aansluit bij de definitie van 'Brede implementatie van gezondheidsthema's' die gaat over zichtbare terreinoverstijgende invoering van concrete initiatieven rond leefstijl, voeding, gewicht en rookpreventie op school.</t>
         </is>
       </c>
-      <c r="J177" s="2" t="n">
+      <c r="J177" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -10773,7 +10775,7 @@
           <t>De uitspraak 'moet verder worden ontwikkeld' duidt op de wens om de aanpak blijvend te verbeteren en te verankeren binnen de school, wat aansluit bij het concept van duurzame verankering zoals beschreven.</t>
         </is>
       </c>
-      <c r="J178" s="2" t="n">
+      <c r="J178" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -10831,7 +10833,7 @@
           <t>De reactie benadrukt het belang van aandacht voor bewegen binnen de Gezonde School-aanpak, wat direct aansluit bij het code-label 'Ruim bewegingsaanbod', dat gaat over het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J179" s="2" t="n">
+      <c r="J179" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -10889,7 +10891,7 @@
           <t>De reactie richt zich op het bevorderen van gezonde lunches, wat direct verband houdt met de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is. Dit sluit goed aan bij de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J180" s="2" t="n">
+      <c r="J180" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -10947,7 +10949,7 @@
           <t>De reactie richt zich expliciet op het vermijden van ongezonde tussendoortjes, wat direct aansluit bij het beleid om het aanbod en de zichtbaarheid van snoep, snacks en frisdrank op school te verminderen, zoals beschreven in de code 'Beperken van ongezonde producten'.</t>
         </is>
       </c>
-      <c r="J181" s="2" t="n">
+      <c r="J181" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -11005,7 +11007,7 @@
           <t>De reactie richt zich expliciet op het aanpakken van ongezonde snacks, wat direct aansluit bij het code label 'Beperken van ongezonde producten', dat gaat over acties of beleid om het aanbod en de zichtbaarheid van snoep, snacks en frisdrank op school te verminderen.</t>
         </is>
       </c>
-      <c r="J182" s="2" t="n">
+      <c r="J182" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -11063,7 +11065,7 @@
           <t>De opmerking over betere temperaturen in lokalen verwijst naar een aspect van de fysieke omgeving dat mogelijk bijdraagt aan een gezonde schoolomgeving. Hoewel geen perfecte match, sluit dit het beste aan bij 'Duurzame verankering' omdat het gaat om blijvende uitvoering en verbetering van de schoolomgeving binnen de Gezonde School-aanpak.</t>
         </is>
       </c>
-      <c r="J183" s="2" t="n">
+      <c r="J183" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -11121,7 +11123,7 @@
           <t>De reactie geeft duidelijk aan dat er behoefte is aan meer tijd en aandacht voor gezondheid, wat direct aansluit bij de code 'Meer lestijd voor gezondheidseducatie' die vraagt om een toename van lesuren voor gezondheidseducatie.</t>
         </is>
       </c>
-      <c r="J184" s="2" t="n">
+      <c r="J184" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -11179,7 +11181,7 @@
           <t>De reactie benadrukt het belang van bewustwording van een gezonde levensstijl, wat direct aansluit bij het code-label 'Handvatten voor gezonde leefstijl' dat concrete maatregelen en hulpmiddelen omvat die bewustwording en gezond gedrag stimuleren.</t>
         </is>
       </c>
-      <c r="J185" s="2" t="n">
+      <c r="J185" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -11237,7 +11239,7 @@
           <t>De uitspraak 'stimuleert de aandacht' duidt op het bieden van concrete maatregelen of hulpmiddelen die bewustwording en gezond gedrag stimuleren, wat aansluit bij de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J186" s="2" t="n">
+      <c r="J186" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
@@ -11295,7 +11297,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak moet beter worden' duidt op ontevredenheid over de huidige uitvoering en verankering van de aanpak. Dit sluit aan bij 'Onvoldoende verankering', wat verwijst naar een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk, wat de reden kan zijn voor de wens tot verbetering.</t>
         </is>
       </c>
-      <c r="J187" s="2" t="n">
+      <c r="J187" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -11353,7 +11355,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak een middel is om het welbevinden te bevorderen, wat aansluit bij het concept van een raamwerk dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert, zoals beschreven bij 'Effectief ingebed kader'.</t>
         </is>
       </c>
-      <c r="J188" s="2" t="n">
+      <c r="J188" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -11411,7 +11413,7 @@
           <t>De term 'nieuwe paraplu' suggereert een overkoepelend, blijvend kader of structuur voor de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering waarbij de aanpak blijvend wordt uitgevoerd door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J189" s="2" t="n">
+      <c r="J189" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -11469,7 +11471,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak niet langer als een prioriteit of doel wordt gezien, wat duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit goed aan bij de code 'Onvoldoende verankering', die verwijst naar lage herkenning, prioriteit of tijd voor de aanpak.</t>
         </is>
       </c>
-      <c r="J190" s="2" t="n">
+      <c r="J190" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
@@ -11527,7 +11529,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak gaat goed' duidt op een positieve beoordeling van de uitvoering en continuïteit van de aanpak, wat aansluit bij het concept van 'Duurzame verankering' waarbij blijvende uitvoering door bestuurlijke steun en brede betrokkenheid centraal staat.</t>
         </is>
       </c>
-      <c r="J191" s="2" t="n">
+      <c r="J191" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -11585,7 +11587,7 @@
           <t>De opmerking gaat over het verbeteren van de aanpak met betrekking tot het welzijn van leerlingen, wat aansluit bij een raamwerk dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert. Dit sluit het beste aan bij 'Effectief ingebed kader'.</t>
         </is>
       </c>
-      <c r="J192" s="2" t="n">
+      <c r="J192" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
@@ -11643,7 +11645,7 @@
           <t>De uitspraak richt zich op het bewust maken van leerlingen over gezond eten, wat direct aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J193" s="2" t="n">
+      <c r="J193" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -11701,7 +11703,7 @@
           <t>De idee richt zich op het bewust maken van ouders over gezond eten, wat direct aansluit bij de code 'Ouderlijke betrokkenheid' die gaat over het informeren van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J194" s="2" t="n">
+      <c r="J194" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
@@ -11759,7 +11761,7 @@
           <t>De uitspraak verwijst naar een verandering in de maatschappelijke opvattingen over gezondheid, wat aansluit bij het concept van brede implementatie van gezondheidsthema's op school, waarbij gezondheid op meerdere terreinen zichtbaar wordt ingevoerd.</t>
         </is>
       </c>
-      <c r="J195" s="2" t="n">
+      <c r="J195" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -11817,7 +11819,7 @@
           <t>De uitspraak 'Gezondheid is nu meer vanzelfsprekend' duidt op een blijvende en geïntegreerde aanwezigheid van gezondheid binnen de school, wat aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering van de Gezonde School-aanpak door brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J196" s="2" t="n">
+      <c r="J196" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -11875,7 +11877,7 @@
           <t>De uitspraak verwijst expliciet naar het betrekken van ouders in de Gezonde School-aanpak, wat precies past bij de code 'Ouderlijke betrokkenheid' die gaat over het informeren en betrekken van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J197" s="2" t="n">
+      <c r="J197" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
@@ -11933,7 +11935,7 @@
           <t>De uitspraak 'De aanpak sluit nu aan bij ouders' duidt op het betrekken en informeren van ouders over gezondheidsthema's ter ondersteuning van schoolinterventies, wat precies past bij de code 'Ouderlijke betrokkenheid'.</t>
         </is>
       </c>
-      <c r="J198" s="2" t="n">
+      <c r="J198" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
@@ -11991,7 +11993,7 @@
           <t>De uitdrukking 'Gezond gedrag is vanzelfsprekend' duidt op een situatie waarin gezond gedrag structureel en blijvend is geïntegreerd in de schoolcultuur, wat aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering van de Gezonde School-aanpak door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J199" s="2" t="n">
+      <c r="J199" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
@@ -12049,7 +12051,7 @@
           <t>De uitspraak benadrukt het belang van het maken van afspraken om de Gezonde School-aanpak te kunnen uitvoeren, wat aansluit bij het concept van blijvende uitvoering door bestuurlijke steun en brede betrokkenheid, zoals beschreven bij 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J200" s="2" t="n">
+      <c r="J200" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K200" s="2" t="inlineStr">
@@ -12107,7 +12109,7 @@
           <t>De uitspraak benadrukt het belang van het vasthouden aan een visie bij nieuwe afspraken of regels, wat aansluit bij het concept van blijvende uitvoering en bestuurlijke steun zoals beschreven in 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J201" s="2" t="n">
+      <c r="J201" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -12165,7 +12167,7 @@
           <t>De uitspraak benadrukt het belang van het vasthouden aan de uitgangspunten van de Gezonde School, wat aansluit bij het concept van blijvende uitvoering en bestuurlijke steun zoals beschreven bij 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J202" s="2" t="n">
+      <c r="J202" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K202" s="2" t="inlineStr">
@@ -12223,7 +12225,7 @@
           <t>De uitspraak 'De gezonde school moet betere beslissingen maken voor de school' duidt op een behoefte aan verbeterde en blijvende besluitvorming en uitvoering binnen de Gezonde School-aanpak. Dit sluit aan bij 'Duurzame verankering', dat gaat over blijvende uitvoering door bestuurlijke steun en brede betrokkenheid, wat nodig is voor betere beslissingen en continuïteit.</t>
         </is>
       </c>
-      <c r="J203" s="2" t="n">
+      <c r="J203" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -12281,7 +12283,7 @@
           <t>De uitspraak suggereert dat de Gezonde School-aanpak invloed heeft op beleidskeuzes, wat aansluit bij het concept van blijvende uitvoering en bestuurlijke steun zoals beschreven bij 'Duurzame verankering'. Dit is de beste match binnen de gegeven opties.</t>
         </is>
       </c>
-      <c r="J204" s="2" t="n">
+      <c r="J204" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -12339,7 +12341,7 @@
           <t>De uitdrukking 'moreel kompas' duidt op een diepgaande, blijvende richtlijn of leidraad binnen de school, wat aansluit bij het concept van 'Duurzame verankering' waarbij de aanpak blijvend wordt uitgevoerd door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J205" s="2" t="n">
+      <c r="J205" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K205" s="2" t="inlineStr">
@@ -12397,7 +12399,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak informatief is via de lessen, wat aansluit bij het concept van regelmatige, eenduidige en verzorgde informatievoorziening aan betrokkenen, zoals beschreven in 'Consistente heldere communicatie'.</t>
         </is>
       </c>
-      <c r="J206" s="2" t="n">
+      <c r="J206" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K206" s="2" t="inlineStr">
@@ -12455,7 +12457,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak breed wordt gedragen door verschillende groepen binnen de schoolgemeenschap, wat wijst op blijvende uitvoering en brede betrokkenheid, precies wat 'Duurzame verankering' beschrijft.</t>
         </is>
       </c>
-      <c r="J207" s="2" t="n">
+      <c r="J207" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K207" s="2" t="inlineStr">
@@ -12513,7 +12515,7 @@
           <t>De uitspraak benadrukt het belang van de Gezonde School-aanpak voor de ontwikkeling van jongeren, wat aansluit bij het concept van blijvende uitvoering en brede betrokkenheid zoals beschreven in 'Duurzame verankering'. Dit codeert de waardering voor de continuïteit en impact van de aanpak op lange termijn.</t>
         </is>
       </c>
-      <c r="J208" s="2" t="n">
+      <c r="J208" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -12571,7 +12573,7 @@
           <t>De uitspraak 'bevordert bewustzijn' sluit goed aan bij het bieden van concrete maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, wat precies de kern is van de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J209" s="2" t="n">
+      <c r="J209" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -12629,7 +12631,7 @@
           <t>De uitspraak 'stimuleert zorgen voor jezelf' sluit goed aan bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, wat precies de kern is van de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J210" s="2" t="n">
+      <c r="J210" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K210" s="2" t="inlineStr">
@@ -12687,7 +12689,7 @@
           <t>De uiting benadrukt het stimuleren van zorg voor anderen, wat kan duiden op betrokkenheid en participatie van leerlingen bij welzijnsaspecten, wat het beste aansluit bij 'Leerlinginspraak' als leerlingen betrokken worden bij besluitvorming en activiteiten voor hun welbevinden. Hoewel het niet expliciet over inspraak gaat, is dit de meest relevante code binnen de gegeven opties.</t>
         </is>
       </c>
-      <c r="J211" s="2" t="n">
+      <c r="J211" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="K211" s="2" t="inlineStr">
@@ -12745,7 +12747,7 @@
           <t>De uitspraak 'Leerlingen drinken meer water' geeft direct een waargenomen toename van gezond gedrag aan, wat precies past bij de code 'Verbeterd gezondheidsgedrag' die gezonde gedragingen zoals vaker water drinken omvat.</t>
         </is>
       </c>
-      <c r="J212" s="2" t="n">
+      <c r="J212" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -12803,7 +12805,7 @@
           <t>De uitspraak 'Leerlingen eten meer groente' geeft direct aan dat er een toename is in gezond gedrag van leerlingen, wat precies past bij de code 'Verbeterd gezondheidsgedrag' die verwijst naar waargenomen toename van gezonde gedragingen bij leerlingen.</t>
         </is>
       </c>
-      <c r="J213" s="2" t="n">
+      <c r="J213" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K213" s="2" t="inlineStr">
@@ -12861,7 +12863,7 @@
           <t>De idee beschrijft expliciet een toename in fruitconsumptie door leerlingen, wat direct overeenkomt met de code 'Toegenomen fruitconsumptie' die aangeeft dat er een toename is van fruitconsumptie tijdens schooltijd.</t>
         </is>
       </c>
-      <c r="J214" s="2" t="n">
+      <c r="J214" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K214" s="2" t="inlineStr">
@@ -12919,7 +12921,7 @@
           <t>De idee beschrijft dat gezonde producten worden aangeboden, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals omschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J215" s="2" t="n">
+      <c r="J215" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -12977,7 +12979,7 @@
           <t>De reactie benadrukt dat subsidie (financiering) helpt bij het aanbieden van gezonde producten, wat direct aansluit bij de code 'Financieringsmogelijkheden' die gaat over beschikbare geldmiddelen en subsidieopties die uitvoering en continuïteit van de aanpak mogelijk maken.</t>
         </is>
       </c>
-      <c r="J216" s="2" t="n">
+      <c r="J216" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K216" s="2" t="inlineStr">
@@ -13035,7 +13037,7 @@
           <t>De reactie geeft aan dat er vooruitgang is geboekt op het gebied van voeding binnen de Gezonde School-aanpak, wat aansluit bij het concept van 'Structureel voedingsbeleid' dat verwijst naar blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J217" s="2" t="n">
+      <c r="J217" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -13093,7 +13095,7 @@
           <t>De reactie benadrukt dat de gezonde kantine leerlingen helpt te zien wat er qua eten mogelijk is, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J218" s="2" t="n">
+      <c r="J218" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K218" s="2" t="inlineStr">
@@ -13151,7 +13153,7 @@
           <t>De uitspraak dat de Gezonde School-aanpak soms moeilijk toe te passen is, duidt op problemen met de verankering van de aanpak in de schoolpraktijk. Dit sluit aan bij de code 'Onvoldoende verankering', die verwijst naar een zwakke of ontbrekende verankering van de aanpak, zichtbaar in lage herkenning, prioriteit, tijd of handhaving.</t>
         </is>
       </c>
-      <c r="J219" s="2" t="n">
+      <c r="J219" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K219" s="2" t="inlineStr">
@@ -13209,7 +13211,7 @@
           <t>De opmerking over 'strenge maatregelen' sluit aan bij het idee van concrete uitvoerbare maatregelen die bewustwording en gezond gedrag stimuleren, wat past bij de code 'Handvatten voor gezonde leefstijl'. Andere codes zijn minder relevant omdat ze niet direct betrekking hebben op maatregelen of gedragsstimulering.</t>
         </is>
       </c>
-      <c r="J220" s="2" t="n">
+      <c r="J220" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
@@ -13267,7 +13269,7 @@
           <t>De term 'sportief' in de reactie verwijst naar een actieve, bewegingsgerichte invulling van de Gezonde School-aanpak. Dit sluit het beste aan bij 'Ruim bewegingsaanbod', dat gaat over frequente, gevarieerde en toegankelijke bewegingsmomenten binnen de school.</t>
         </is>
       </c>
-      <c r="J221" s="2" t="n">
+      <c r="J221" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K221" s="2" t="inlineStr">
@@ -13325,7 +13327,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak rekening houdt met bewegend leren, wat direct aansluit bij het concept van een ruim bewegingsaanbod, namelijk frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J222" s="2" t="n">
+      <c r="J222" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
@@ -13383,7 +13385,7 @@
           <t>De suggestie om aandacht te besteden aan water drinken sluit direct aan bij het stimuleren van gezond gedrag bij leerlingen, wat precies wordt beschreven in de code 'Verbeterd gezondheidsgedrag'.</t>
         </is>
       </c>
-      <c r="J223" s="2" t="n">
+      <c r="J223" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K223" s="2" t="inlineStr">
@@ -13441,7 +13443,7 @@
           <t>De reactie benadrukt het belang van aandacht voor gezond eten, specifiek in de ochtend, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J224" s="2" t="n">
+      <c r="J224" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
@@ -13499,7 +13501,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak moet leiden tot verbetering, wat aansluit bij het concept van een 'Effectief ingebed kader' dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert. Dit is de beste match binnen de gegeven codes, omdat het gaat om het beoogde resultaat van de aanpak.</t>
         </is>
       </c>
-      <c r="J225" s="2" t="n">
+      <c r="J225" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -13557,7 +13559,7 @@
           <t>De uiting geeft aan dat externe invloeden de intenties van de Gezonde School-aanpak overspoelen, wat duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit goed aan bij de code 'Onvoldoende verankering', die verwijst naar een lage herkenning, prioriteit of tijd voor de aanpak.</t>
         </is>
       </c>
-      <c r="J226" s="2" t="n">
+      <c r="J226" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
@@ -13615,7 +13617,7 @@
           <t>De uiting 'goede leidraad' duidt op concrete uitvoerbare maatregelen of hulpmiddelen die de Gezonde School-aanpak biedt om een gezonde leefstijl te stimuleren, wat aansluit bij de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J227" s="2" t="n">
+      <c r="J227" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K227" s="2" t="inlineStr">
@@ -13673,7 +13675,7 @@
           <t>De uitspraak geeft aan dat gezonde voeding moeilijk bereikbaar of beschikbaar is voor veel mensen, wat direct aansluit bij de code 'Toegankelijkheid gezond voedingsaanbod', die gaat over de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is.</t>
         </is>
       </c>
-      <c r="J228" s="2" t="n">
+      <c r="J228" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
@@ -13731,7 +13733,7 @@
           <t>De opmerking benadrukt dat gezonde voeding voor mensen verschillend is, wat aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is en aansluit bij diversiteit in aanbod en toegankelijkheid.</t>
         </is>
       </c>
-      <c r="J229" s="2" t="n">
+      <c r="J229" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K229" s="2" t="inlineStr">
@@ -13789,7 +13791,7 @@
           <t>De uitspraak benadrukt het belang van bewustwording over gezonde voeding, wat direct aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J230" s="2" t="n">
+      <c r="J230" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K230" s="2" t="inlineStr">
@@ -13847,7 +13849,7 @@
           <t>De idee benadrukt het belang van het bewust maken van ouders over een gezonde leefstijl, wat direct aansluit bij de code 'Ouderlijke betrokkenheid' die gaat over het informeren van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J231" s="2" t="n">
+      <c r="J231" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K231" s="2" t="inlineStr">
@@ -13905,7 +13907,7 @@
           <t>De uitspraak 'moet behouden blijven' duidt op het belang van blijvende uitvoering en continuïteit van de Gezonde School-aanpak, wat precies aansluit bij de code 'Duurzame verankering' die verwijst naar blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J232" s="2" t="n">
+      <c r="J232" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
@@ -13963,7 +13965,7 @@
           <t>De uitspraak benadrukt het belang van gezondheid als fundamentele voorwaarde voor goed onderwijs, wat aansluit bij het concept van duurzame verankering waarbij gezondheid blijvend geïntegreerd wordt in de schoolpraktijk en bestuurlijke steun krijgt.</t>
         </is>
       </c>
-      <c r="J233" s="2" t="n">
+      <c r="J233" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -14021,7 +14023,7 @@
           <t>De uitspraak benadrukt het belang van een gezonde levensstijl voor goed onderwijs, wat aansluit bij het bieden van concrete maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J234" s="2" t="n">
+      <c r="J234" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
@@ -14079,7 +14081,7 @@
           <t>De uitspraak geeft aan dat de huidige Gezonde School-aanpak niet naar wens is en verbetering behoeft, wat wijst op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit aan bij de code 'Onvoldoende verankering' die verwijst naar een lage herkenning, prioriteit of tijd voor de aanpak.</t>
         </is>
       </c>
-      <c r="J235" s="2" t="n">
+      <c r="J235" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K235" s="2" t="inlineStr">
@@ -14137,7 +14139,7 @@
           <t>De uitspraak geeft aan dat de aanpak goed functioneert en impliceert een blijvende, succesvolle uitvoering, wat aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J236" s="2" t="n">
+      <c r="J236" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
@@ -14195,7 +14197,7 @@
           <t>De uitspraak 'Er is veel te halen qua gezondheid van leerlingen' impliceert dat er ruimte is voor verbetering in het gezondheidsgedrag van leerlingen. Dit sluit goed aan bij de code 'Verbeterd gezondheidsgedrag', die verwijst naar waargenomen toename van gezonde gedragingen bij leerlingen. Hoewel de uitspraak niet expliciet zegt dat het gedrag al verbeterd is, geeft het wel aan dat er potentie is voor verbetering, wat een sterke match is met deze code.</t>
         </is>
       </c>
-      <c r="J237" s="2" t="n">
+      <c r="J237" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -14253,7 +14255,7 @@
           <t>De uitspraak verwijst naar het potentieel voor verbetering van de gezondheid van ouders, wat aansluit bij het code-label 'Ouderlijke betrokkenheid' dat gaat over het informeren en betrekken van ouders bij gezondheidsthema's ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J238" s="2" t="n">
+      <c r="J238" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
@@ -14311,7 +14313,7 @@
           <t>De reactie benadrukt het belang van veel aandacht voor sport en bewegen binnen de Gezonde School-aanpak, wat direct aansluit bij het code label 'Ruim bewegingsaanbod' dat verwijst naar een gevarieerd en frequent aanbod van bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J239" s="2" t="n">
+      <c r="J239" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K239" s="2" t="inlineStr">
@@ -14369,7 +14371,7 @@
           <t>De opmerking dat de aanpak 'directief overkomt' duidt op een perceptie van de manier waarop de communicatie en uitvoering van de aanpak plaatsvindt. 'Consistente heldere communicatie' gaat over regelmatige, eenduidige en verzorgde informatievoorziening, wat hier relevant is omdat een directieve aanpak vaak samenhangt met de wijze van communiceren en informeren.</t>
         </is>
       </c>
-      <c r="J240" s="2" t="n">
+      <c r="J240" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K240" s="2" t="inlineStr">
@@ -14427,7 +14429,7 @@
           <t>De uitspraak geeft aan dat de aanpak niet consequent wordt gehandhaafd, wat duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit direct aan bij de definitie van 'Onvoldoende verankering'.</t>
         </is>
       </c>
-      <c r="J241" s="2" t="n">
+      <c r="J241" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -14485,7 +14487,7 @@
           <t>De uitspraak geeft aan dat niet iedereen binnen de school het belang van de Gezonde School-aanpak inziet, wat wijst op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit goed aan bij de code 'Onvoldoende verankering', die lage herkenning en prioriteit binnen de school beschrijft.</t>
         </is>
       </c>
-      <c r="J242" s="2" t="n">
+      <c r="J242" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K242" s="2" t="inlineStr">
@@ -14543,7 +14545,7 @@
           <t>De uitspraak geeft aan dat studenten prioriteit geven aan diploma halen boven een gezonde leefstijl, wat impliceert dat er mogelijk een gebrek is aan concrete maatregelen of hulpmiddelen die gezonde leefstijl stimuleren. Dit sluit het beste aan bij 'Handvatten voor gezonde leefstijl', omdat het gaat om het stimuleren van gezond gedrag.</t>
         </is>
       </c>
-      <c r="J243" s="2" t="n">
+      <c r="J243" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K243" s="2" t="inlineStr">
@@ -14601,7 +14603,7 @@
           <t>De idee benadrukt dat studenten zelf bepalen hoe ze een gezonde leefstijl invullen, wat direct aansluit bij het concept van 'Leerlinginspraak', waarbij leerlingen betrokken worden bij besluitvorming en activiteiten die hun welzijn verbeteren.</t>
         </is>
       </c>
-      <c r="J244" s="2" t="n">
+      <c r="J244" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K244" s="2" t="inlineStr">
@@ -14659,7 +14661,7 @@
           <t>De uitspraak 'moet verantwoordelijk eten maken' verwijst naar het bevorderen van gezond en verantwoord eten binnen de Gezonde School-aanpak. Dit sluit het beste aan bij de code 'Toegankelijkheid gezond voedingsaanbod', die gaat over de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is.</t>
         </is>
       </c>
-      <c r="J245" s="2" t="n">
+      <c r="J245" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K245" s="2" t="inlineStr">
@@ -14717,7 +14719,7 @@
           <t>De opmerking dat de Gezonde School-aanpak niet 'vet afwisselend' moet zijn, duidt op een wens voor een vaste, consistente programmaopzet met een jaarlijkse themawissel die uitvoering en voortgang faciliteert, wat aansluit bij de code 'Programmastructuur voor continuïteit'.</t>
         </is>
       </c>
-      <c r="J246" s="2" t="n">
+      <c r="J246" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K246" s="2" t="inlineStr">
@@ -14775,7 +14777,7 @@
           <t>De opmerking over een 'redelijke prijs' verwijst direct naar de beschikbaarheid van geldmiddelen en financiering, wat precies valt onder 'Financieringsmogelijkheden'. Dit codeert de noodzaak van betaalbare financiering voor de uitvoering en continuïteit van de Gezonde School-aanpak.</t>
         </is>
       </c>
-      <c r="J247" s="2" t="n">
+      <c r="J247" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K247" s="2" t="inlineStr">
@@ -14833,7 +14835,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak zich richt op bewegen, wat direct aansluit bij het code label 'Ruim bewegingsaanbod', dat gaat over het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J248" s="2" t="n">
+      <c r="J248" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K248" s="2" t="inlineStr">
@@ -14891,7 +14893,7 @@
           <t>De uitspraak 'De school is dagelijks bezig met gym' duidt op een frequente en actieve inzet van bewegingsmomenten gedurende de schooldag, wat precies past bij de definitie van 'Ruim bewegingsaanbod' als een aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten.</t>
         </is>
       </c>
-      <c r="J249" s="2" t="n">
+      <c r="J249" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K249" s="2" t="inlineStr">
@@ -14949,7 +14951,7 @@
           <t>De uitspraak 'De school is dagelijks bezig met beweging' sluit direct aan bij het code label 'Ruim bewegingsaanbod', dat verwijst naar een aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag. Dit is een uitstekende match omdat het idee expliciet aangeeft dat beweging dagelijks plaatsvindt op school.</t>
         </is>
       </c>
-      <c r="J250" s="2" t="n">
+      <c r="J250" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K250" s="2" t="inlineStr">
@@ -15007,7 +15009,7 @@
           <t>De uitspraak 'De school is dagelijks bezig met bewegend leren' duidt op een frequente en actieve inzet van bewegingsmomenten gedurende de schooldag, wat precies aansluit bij de definitie van 'Ruim bewegingsaanbod' als een aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten en materialen gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J251" s="2" t="n">
+      <c r="J251" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K251" s="2" t="inlineStr">
@@ -15065,7 +15067,7 @@
           <t>De uitspraak 'wordt goed nageleefd' duidt op een blijvende uitvoering en naleving van de Gezonde School-aanpak, wat aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J252" s="2" t="n">
+      <c r="J252" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K252" s="2" t="inlineStr">
@@ -15123,7 +15125,7 @@
           <t>De uitdrukking 'ligt in het midden' suggereert een neutrale of gemengde tevredenheid, wat kan duiden op onduidelijkheid over de effectiviteit van de aanpak. Dit sluit het beste aan bij 'Onmeetbare effectiviteit', omdat het idee impliceert dat de resultaten niet duidelijk positief of negatief zijn.</t>
         </is>
       </c>
-      <c r="J253" s="2" t="n">
+      <c r="J253" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K253" s="2" t="inlineStr">
@@ -15181,7 +15183,7 @@
           <t>De uitspraak benadrukt het belang van het leggen van verantwoordelijkheid bij een persoon, wat aansluit bij het concept van duurzame verankering waarbij blijvende uitvoering en brede betrokkenheid centraal staan.</t>
         </is>
       </c>
-      <c r="J254" s="2" t="n">
+      <c r="J254" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K254" s="2" t="inlineStr">
@@ -15239,7 +15241,7 @@
           <t>De opmerking verwijst naar het belang van een vaste programmaopzet die de uitvoering en voortgang van de Gezonde School-aanpak faciliteert, wat aansluit bij de code 'Programmastructuur voor continuïteit' die een vaste programmaopzet met jaarlijkse themawissel beschrijft.</t>
         </is>
       </c>
-      <c r="J255" s="2" t="n">
+      <c r="J255" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K255" s="2" t="inlineStr">
@@ -15297,7 +15299,7 @@
           <t>De uitspraak suggereert dat de Gezonde School-aanpak exclusief en blijvend moet worden uitgevoerd, wat aansluit bij het concept van duurzame verankering waarbij blijvende uitvoering en brede betrokkenheid centraal staan.</t>
         </is>
       </c>
-      <c r="J256" s="2" t="n">
+      <c r="J256" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K256" s="2" t="inlineStr">
@@ -15355,7 +15357,7 @@
           <t>De kern van de uitspraak is dat de Gezonde School-aanpak goed is omdat ouders meegaan in de keuzes die de school maakt. Dit sluit direct aan bij 'Ouderlijke betrokkenheid', dat gaat over het informeren en betrekken van ouders bij gezondheidsthema's ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J257" s="2" t="n">
+      <c r="J257" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K257" s="2" t="inlineStr">
@@ -15413,7 +15415,7 @@
           <t>De uitspraak 'Kinderen drinken veel water' geeft direct een waargenomen toename van gezond gedrag aan, wat precies past bij de code 'Verbeterd gezondheidsgedrag' die gezonde gedragingen zoals vaker water drinken beschrijft.</t>
         </is>
       </c>
-      <c r="J258" s="2" t="n">
+      <c r="J258" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K258" s="2" t="inlineStr">
@@ -15471,7 +15473,7 @@
           <t>De uitspraak beschrijft expliciet dat kinderen fruit eten tijdens de kleine pauze, wat direct aansluit bij de code 'Toegenomen fruitconsumptie' die verwijst naar een toename van fruitconsumptie tijdens schooltijd.</t>
         </is>
       </c>
-      <c r="J259" s="2" t="n">
+      <c r="J259" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K259" s="2" t="inlineStr">
@@ -15529,7 +15531,7 @@
           <t>De uitspraak 'Kinderen nemen een gezonde lunch mee' duidt op het feit dat gezond eten binnen of nabij de school gemakkelijk beschikbaar en toegankelijk is, wat aansluit bij de code 'Toegankelijkheid gezond voedingsaanbod' die gaat over de mate waarin gezond eten gemakkelijk te verkrijgen is.</t>
         </is>
       </c>
-      <c r="J260" s="2" t="n">
+      <c r="J260" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -15587,7 +15589,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak een positief effect heeft op de leerlingen, wat direct aansluit bij de code 'Verbeterd gezondheidsgedrag' die verwijst naar een waargenomen toename van gezonde gedragingen bij leerlingen.</t>
         </is>
       </c>
-      <c r="J261" s="2" t="n">
+      <c r="J261" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K261" s="2" t="inlineStr">
@@ -15645,7 +15647,7 @@
           <t>De idee beschrijft dat de Gezonde School-aanpak leerlingen concrete tips geeft om hun leven gezonder in te richten, wat direct aansluit bij de code 'Handvatten voor gezonde leefstijl' die gaat over concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren.</t>
         </is>
       </c>
-      <c r="J262" s="2" t="n">
+      <c r="J262" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K262" s="2" t="inlineStr">
@@ -15703,7 +15705,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak concrete hulpmiddelen en maatregelen biedt om een gezonder leven te stimuleren, wat precies aansluit bij de code 'Handvatten voor gezonde leefstijl' die gaat over uitvoerbare maatregelen en hulpmiddelen voor bewustwording en gezond gedrag.</t>
         </is>
       </c>
-      <c r="J263" s="2" t="n">
+      <c r="J263" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K263" s="2" t="inlineStr">
@@ -15761,7 +15763,7 @@
           <t>De reactie benadrukt het nut van de thema's van de Gezonde School-aanpak voor leerlingen, wat direct aansluit bij de code 'Brede implementatie van gezondheidsthema's' die gaat over de zichtbare invoering van gezondheidsthema's op school.</t>
         </is>
       </c>
-      <c r="J264" s="2" t="n">
+      <c r="J264" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K264" s="2" t="inlineStr">
@@ -15819,7 +15821,7 @@
           <t>De reactie richt zich expliciet op het verminderen van ongezonde producten in de kantine en automaten, wat precies overeenkomt met de code 'Beperken van ongezonde producten' die acties of beleid beschrijft om het aanbod en de zichtbaarheid van snoep, snacks en frisdrank op school te verminderen.</t>
         </is>
       </c>
-      <c r="J265" s="2" t="n">
+      <c r="J265" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K265" s="2" t="inlineStr">
@@ -15877,7 +15879,7 @@
           <t>De reactie gaat over het verminderen van ongezonde voedingsproducten (frikandelbroodjes) in de schoolomgeving, wat direct aansluit bij het code label 'Beperken van ongezonde producten' dat acties of beleid beschrijft om het aanbod van ongezonde snacks te verminderen.</t>
         </is>
       </c>
-      <c r="J266" s="2" t="n">
+      <c r="J266" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K266" s="2" t="inlineStr">
@@ -15935,7 +15937,7 @@
           <t>De reactie richt zich expliciet op het verminderen van ongezonde koekjes in de kantine en automaten, wat direct aansluit bij het code label 'Beperken van ongezonde producten', dat gaat over acties of beleid om het aanbod van snoep, snacks en frisdrank te verminderen.</t>
         </is>
       </c>
-      <c r="J267" s="2" t="n">
+      <c r="J267" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K267" s="2" t="inlineStr">
@@ -15993,7 +15995,7 @@
           <t>De vermelding van een dagelijks schoolontbijt sluit direct aan bij het concept van 'Structureel voedingsbeleid', dat verwijst naar blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J268" s="2" t="n">
+      <c r="J268" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K268" s="2" t="inlineStr">
@@ -16051,7 +16053,7 @@
           <t>De uitspraak benadrukt het duidelijk communiceren van het traktatiesbeleid naar ouders, wat direct aansluit bij het code label 'Ouderlijke betrokkenheid' dat gaat over het informeren van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J269" s="2" t="n">
+      <c r="J269" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K269" s="2" t="inlineStr">
@@ -16109,7 +16111,7 @@
           <t>De opmerking verwijst naar een probleem met traktaties die niet voldoen aan de regels, wat duidt op een gebrek aan duidelijke beleidsregels of communicatie hierover. Dit sluit goed aan bij de code 'Onvoldoende beleidsduidelijkheid traktaties', die gaat over het ontbreken van duidelijke traktatieregels en de daaruit voortvloeiende problemen.</t>
         </is>
       </c>
-      <c r="J270" s="2" t="n">
+      <c r="J270" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K270" s="2" t="inlineStr">
@@ -16167,7 +16169,7 @@
           <t>De idee beschrijft het stimuleren van gezond gedrag zoals water drinken en fruit eten, wat direct aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals omschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J271" s="2" t="n">
+      <c r="J271" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K271" s="2" t="inlineStr">
@@ -16225,7 +16227,7 @@
           <t>De uitspraak gaat over het verbod op ongezonde traktaties tijdens de lunch, wat direct aansluit bij het beleid om het aanbod en de zichtbaarheid van ongezonde producten op school te verminderen.</t>
         </is>
       </c>
-      <c r="J272" s="2" t="n">
+      <c r="J272" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K272" s="2" t="inlineStr">
@@ -16283,7 +16285,7 @@
           <t>De opmerking richt zich op het verbeteren van de gezondheid van lunches voor alle leerlingen, wat direct aansluit bij het concept van een blijvend beleid gericht op gezond eten op school, zoals beschreven in 'Structureel voedingsbeleid'.</t>
         </is>
       </c>
-      <c r="J273" s="2" t="n">
+      <c r="J273" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K273" s="2" t="inlineStr">
@@ -16341,7 +16343,7 @@
           <t>De uitdrukking 'gaat steeds meer leven op school' duidt op een groeiende en blijvende betrokkenheid en integratie van de Gezonde School-aanpak binnen de school, wat aansluit bij het concept van 'Duurzame verankering' als blijvende uitvoering door brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J274" s="2" t="n">
+      <c r="J274" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K274" s="2" t="inlineStr">
@@ -16399,7 +16401,7 @@
           <t>De idee beschrijft dat gezonde broodjes kosteloos worden aangeboden, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals omschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J275" s="2" t="n">
+      <c r="J275" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K275" s="2" t="inlineStr">
@@ -16457,7 +16459,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak duidelijke informatie biedt, wat direct aansluit bij het code label 'Consistente heldere communicatie', dat gaat over regelmatige, eenduidige en verzorgde informatievoorziening aan betrokkenen.</t>
         </is>
       </c>
-      <c r="J276" s="2" t="n">
+      <c r="J276" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K276" s="2" t="inlineStr">
@@ -16515,7 +16517,7 @@
           <t>De uitspraak 'werkt prettig' duidt op een positieve ervaring met de uitvoering en continuïteit van de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering door blijvende uitvoering en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J277" s="2" t="n">
+      <c r="J277" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K277" s="2" t="inlineStr">
@@ -16573,7 +16575,7 @@
           <t>De suggestie om twee keer per week gym aan te bieden sluit direct aan bij het concept van een ruim bewegingsaanbod, dat staat voor frequente en gevarieerde bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J278" s="2" t="n">
+      <c r="J278" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K278" s="2" t="inlineStr">
@@ -16631,7 +16633,7 @@
           <t>De reactie benadrukt de noodzaak van een voedingsbeleid binnen de Gezonde School-aanpak, wat direct aansluit bij de code 'Structureel voedingsbeleid' die verwijst naar blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J279" s="2" t="n">
+      <c r="J279" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K279" s="2" t="inlineStr">
@@ -16689,7 +16691,7 @@
           <t>De respondent geeft aan zeer tevreden te zijn over de Gezonde School-aanpak, wat duidt op een positieve waardering die kan voortkomen uit een blijvende en goed verankerde uitvoering van de aanpak binnen de school. Dit sluit het beste aan bij 'Duurzame verankering', omdat het gaat om blijvende uitvoering en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J280" s="2" t="n">
+      <c r="J280" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K280" s="2" t="inlineStr">
@@ -16747,7 +16749,7 @@
           <t>De reactie benadrukt het belang van het informeren en betrekken van ouders bij de Gezonde School-aanpak, wat precies aansluit bij de code 'Ouderlijke betrokkenheid' die gaat over het informeren van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J281" s="2" t="n">
+      <c r="J281" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K281" s="2" t="inlineStr">
@@ -16805,7 +16807,7 @@
           <t>De idee benadrukt het belang van het informeren en betrekken van ouders bij de doelstellingen van de Gezonde School-aanpak, wat precies aansluit bij de code 'Ouderlijke betrokkenheid' die gaat over het informeren van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J282" s="2" t="n">
+      <c r="J282" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K282" s="2" t="inlineStr">
@@ -16863,7 +16865,7 @@
           <t>De term 'geborgd' duidt op een blijvende uitvoering en verankering van de Gezonde School-aanpak, wat precies aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J283" s="2" t="n">
+      <c r="J283" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K283" s="2" t="inlineStr">
@@ -16921,7 +16923,7 @@
           <t>Het monitoren van de Gezonde School-aanpak duidt op een blijvende uitvoering en aandacht voor continuïteit, wat aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J284" s="2" t="n">
+      <c r="J284" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K284" s="2" t="inlineStr">
@@ -16979,7 +16981,7 @@
           <t>De uitspraak richt zich op het verminderen van suikerconsumptie bij kinderen, wat direct verband houdt met het beperken van ongezonde producten zoals suikerhoudende snacks en dranken op school. Dit sluit nauw aan bij de code 'Beperken van ongezonde producten' die acties of beleid beschrijft om het aanbod en de zichtbaarheid van ongezonde producten te verminderen.</t>
         </is>
       </c>
-      <c r="J285" s="2" t="n">
+      <c r="J285" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K285" s="2" t="inlineStr">
@@ -17037,7 +17039,7 @@
           <t>De vermelding dat de Gezonde School-aanpak zichtbaar hangt in de school duidt op een zichtbare en brede invoering van initiatieven rond gezondheidsthema's binnen de schoolomgeving, wat aansluit bij de definitie van 'Brede implementatie van gezondheidsthema's'.</t>
         </is>
       </c>
-      <c r="J286" s="2" t="n">
+      <c r="J286" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K286" s="2" t="inlineStr">
@@ -17095,7 +17097,7 @@
           <t>De opmerking geeft aan dat er regelmatig en duidelijk over de Gezonde School-aanpak wordt verteld door een persoon binnen de schoolomgeving, wat aansluit bij het concept van consistente en heldere communicatie over de aanpak.</t>
         </is>
       </c>
-      <c r="J287" s="2" t="n">
+      <c r="J287" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K287" s="2" t="inlineStr">
@@ -17153,7 +17155,7 @@
           <t>De uitspraak 'Er is bewust beleg beschikbaar' verwijst direct naar de beschikbaarheid van gezond voedsel binnen de schoolomgeving, wat precies past bij de code 'Toegankelijkheid gezond voedingsaanbod' die gaat over de mate waarin gezond eten gemakkelijk te verkrijgen is.</t>
         </is>
       </c>
-      <c r="J288" s="2" t="n">
+      <c r="J288" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K288" s="2" t="inlineStr">
@@ -17211,7 +17213,7 @@
           <t>De opmerking verwijst naar het bestaan van gezonde broodjes, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J289" s="2" t="n">
+      <c r="J289" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K289" s="2" t="inlineStr">
@@ -17269,7 +17271,7 @@
           <t>De term 'vitaliteit' verwijst naar een breed gezondheidsthema dat verder gaat dan alleen voeding of beweging. De code 'Aandacht voor brede gezondheidsthema's' omvat integratie van diverse gezondheidsonderwerpen, wat het beste past bij de wens voor aandacht voor vitaliteit binnen de Gezonde School-aanpak.</t>
         </is>
       </c>
-      <c r="J290" s="2" t="n">
+      <c r="J290" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K290" s="2" t="inlineStr">
@@ -17327,7 +17329,7 @@
           <t>De uiting benadrukt het belang van aandacht voor positieve gezondheid, wat aansluit bij de code 'Aandacht voor brede gezondheidsthema's' die integratie van brede gezondheidsonderwerpen in schoolbeleid beschrijft. Dit is een directe conceptuele match.</t>
         </is>
       </c>
-      <c r="J291" s="2" t="n">
+      <c r="J291" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K291" s="2" t="inlineStr">
@@ -17385,7 +17387,7 @@
           <t>De vermelding van een certificaat sluit direct aan bij de code 'Certificaten als vrijwillige erkenning', die certificaten beschrijft als optionele erkenning zonder verplichte opvolging. Dit is een directe en duidelijke match met de gegeven omschrijving.</t>
         </is>
       </c>
-      <c r="J292" s="2" t="n">
+      <c r="J292" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K292" s="2" t="inlineStr">
@@ -17443,7 +17445,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak in de praktijk niet altijd effectief is, wat wijst op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit goed aan bij de code 'Onvoldoende verankering', die verwijst naar lage herkenning, prioriteit, tijd of handhaving van de aanpak.</t>
         </is>
       </c>
-      <c r="J293" s="2" t="n">
+      <c r="J293" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K293" s="2" t="inlineStr">
@@ -17501,7 +17503,7 @@
           <t>De reactie geeft aan dat er nog steeds ongezonde snacks worden verkocht, wat direct aansluit bij het code-label 'Beperken van ongezonde producten', dat gaat over acties of beleid om het aanbod van snoep, snacks en frisdrank te verminderen.</t>
         </is>
       </c>
-      <c r="J294" s="2" t="n">
+      <c r="J294" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K294" s="2" t="inlineStr">
@@ -17559,7 +17561,7 @@
           <t>De aanwezigheid van een supermarkt en tankstation in de buurt van de school duidt op de mate waarin gezond eten gemakkelijk verkrijgbaar is in de omgeving van de school, wat aansluit bij de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J295" s="2" t="n">
+      <c r="J295" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K295" s="2" t="inlineStr">
@@ -17617,7 +17619,7 @@
           <t>De uitspraak 'Ongezonde zaken worden regelmatig gekocht' verwijst direct naar het aanbod en consumptie van ongezonde producten op school. Dit sluit nauw aan bij de code 'Beperken van ongezonde producten', die gaat over acties of beleid om het aanbod en de zichtbaarheid van snoep, snacks en frisdrank te verminderen. De idee geeft een observatie die impliceert dat er onvoldoende beperking is, wat precies binnen het domein van deze code valt.</t>
         </is>
       </c>
-      <c r="J296" s="2" t="n">
+      <c r="J296" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K296" s="2" t="inlineStr">
@@ -17675,7 +17677,7 @@
           <t>De uitdrukking 'mooie kapstok om vanuit te werken' duidt op een raamwerk of structuur die als basis dient voor verdere uitvoering. Dit sluit goed aan bij de code 'Effectief ingebed kader', die verwijst naar een raamwerk dat zichtbare verbeteringen bevordert. Andere codes zijn minder passend omdat ze meer specifieke thema's of middelen betreffen, terwijl hier de algemene bruikbaarheid en structuur van de aanpak wordt benadrukt.</t>
         </is>
       </c>
-      <c r="J297" s="2" t="n">
+      <c r="J297" s="3" t="n">
         <v>0.85</v>
       </c>
       <c r="K297" s="2" t="inlineStr">
@@ -17733,7 +17735,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak geïntegreerd is in het schoolplan, wat duidt op blijvende uitvoering en bestuurlijke steun, precies wat 'Duurzame verankering' beschrijft.</t>
         </is>
       </c>
-      <c r="J298" s="2" t="n">
+      <c r="J298" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K298" s="2" t="inlineStr">
@@ -17791,7 +17793,7 @@
           <t>De uitspraak richt zich op het bevorderen van bewustwording omtrent voeding, wat direct aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J299" s="2" t="n">
+      <c r="J299" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K299" s="2" t="inlineStr">
@@ -17849,7 +17851,7 @@
           <t>De uitspraak benadrukt het belang van duidelijke en eenduidige communicatie van regels, wat aansluit bij de code 'Consistente heldere communicatie' die staat voor regelmatige, eenduidige en verzorgde informatievoorziening aan alle betrokkenen.</t>
         </is>
       </c>
-      <c r="J300" s="2" t="n">
+      <c r="J300" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K300" s="2" t="inlineStr">
@@ -17907,7 +17909,7 @@
           <t>De uitspraak 'Ouders moeten zich aan de regels houden' verwijst naar de betrokkenheid van ouders bij het naleven van afspraken die waarschijnlijk voortkomen uit schoolinterventies. Dit sluit aan bij de code 'Betrokkenheid thuis', die gaat over het toepassen van adviezen uit school door ouders en hun samenwerking met de school.</t>
         </is>
       </c>
-      <c r="J301" s="2" t="n">
+      <c r="J301" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K301" s="2" t="inlineStr">
@@ -17965,7 +17967,7 @@
           <t>De opmerking over 'makkelijke procedures' duidt op een positieve ervaring met de uitvoering en continuïteit van de Gezonde School-aanpak, wat aansluit bij het concept van 'Duurzame verankering' waarbij blijvende uitvoering door bestuurlijke steun en betrokkenheid centraal staat.</t>
         </is>
       </c>
-      <c r="J302" s="2" t="n">
+      <c r="J302" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K302" s="2" t="inlineStr">
@@ -18023,7 +18025,7 @@
           <t>De reactie benadrukt dat de communicatie over de Gezonde School-aanpak verzorgd is, wat direct aansluit bij de code 'Consistente heldere communicatie' die staat voor regelmatige, eenduidige en verzorgde informatievoorziening.</t>
         </is>
       </c>
-      <c r="J303" s="2" t="n">
+      <c r="J303" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K303" s="2" t="inlineStr">
@@ -18081,7 +18083,7 @@
           <t>De reactie geeft aan dat de Gezonde School-aanpak meer of andere thema's moet omvatten, wat aansluit bij het concept van integratie van brede gezondheidsthema's zoals milieu, seksuele relaties en sociaal-emotionele onderwerpen in het schoolbeleid en onderwijs.</t>
         </is>
       </c>
-      <c r="J304" s="2" t="n">
+      <c r="J304" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K304" s="2" t="inlineStr">
@@ -18139,7 +18141,7 @@
           <t>De uitspraak benadrukt het belang van een blijvende focus op voeding binnen de Gezonde School-aanpak, wat direct aansluit bij het concept van 'Structureel voedingsbeleid' dat gaat over blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J305" s="2" t="n">
+      <c r="J305" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K305" s="2" t="inlineStr">
@@ -18197,7 +18199,7 @@
           <t>De reactie geeft aan dat er behoefte is aan het introduceren van nieuwe onderwerpen binnen de Gezonde School-aanpak, wat aansluit bij het concept van brede implementatie van gezondheidsthema's die meerdere leefstijl- en gezondheidsonderwerpen omvat.</t>
         </is>
       </c>
-      <c r="J306" s="2" t="n">
+      <c r="J306" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K306" s="2" t="inlineStr">
@@ -18255,7 +18257,7 @@
           <t>De opmerking suggereert dat de aanpak gestructureerd en gefaseerd moet worden uitgevoerd, wat aansluit bij het concept van een vaste programmaopzet die uitvoering en voortgang faciliteert.</t>
         </is>
       </c>
-      <c r="J307" s="2" t="n">
+      <c r="J307" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K307" s="2" t="inlineStr">
@@ -18313,7 +18315,7 @@
           <t>De uitspraak benadrukt het belang van het blijven stimuleren van beweging binnen de Gezonde School-aanpak, wat direct aansluit bij het concept van een ruim bewegingsaanbod, namelijk frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J308" s="2" t="n">
+      <c r="J308" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K308" s="2" t="inlineStr">
@@ -18371,7 +18373,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak aandacht besteedt aan verschillende terreinen, wat overeenkomt met de definitie van 'Brede implementatie van gezondheidsthema's' die verwijst naar de invoering van concrete initiatieven rond diverse gezondheidsthema's op school.</t>
         </is>
       </c>
-      <c r="J309" s="2" t="n">
+      <c r="J309" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K309" s="2" t="inlineStr">
@@ -18429,7 +18431,7 @@
           <t>De idee beschrijft het betrekken van leerlingen bij overleg over verbetering van de Gezonde School-aanpak, wat precies aansluit bij de definitie van 'Leerlinginspraak' als het betrekken van leerlingen bij besluitvorming en activiteiten om hun welbevinden te verbeteren.</t>
         </is>
       </c>
-      <c r="J310" s="2" t="n">
+      <c r="J310" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K310" s="2" t="inlineStr">
@@ -18487,7 +18489,7 @@
           <t>De uitdrukking 'goed in beeld' duidt op een duidelijke en consistente zichtbaarheid of communicatie van de Gezonde School-aanpak binnen de school, wat aansluit bij de code 'Consistente heldere communicatie' die regelmatige, eenduidige en verzorgde informatievoorziening beschrijft.</t>
         </is>
       </c>
-      <c r="J311" s="2" t="n">
+      <c r="J311" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K311" s="2" t="inlineStr">
@@ -18545,7 +18547,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak organiseert veel' suggereert dat er een breed scala aan activiteiten of initiatieven wordt georganiseerd, wat aansluit bij de code 'Brede implementatie van gezondheidsthema's' die verwijst naar zichtbare en terreinoverstijgende invoering van initiatieven rond leefstijl, voeding, gewicht en rookpreventie.</t>
         </is>
       </c>
-      <c r="J312" s="2" t="n">
+      <c r="J312" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K312" s="2" t="inlineStr">
@@ -18603,7 +18605,7 @@
           <t>De reactie benadrukt het ontvangen van subsidie, wat direct betrekking heeft op beschikbare geldmiddelen en subsidieopties die de uitvoering van de Gezonde School-aanpak mogelijk maken. Dit sluit nauw aan bij de code 'Financieringsmogelijkheden'.</t>
         </is>
       </c>
-      <c r="J313" s="2" t="n">
+      <c r="J313" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K313" s="2" t="inlineStr">
@@ -18661,7 +18663,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak goed wordt uitgevoerd en ingebed op de school, wat aansluit bij het concept van blijvende uitvoering door bestuurlijke steun en brede betrokkenheid, zoals beschreven bij 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J314" s="2" t="n">
+      <c r="J314" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K314" s="2" t="inlineStr">
@@ -18719,7 +18721,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak structureel is ingebed en blijvend wordt uitgevoerd, wat precies aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J315" s="2" t="n">
+      <c r="J315" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K315" s="2" t="inlineStr">
@@ -18777,7 +18779,7 @@
           <t>Het feit dat de school een pilotschool was, duidt op een vroege en mogelijk blijvende betrokkenheid bij de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J316" s="2" t="n">
+      <c r="J316" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K316" s="2" t="inlineStr">
@@ -18835,7 +18837,7 @@
           <t>De uitspraak 'zou meer moeten kunnen' duidt op een gevoel dat de huidige uitvoering of verankering van de Gezonde School-aanpak onvoldoende is, wat aansluit bij de code 'Onvoldoende verankering' die verwijst naar zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J317" s="2" t="n">
+      <c r="J317" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K317" s="2" t="inlineStr">
@@ -18893,7 +18895,7 @@
           <t>De uitspraak geeft aan dat de aanpak verbeterd kan worden, wat wijst op een zwakke of onvoldoende verankering van de Gezonde School-aanpak in de schoolpraktijk. Dit sluit aan bij de code 'Onvoldoende verankering' die verwijst naar een zwakke of ontbrekende verankering van de aanpak.</t>
         </is>
       </c>
-      <c r="J318" s="2" t="n">
+      <c r="J318" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K318" s="2" t="inlineStr">
@@ -18951,7 +18953,7 @@
           <t>De uitspraak geeft aan dat de aanpak meer moet doen om een gezonde school te zijn, wat wijst op een behoefte aan blijvende uitvoering en verankering van de Gezonde School-aanpak binnen de school. Dit sluit het beste aan bij 'Duurzame verankering', dat gaat over blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J319" s="2" t="n">
+      <c r="J319" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K319" s="2" t="inlineStr">
@@ -19009,7 +19011,7 @@
           <t>De opmerking gaat over het meenemen van ongezonde snacks door kinderen, wat direct aansluit bij het thema van het beperken van ongezonde producten op school. Dit codeert het probleem van ongezonde voeding die via ouders wordt meegegeven, wat past binnen acties of beleid om het aanbod van snoep en snacks te verminderen.</t>
         </is>
       </c>
-      <c r="J320" s="2" t="n">
+      <c r="J320" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K320" s="2" t="inlineStr">
@@ -19067,7 +19069,7 @@
           <t>De uitdrukking 'papieren werkelijkheid' suggereert dat de aanpak wel formeel bestaat maar in de praktijk niet goed is ingebed of uitgevoerd. Dit sluit nauw aan bij de code 'Onvoldoende verankering', die verwijst naar een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J321" s="2" t="n">
+      <c r="J321" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K321" s="2" t="inlineStr">
@@ -19125,7 +19127,7 @@
           <t>De opmerking dat de Gezonde School-aanpak een 'deelaanpak' is, suggereert dat de aanpak niet volledig of integraal is verankerd in de schoolpraktijk. Dit sluit aan bij de code 'Onvoldoende verankering', die verwijst naar een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J322" s="2" t="n">
+      <c r="J322" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K322" s="2" t="inlineStr">
@@ -19183,7 +19185,7 @@
           <t>De uitspraak benadrukt de steun van leerlingen voor de Gezonde School-aanpak, wat aansluit bij het concept van 'Leerlinginspraak' waarbij leerlingen betrokken zijn bij activiteiten en besluitvorming die hun welzijn verbeteren. Hoewel het niet expliciet over inspraak gaat, is steun van leerlingen een indicatie van betrokkenheid en participatie.</t>
         </is>
       </c>
-      <c r="J323" s="2" t="n">
+      <c r="J323" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K323" s="2" t="inlineStr">
@@ -19241,7 +19243,7 @@
           <t>De uitspraak benadrukt de steun van ouders voor de Gezonde School-aanpak, wat direct aansluit bij het code label 'Ouderlijke betrokkenheid' dat gaat over het informeren en betrekken van ouders bij gezondheidsthema's ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J324" s="2" t="n">
+      <c r="J324" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K324" s="2" t="inlineStr">
@@ -19299,7 +19301,7 @@
           <t>De vermelding van 'schoolfruit' sluit direct aan bij het concept van een consistente gratis dagelijkse verstrekking van fruit op school, wat precies wordt beschreven in de code 'Structurele gratis fruitvoorziening'.</t>
         </is>
       </c>
-      <c r="J325" s="2" t="n">
+      <c r="J325" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K325" s="2" t="inlineStr">
@@ -19357,7 +19359,7 @@
           <t>De vermelding van een waterdrinkdag binnen de Gezonde School-aanpak duidt op een concreet initiatief dat gericht is op het stimuleren van gezond gedrag, namelijk vaker water drinken door leerlingen. Dit sluit direct aan bij de code 'Verbeterd gezondheidsgedrag', die een waargenomen toename van gezonde gedragingen beschrijft.</t>
         </is>
       </c>
-      <c r="J326" s="2" t="n">
+      <c r="J326" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K326" s="2" t="inlineStr">
@@ -19415,7 +19417,7 @@
           <t>De vermelding van 'gezonde tussendoortjes' sluit direct aan bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, wat precies wordt beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J327" s="2" t="n">
+      <c r="J327" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K327" s="2" t="inlineStr">
@@ -19473,7 +19475,7 @@
           <t>De uitspraak benadrukt het belang van het jaarlijks verkrijgen van het vignet, wat duidt op een wens voor blijvende uitvoering en verankering van de Gezonde School-aanpak binnen de school. Dit sluit aan bij de code 'Duurzame verankering', die gaat over blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J328" s="2" t="n">
+      <c r="J328" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K328" s="2" t="inlineStr">
@@ -19531,7 +19533,7 @@
           <t>De suggestie om kooklessen op te nemen in de Gezonde School-aanpak sluit aan bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, wat precies past bij de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J329" s="2" t="n">
+      <c r="J329" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K329" s="2" t="inlineStr">
@@ -19589,7 +19591,7 @@
           <t>De uitspraak richt zich op het belang van een gezonde kantine binnen de Gezonde School-aanpak, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J330" s="2" t="n">
+      <c r="J330" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K330" s="2" t="inlineStr">
@@ -19647,7 +19649,7 @@
           <t>De uitspraak 'De school moet het goede voorbeeld geven' duidt op het belang van een blijvende en zichtbare inzet van de school voor de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J331" s="2" t="n">
+      <c r="J331" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K331" s="2" t="inlineStr">
@@ -19705,7 +19707,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak een duidelijk overzicht biedt van de activiteiten op het gebied van welbevinden, wat aansluit bij een raamwerk dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert. Dit sluit het beste aan bij 'Effectief ingebed kader'.</t>
         </is>
       </c>
-      <c r="J332" s="2" t="n">
+      <c r="J332" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K332" s="2" t="inlineStr">
@@ -19763,7 +19765,7 @@
           <t>De uitspraak benadrukt het belang van een consistente en blijvende uitvoering van de Gezonde School-aanpak in elke klas, wat aansluit bij het concept van duurzame verankering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J333" s="2" t="n">
+      <c r="J333" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K333" s="2" t="inlineStr">
@@ -19821,7 +19823,7 @@
           <t>De uitspraak benadrukt het belang van blijvende uitvoering en handhaving van de Gezonde School-aanpak in elke klas, wat direct aansluit bij het concept van duurzame verankering zoals omschreven in de code.</t>
         </is>
       </c>
-      <c r="J334" s="2" t="n">
+      <c r="J334" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K334" s="2" t="inlineStr">
@@ -19879,7 +19881,7 @@
           <t>De uitspraak 'Kinderen nemen fruit mee als tussendoortje' geeft direct aan dat er een toename is in het consumeren van fruit tijdens schooltijd, wat precies past bij de code 'Toegenomen fruitconsumptie' die deze toename beschrijft.</t>
         </is>
       </c>
-      <c r="J335" s="2" t="n">
+      <c r="J335" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K335" s="2" t="inlineStr">
@@ -19937,7 +19939,7 @@
           <t>De uitspraak 'Kinderen drinken altijd water op school' geeft direct aan dat er een toename is in gezond gedrag, namelijk het vaker drinken van water. Dit sluit nauw aan bij de code 'Verbeterd gezondheidsgedrag', die verwijst naar waargenomen toename van gezonde gedragingen bij leerlingen.</t>
         </is>
       </c>
-      <c r="J336" s="2" t="n">
+      <c r="J336" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K336" s="2" t="inlineStr">
@@ -19995,7 +19997,7 @@
           <t>De opmerking over het zoveel mogelijk gebruiken van bruinbrood bij de lunch duidt op een blijvend beleid gericht op gezond eten op school, wat precies valt onder 'Structureel voedingsbeleid'.</t>
         </is>
       </c>
-      <c r="J337" s="2" t="n">
+      <c r="J337" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K337" s="2" t="inlineStr">
@@ -20053,7 +20055,7 @@
           <t>De reactie geeft aan dat de overblijfmomenten worden ingevuld met beweegactiviteiten, wat direct aansluit bij het concept van een ruim bewegingsaanbod, namelijk frequente en gevarieerde bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J338" s="2" t="n">
+      <c r="J338" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K338" s="2" t="inlineStr">
@@ -20111,7 +20113,7 @@
           <t>De opmerking verwijst naar het beschikbaar zijn van gezonde traktaties tijdens de overblijf, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J339" s="2" t="n">
+      <c r="J339" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K339" s="2" t="inlineStr">
@@ -20169,7 +20171,7 @@
           <t>De uitspraak 'Gezonde School-aanpak werkt goed' duidt op een positieve waardering van de uitvoering en resultaten van de aanpak, wat aansluit bij het concept van 'Duurzame verankering' waarbij blijvende uitvoering en brede betrokkenheid centraal staan.</t>
         </is>
       </c>
-      <c r="J340" s="2" t="n">
+      <c r="J340" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K340" s="2" t="inlineStr">
@@ -20227,7 +20229,7 @@
           <t>De uitspraak benadrukt het belang dat de Gezonde School-aanpak haar doel bereikt, wat aansluit bij het concept van duurzame verankering waarbij blijvende uitvoering en brede betrokkenheid centraal staan.</t>
         </is>
       </c>
-      <c r="J341" s="2" t="n">
+      <c r="J341" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K341" s="2" t="inlineStr">
@@ -20285,7 +20287,7 @@
           <t>De reactie benadrukt het belang van ouders die de adviezen en lessen van school toepassen, wat direct aansluit bij de code 'Ouderlijke betrokkenheid' die gaat over het informeren en betrekken van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J342" s="2" t="n">
+      <c r="J342" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K342" s="2" t="inlineStr">
@@ -20343,7 +20345,7 @@
           <t>De opmerking 'Het zorgteam is goed bezig' duidt op een positieve waardering van een interne groep die betrokken is bij de uitvoering van de Gezonde School-aanpak. Dit sluit het beste aan bij 'Duurzame verankering', omdat het wijst op blijvende uitvoering en betrokkenheid binnen de school, wat essentieel is voor continuïteit.</t>
         </is>
       </c>
-      <c r="J343" s="2" t="n">
+      <c r="J343" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K343" s="2" t="inlineStr">
@@ -20401,7 +20403,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak bewuster bezig is met gezondheid, wat duidt op een zichtbare en brede invoering van gezondheidsthema's binnen de school. Dit sluit goed aan bij de code 'Brede implementatie van gezondheidsthema's', die gaat over de zichtbare terreinoverstijgende invoering van initiatieven rond leefstijl, voeding, gewicht en rookpreventie.</t>
         </is>
       </c>
-      <c r="J344" s="2" t="n">
+      <c r="J344" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K344" s="2" t="inlineStr">
@@ -20459,7 +20461,7 @@
           <t>De uitspraak richt zich expliciet op het voorkomen dat leerlingen ongezonde producten kunnen kopen, wat direct aansluit bij het code label 'Beperken van ongezonde producten' dat gaat over acties of beleid om het aanbod en de zichtbaarheid van snoep, snacks en frisdrank op school te verminderen.</t>
         </is>
       </c>
-      <c r="J345" s="2" t="n">
+      <c r="J345" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K345" s="2" t="inlineStr">
@@ -20517,7 +20519,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak nauwelijks wordt uitgevoerd, wat duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit direct aan bij de code 'Onvoldoende verankering', die verwijst naar een lage herkenning, prioriteit, tijd of handhaving van de aanpak.</t>
         </is>
       </c>
-      <c r="J346" s="2" t="n">
+      <c r="J346" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K346" s="2" t="inlineStr">
@@ -20575,7 +20577,7 @@
           <t>De opmerking gaat over het ongezonde aanbod in de kantine, wat direct aansluit bij het code-label 'Beperken van ongezonde producten', dat betrekking heeft op acties of beleid om het aanbod van ongezonde snacks en frisdrank te verminderen.</t>
         </is>
       </c>
-      <c r="J347" s="2" t="n">
+      <c r="J347" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K347" s="2" t="inlineStr">
@@ -20633,7 +20635,7 @@
           <t>De opmerking 'Er wordt gerookt op het terrein van de school' duidt op het probleem dat er onvoldoende toezicht of interventie is om roken op het schoolterrein te voorkomen. Dit sluit direct aan bij de code 'Onvoldoende nalevingstoezicht', die expliciet verwijst naar het gebrek aan toezicht waardoor roken blijft voorkomen.</t>
         </is>
       </c>
-      <c r="J348" s="2" t="n">
+      <c r="J348" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K348" s="2" t="inlineStr">
@@ -20691,7 +20693,7 @@
           <t>De opmerking gaat over het voorkomen van vapen op het schoolterrein, wat duidt op een probleem met het toezicht en de handhaving van regels rondom roken en vapen. Dit sluit direct aan bij de code 'Onvoldoende nalevingstoezicht', die verwijst naar onvoldoende toezicht of interventie waardoor roken of vapen op schoolterrein blijft voorkomen.</t>
         </is>
       </c>
-      <c r="J349" s="2" t="n">
+      <c r="J349" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K349" s="2" t="inlineStr">
@@ -20749,7 +20751,7 @@
           <t>De reactie geeft aan dat er geen interventie plaatsvindt bij roken en vapen op het schoolterrein, wat direct aansluit bij het concept van onvoldoende toezicht of interventie zoals beschreven in de code 'Onvoldoende nalevingstoezicht'.</t>
         </is>
       </c>
-      <c r="J350" s="2" t="n">
+      <c r="J350" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K350" s="2" t="inlineStr">
@@ -20807,7 +20809,7 @@
           <t>De uitspraak richt zich op het moeilijker maken van de keuze voor ongezonde voeding, wat direct aansluit bij het beleid of acties om het aanbod en de zichtbaarheid van ongezonde producten te verminderen, zoals beschreven in de code 'Beperken van ongezonde producten'.</t>
         </is>
       </c>
-      <c r="J351" s="2" t="n">
+      <c r="J351" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K351" s="2" t="inlineStr">
@@ -20865,7 +20867,7 @@
           <t>De opmerking gaat over het verbeteren van de aanpak rondom voedselkeuzes, specifiek vlees, wat past binnen het bredere kader van structureel voedingsbeleid dat gericht is op blijvende voorzieningen en beleid voor gezond eten op school.</t>
         </is>
       </c>
-      <c r="J352" s="2" t="n">
+      <c r="J352" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K352" s="2" t="inlineStr">
@@ -20923,7 +20925,7 @@
           <t>De vermelding van een coördinator die veel betekent voor de school duidt op een blijvende en structurele betrokkenheid binnen de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J353" s="2" t="n">
+      <c r="J353" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K353" s="2" t="inlineStr">
@@ -20981,7 +20983,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak niet herkend wordt op de school, wat duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit direct aan bij de code 'Onvoldoende verankering', die gaat over lage herkenning en prioriteit van de aanpak.</t>
         </is>
       </c>
-      <c r="J354" s="2" t="n">
+      <c r="J354" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K354" s="2" t="inlineStr">
@@ -21039,7 +21041,7 @@
           <t>De uitdrukking 'een vinkje dat je haalt' suggereert dat de Gezonde School-aanpak wordt gezien als een formele erkenning of certificaat dat je kunt behalen zonder dat het noodzakelijkerwijs diepgaande impact heeft. Dit sluit goed aan bij de code 'Certificaten als vrijwillige erkenning', die beschrijft dat certificaten optioneel zijn en zonder verplichte opvolging worden toegekend.</t>
         </is>
       </c>
-      <c r="J355" s="2" t="n">
+      <c r="J355" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K355" s="2" t="inlineStr">
@@ -21097,7 +21099,7 @@
           <t>De uitspraak geeft aan dat de ondersteuning vanuit de Gezonde School afneemt, wat duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit aan bij de code 'Onvoldoende verankering', die verwijst naar een lage herkenning, prioriteit of tijd voor de aanpak.</t>
         </is>
       </c>
-      <c r="J356" s="2" t="n">
+      <c r="J356" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K356" s="2" t="inlineStr">
@@ -21155,7 +21157,7 @@
           <t>De uitspraak geeft aan dat de resultaten niet aantoonbaar of zichtbaar zijn met bestaande meetinstrumenten, wat precies overeenkomt met de code 'Onmeetbare effectiviteit' die bezorgdheid over niet meetbare resultaten beschrijft.</t>
         </is>
       </c>
-      <c r="J357" s="2" t="n">
+      <c r="J357" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K357" s="2" t="inlineStr">
@@ -21213,7 +21215,7 @@
           <t>De term 'denkwijze' duidt op een blijvende, ingebedde manier van denken over de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering, namelijk de blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J358" s="2" t="n">
+      <c r="J358" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K358" s="2" t="inlineStr">
@@ -21271,7 +21273,7 @@
           <t>De opmerking dat er geen predicaat meer is voor de Gezonde School-aanpak verwijst naar het ontbreken van een vorm van erkenning of certificaat. Dit sluit het beste aan bij de code 'Certificaten als vrijwillige erkenning', die gaat over certificaten als optionele erkenning zonder verplichte opvolging.</t>
         </is>
       </c>
-      <c r="J359" s="2" t="n">
+      <c r="J359" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K359" s="2" t="inlineStr">
@@ -21329,7 +21331,7 @@
           <t>De uitdrukking 'staat nog in de kinderschoenen' duidt op een beginnend, nog niet volledig ontwikkelde of verankerde aanpak. Dit sluit goed aan bij de code 'Onvoldoende verankering', die verwijst naar een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J360" s="2" t="n">
+      <c r="J360" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K360" s="2" t="inlineStr">
@@ -21387,7 +21389,7 @@
           <t>De idee beschrijft expliciet het dagelijks aanbieden van gratis fruit op school, wat precies overeenkomt met de code 'Structurele gratis fruitvoorziening' die verwijst naar consistente gratis dagelijkse verstrekking van fruit aan leerlingen.</t>
         </is>
       </c>
-      <c r="J361" s="2" t="n">
+      <c r="J361" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K361" s="2" t="inlineStr">
@@ -21445,7 +21447,7 @@
           <t>De reactie benadrukt het frequente en gestructureerde aanbod van gymles door een vakleerkracht, wat direct aansluit bij het concept van een ruim bewegingsaanbod met frequente en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J362" s="2" t="n">
+      <c r="J362" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K362" s="2" t="inlineStr">
@@ -21503,7 +21505,7 @@
           <t>De uitspraak benadrukt het stimuleren van gezondheid bij leerlingen, wat direct aansluit bij het bieden van concrete maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J363" s="2" t="n">
+      <c r="J363" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K363" s="2" t="inlineStr">
@@ -21561,7 +21563,7 @@
           <t>De uitspraak 'Een deel van de leerlingen heeft een goed voorbeeld nodig' impliceert dat er behoefte is aan concrete uitvoerbare maatregelen of hulpmiddelen die leerlingen kunnen stimuleren tot gezond gedrag, wat aansluit bij de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J364" s="2" t="n">
+      <c r="J364" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K364" s="2" t="inlineStr">
@@ -21619,7 +21621,7 @@
           <t>De uitspraak richt zich op het stimuleren van kinderen om gezonder te eten, wat direct aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J365" s="2" t="n">
+      <c r="J365" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K365" s="2" t="inlineStr">
@@ -21677,7 +21679,7 @@
           <t>De uitspraak 'Er moet tijd aangeboden worden om te bewegen' sluit direct aan bij het codebegrip 'Ruim bewegingsaanbod', dat gaat over het aanbieden van frequente en toegankelijke bewegingsmomenten gedurende de schooldag. De respondent benadrukt de noodzaak van tijd voor bewegen, wat precies past binnen de definitie van deze code.</t>
         </is>
       </c>
-      <c r="J366" s="2" t="n">
+      <c r="J366" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K366" s="2" t="inlineStr">
@@ -21735,7 +21737,7 @@
           <t>De idee beschrijft expliciet het organiseren van bijeenkomsten over seksualiteit voor leerlingen, wat direct overeenkomt met de code 'Seksualiteitsvoorlichting' die gaat over regelmatige lessen of activiteiten over seksualiteit om kennis en bewustzijn te vergroten.</t>
         </is>
       </c>
-      <c r="J367" s="2" t="n">
+      <c r="J367" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K367" s="2" t="inlineStr">
@@ -21793,7 +21795,7 @@
           <t>De idee beschrijft het organiseren van bijeenkomsten over middelengebruik, wat valt onder de zichtbare invoering van gezondheidsthema's op school. Dit sluit goed aan bij de code 'Brede implementatie van gezondheidsthema's' die gaat over concrete initiatieven rond leefstijl en gezondheid.</t>
         </is>
       </c>
-      <c r="J368" s="2" t="n">
+      <c r="J368" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K368" s="2" t="inlineStr">
@@ -21851,7 +21853,7 @@
           <t>De bijeenkomst over 'online onderweg zijn' valt onder een breed gezondheidsthema dat niet alleen fysieke gezondheid betreft, maar ook sociale en emotionele aspecten. Dit sluit aan bij de code 'Aandacht voor brede gezondheidsthema's' die integratie van diverse gezondheidsonderwerpen in het schoolbeleid beschrijft.</t>
         </is>
       </c>
-      <c r="J369" s="2" t="n">
+      <c r="J369" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K369" s="2" t="inlineStr">
@@ -21909,7 +21911,7 @@
           <t>De idee benadrukt het betrekken van leerlingen en docenten bij de Gezonde School-aanpak, wat direct aansluit bij het concept van 'Leerlinginspraak', waarbij leerlingen betrokken worden bij besluitvorming en activiteiten.</t>
         </is>
       </c>
-      <c r="J370" s="2" t="n">
+      <c r="J370" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K370" s="2" t="inlineStr">
@@ -21967,7 +21969,7 @@
           <t>De uitspraak benadrukt het belang dat leerlingen zelf leren omgaan met complexe maatschappelijke situaties, wat aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'. Andere codes richten zich meer op specifieke thema's of organisatorische aspecten, terwijl deze code het beste past bij het algemene idee van zelfredzaamheid en vaardigheden ontwikkelen.</t>
         </is>
       </c>
-      <c r="J371" s="2" t="n">
+      <c r="J371" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K371" s="2" t="inlineStr">
@@ -22025,7 +22027,7 @@
           <t>De uitspraak benadrukt het belang van goede voorbereiding voor leerlingen, wat aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J372" s="2" t="n">
+      <c r="J372" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K372" s="2" t="inlineStr">
@@ -22083,7 +22085,7 @@
           <t>De opmerking over een 'fijne werksfeer' duidt op een positieve verandering in de schoolcultuur of het welzijn, wat aansluit bij het code label 'Effectief ingebed kader' dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert.</t>
         </is>
       </c>
-      <c r="J373" s="2" t="n">
+      <c r="J373" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K373" s="2" t="inlineStr">
@@ -22141,7 +22143,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak aandacht besteedt aan gezonde traktaties, wat past binnen het bredere kader van structureel voedingsbeleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J374" s="2" t="n">
+      <c r="J374" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K374" s="2" t="inlineStr">
@@ -22199,7 +22201,7 @@
           <t>De idee benadrukt het betrekken van leerlingen bij besluitvorming om hun welbevinden te verbeteren, wat precies overeenkomt met de definitie van 'Leerlinginspraak'.</t>
         </is>
       </c>
-      <c r="J375" s="2" t="n">
+      <c r="J375" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K375" s="2" t="inlineStr">
@@ -22257,7 +22259,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak goed is voor het opstarten van activiteiten, wat aansluit bij het concept van een vaste programmaopzet die uitvoering en voortgang faciliteert, zoals beschreven bij 'Programmastructuur voor continuïteit'.</t>
         </is>
       </c>
-      <c r="J376" s="2" t="n">
+      <c r="J376" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K376" s="2" t="inlineStr">
@@ -22315,7 +22317,7 @@
           <t>De term 'structurele aanpak' duidt op een blijvende uitvoering en verankering van de Gezonde School-aanpak, wat precies aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J377" s="2" t="n">
+      <c r="J377" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K377" s="2" t="inlineStr">
@@ -22373,7 +22375,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak minder ondersteuning nodig heeft als deze geïntegreerd is in de cultuur en het aanbod van de school, wat precies aansluit bij het concept van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J378" s="2" t="n">
+      <c r="J378" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K378" s="2" t="inlineStr">
@@ -22431,7 +22433,7 @@
           <t>De uitspraak benadrukt het belang van voortdurende aandacht en steun van het bestuur, wat direct aansluit bij het concept van duurzame verankering waarbij blijvende uitvoering door bestuurlijke steun centraal staat.</t>
         </is>
       </c>
-      <c r="J379" s="2" t="n">
+      <c r="J379" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K379" s="2" t="inlineStr">
@@ -22489,7 +22491,7 @@
           <t>De opmerking gaat over de noodzaak dat de catering, die verantwoordelijk is voor het voedselaanbod, regelmatig aandacht besteedt aan de Gezonde School-aanpak. Dit sluit aan bij het code-label 'Structureel voedingsbeleid', dat betrekking heeft op blijvende voorzieningen of beleid gericht op gezond eten op school, waaronder catering.</t>
         </is>
       </c>
-      <c r="J380" s="2" t="n">
+      <c r="J380" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K380" s="2" t="inlineStr">
@@ -22547,7 +22549,7 @@
           <t>De uiting benadrukt de waardering voor fruit op het werk, wat direct aansluit bij de mate waarin gezond eten gemakkelijk te verkrijgen is binnen of nabij de schoolomgeving.</t>
         </is>
       </c>
-      <c r="J381" s="2" t="n">
+      <c r="J381" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K381" s="2" t="inlineStr">
@@ -22605,7 +22607,7 @@
           <t>De reactie geeft aan dat de Gezonde School-aanpak invloed heeft gehad op het koopgedrag van leerlingen in de kantine, wat inhoudt dat er waarschijnlijk maatregelen zijn genomen om het aanbod van ongezonde producten te beperken. Dit sluit goed aan bij de code 'Beperken van ongezonde producten', die acties of beleid beschrijft om het aanbod en de zichtbaarheid van snoep, snacks en frisdrank op school te verminderen.</t>
         </is>
       </c>
-      <c r="J382" s="2" t="n">
+      <c r="J382" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K382" s="2" t="inlineStr">
@@ -22663,7 +22665,7 @@
           <t>De opmerking dat leerlingen de snoepautomaat niet meer missen, duidt op een vermindering van de beschikbaarheid of aantrekkelijkheid van ongezonde producten zoals snoep. Dit sluit direct aan bij het code-label 'Beperken van ongezonde producten', dat gaat over acties of beleid om het aanbod en de zichtbaarheid van snoep, snacks en frisdrank op school te verminderen.</t>
         </is>
       </c>
-      <c r="J383" s="2" t="n">
+      <c r="J383" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K383" s="2" t="inlineStr">
@@ -22721,7 +22723,7 @@
           <t>De uitspraak benadrukt het belang van de rol van ouders in het meegeven van juiste waarden of informatie, wat aansluit bij het code label 'Ouderlijke betrokkenheid' dat gaat over het informeren van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J384" s="2" t="n">
+      <c r="J384" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K384" s="2" t="inlineStr">
@@ -22779,7 +22781,7 @@
           <t>De uitspraak 'Het is lastig om met de verkeerde dingen om te gaan' suggereert een probleem met het omgaan met ongewenste of ongezonde aspecten binnen de Gezonde School-aanpak. Dit kan duiden op onduidelijkheid of problemen in het beleid of de communicatie hierover, wat aansluit bij 'Onvoldoende beleidsduidelijkheid traktaties' als een bredere interpretatie van onduidelijkheid in regels of handhaving.</t>
         </is>
       </c>
-      <c r="J385" s="2" t="n">
+      <c r="J385" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="K385" s="2" t="inlineStr">
@@ -22837,7 +22839,7 @@
           <t>De uitspraak suggereert dat de aanpak vooral een 'praatje' is, wat duidt op een gebrek aan daadwerkelijke uitvoering en verankering in de schoolpraktijk. Dit sluit goed aan bij de code 'Onvoldoende verankering', die verwijst naar een zwakke of ontbrekende verankering van de aanpak.</t>
         </is>
       </c>
-      <c r="J386" s="2" t="n">
+      <c r="J386" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K386" s="2" t="inlineStr">
@@ -22895,7 +22897,7 @@
           <t>De uitdrukking 'leeft niet echt' duidt op een zwakke of ontbrekende verankering van de Gezonde School-aanpak in de schoolpraktijk, wat precies aansluit bij de code 'Onvoldoende verankering' die spreekt over lage herkenning, prioriteit, tijd of handhaving.</t>
         </is>
       </c>
-      <c r="J387" s="2" t="n">
+      <c r="J387" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K387" s="2" t="inlineStr">
@@ -22953,7 +22955,7 @@
           <t>De opmerking 'Docenten moeten enthousiaster zijn' duidt op een gebrek aan betrokkenheid of prioriteit van docenten bij de Gezonde School-aanpak, wat past bij 'Onvoldoende verankering' die wijst op zwakke of ontbrekende verankering in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J388" s="2" t="n">
+      <c r="J388" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K388" s="2" t="inlineStr">
@@ -23011,7 +23013,7 @@
           <t>De reactie geeft aan dat het effect van de Gezonde School-aanpak niet aantoonbaar of zichtbaar is met bestaande meetinstrumenten, wat precies overeenkomt met de code 'Onmeetbare effectiviteit'.</t>
         </is>
       </c>
-      <c r="J389" s="2" t="n">
+      <c r="J389" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K389" s="2" t="inlineStr">
@@ -23069,7 +23071,7 @@
           <t>De respondent geeft aan dat het effect van de Gezonde School-aanpak niet aantoonbaar of zichtbaar is met de bestaande meetinstrumenten (de vragenlijst van de GGD). Dit sluit direct aan bij de code 'Onmeetbare effectiviteit', die bezorgdheid uitdrukt over het niet meetbaar zijn van resultaten.</t>
         </is>
       </c>
-      <c r="J390" s="2" t="n">
+      <c r="J390" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K390" s="2" t="inlineStr">
@@ -23127,7 +23129,7 @@
           <t>De term 'predikaat' duidt op een vorm van erkenning of certificaat dat aan de Gezonde School-aanpak is toegekend, wat direct aansluit bij de code 'Certificaten als vrijwillige erkenning' die optionele erkenning zonder verplichte opvolging beschrijft.</t>
         </is>
       </c>
-      <c r="J391" s="2" t="n">
+      <c r="J391" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K391" s="2" t="inlineStr">
@@ -23185,7 +23187,7 @@
           <t>De vermelding dat de Gezonde School-aanpak meerdere keren het predikaat heeft gekregen, sluit direct aan bij het concept van certificaten als optionele erkenning zonder verplichte opvolging, wat precies wordt beschreven in de code 'Certificaten als vrijwillige erkenning'.</t>
         </is>
       </c>
-      <c r="J392" s="2" t="n">
+      <c r="J392" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K392" s="2" t="inlineStr">
@@ -23243,7 +23245,7 @@
           <t>De reactie benoemt positieve initiatieven binnen de Gezonde School-aanpak, wat het beste aansluit bij de code 'Brede implementatie van gezondheidsthema's' die verwijst naar zichtbare en concrete initiatieven rond gezondheidsthema's op school.</t>
         </is>
       </c>
-      <c r="J393" s="2" t="n">
+      <c r="J393" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K393" s="2" t="inlineStr">
@@ -23301,7 +23303,7 @@
           <t>De opmerking 'De kantine is nog een aandachtspunt' duidt op aandacht voor het aanbod in de kantine, wat direct verband houdt met de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is. Dit sluit goed aan bij de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J394" s="2" t="n">
+      <c r="J394" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K394" s="2" t="inlineStr">
@@ -23359,7 +23361,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak momenteel niet hoog op de agenda staat, wat duidt op een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk. Dit sluit direct aan bij de code 'Onvoldoende verankering', die verwijst naar lage prioriteit en tijdsbesteding aan de aanpak.</t>
         </is>
       </c>
-      <c r="J395" s="2" t="n">
+      <c r="J395" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K395" s="2" t="inlineStr">
@@ -23417,7 +23419,7 @@
           <t>De suggestie om de schoolkantine in eigen beheer te starten heeft betrekking op het structureel organiseren en beheren van het voedingsaanbod op school, wat aansluit bij het code label 'Structureel voedingsbeleid' dat gaat over blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J396" s="2" t="n">
+      <c r="J396" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K396" s="2" t="inlineStr">
@@ -23475,7 +23477,7 @@
           <t>De opmerking over de gezonde schoolkantine die een nieuwe impuls moet krijgen, verwijst naar het verbeteren of vernieuwen van het aanbod van gezond eten binnen de schoolomgeving. Dit sluit het beste aan bij de code 'Toegankelijkheid gezond voedingsaanbod', die gaat over de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is.</t>
         </is>
       </c>
-      <c r="J397" s="2" t="n">
+      <c r="J397" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K397" s="2" t="inlineStr">
@@ -23533,7 +23535,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak goed beleid is over de omgang met elkaar, wat aansluit bij een raamwerk dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert, zoals beschreven bij 'Effectief ingebed kader'.</t>
         </is>
       </c>
-      <c r="J398" s="2" t="n">
+      <c r="J398" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K398" s="2" t="inlineStr">
@@ -23591,7 +23593,7 @@
           <t>De uitspraak benadrukt dat er op school veel beweging plaatsvindt, wat direct aansluit bij het concept van een ruim bewegingsaanbod, namelijk frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J399" s="2" t="n">
+      <c r="J399" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K399" s="2" t="inlineStr">
@@ -23649,7 +23651,7 @@
           <t>De opmerking gaat over het aanbod van ongezonde producten in de schoolkantine, wat direct aansluit bij het code label 'Beperken van ongezonde producten' dat acties of beleid beschrijft om het aanbod van snoep, snacks en frisdrank te verminderen.</t>
         </is>
       </c>
-      <c r="J400" s="2" t="n">
+      <c r="J400" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K400" s="2" t="inlineStr">
@@ -23707,7 +23709,7 @@
           <t>De reactie uit ontevredenheid over het aanbod van ongezonde producten in de schoolkantine, wat direct aansluit bij het code-label 'Beperken van ongezonde producten' dat gaat over acties of beleid om het aanbod van snoep, snacks en frisdrank te verminderen.</t>
         </is>
       </c>
-      <c r="J401" s="2" t="n">
+      <c r="J401" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K401" s="2" t="inlineStr">
@@ -23765,7 +23767,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak bijdraagt aan gezonder eten van kinderen, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J402" s="2" t="n">
+      <c r="J402" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K402" s="2" t="inlineStr">
@@ -23823,7 +23825,7 @@
           <t>De reactie geeft aan dat de Gezonde School-aanpak leidt tot gezonder drinkgedrag bij kinderen, wat direct aansluit bij de code 'Verbeterd gezondheidsgedrag' die een waargenomen toename van gezonde gedragingen beschrijft.</t>
         </is>
       </c>
-      <c r="J403" s="2" t="n">
+      <c r="J403" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K403" s="2" t="inlineStr">
@@ -23881,7 +23883,7 @@
           <t>De opmerking 'Schoolfruit is fijn' verwijst direct naar het aanbieden van fruit op school, wat het beste past bij de code 'Structurele gratis fruitvoorziening', die staat voor consistente gratis dagelijkse verstrekking van fruit op school.</t>
         </is>
       </c>
-      <c r="J404" s="2" t="n">
+      <c r="J404" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K404" s="2" t="inlineStr">
@@ -23939,7 +23941,7 @@
           <t>De reactie geeft aan dat de Gezonde School-aanpak concrete uitvoerbare maatregelen en hulpmiddelen heeft geleverd om een gezonde leefstijl te promoten, wat precies aansluit bij de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J405" s="2" t="n">
+      <c r="J405" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K405" s="2" t="inlineStr">
@@ -23997,7 +23999,7 @@
           <t>De reactie geeft aan dat er vooruitgang is in het aanbod gericht op bewegen, wat direct aansluit bij de definitie van 'Ruim bewegingsaanbod' als een gevarieerd en toegankelijk aanbod van bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J406" s="2" t="n">
+      <c r="J406" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K406" s="2" t="inlineStr">
@@ -24055,7 +24057,7 @@
           <t>De reactie verwijst naar vooruitgang in het bereiden van eigen voedsel, wat past bij het concept van structureel voedingsbeleid dat gericht is op blijvende voorzieningen of beleid voor gezond eten op school.</t>
         </is>
       </c>
-      <c r="J407" s="2" t="n">
+      <c r="J407" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K407" s="2" t="inlineStr">
@@ -24113,7 +24115,7 @@
           <t>Het idee beschrijft het inrichten van een ontbijtbar, wat een blijvende voorziening is gericht op gezond eten op school. Dit sluit direct aan bij de code 'Structureel voedingsbeleid', die gaat over blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J408" s="2" t="n">
+      <c r="J408" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K408" s="2" t="inlineStr">
@@ -24171,7 +24173,7 @@
           <t>De vermelding van watertappunten sluit direct aan bij het code label 'Structureel voedingsbeleid', dat voorzieningen zoals watertappunten omvat als onderdeel van blijvend beleid gericht op gezond eten en drinken op school.</t>
         </is>
       </c>
-      <c r="J409" s="2" t="n">
+      <c r="J409" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K409" s="2" t="inlineStr">
@@ -24229,7 +24231,7 @@
           <t>De idee beschrijft expliciet het aanbieden van fruit en groente gedurende de schooldag, wat direct aansluit bij de code 'Structurele gratis fruitvoorziening' die staat voor consistente gratis dagelijkse verstrekking van fruit op school.</t>
         </is>
       </c>
-      <c r="J410" s="2" t="n">
+      <c r="J410" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K410" s="2" t="inlineStr">
@@ -24287,7 +24289,7 @@
           <t>De aanwezigheid van een snoepautomaat binnen de Gezonde School-aanpak duidt op het niet verminderen van het aanbod van ongezonde producten, wat direct aansluit bij de code 'Beperken van ongezonde producten' die gaat over acties of beleid om het aanbod van snoep, snacks en frisdrank te verminderen.</t>
         </is>
       </c>
-      <c r="J411" s="2" t="n">
+      <c r="J411" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K411" s="2" t="inlineStr">
@@ -24345,7 +24347,7 @@
           <t>De aanwezigheid van een frisdrankautomaat binnen de Gezonde School-aanpak raakt aan het thema van het aanbod van ongezonde producten. Hoewel de tekst niet expliciet zegt dat het aanbod beperkt wordt, impliceert het noemen van de frisdrankautomaat een relevantie voor het beleid omtrent ongezonde producten op school.</t>
         </is>
       </c>
-      <c r="J412" s="2" t="n">
+      <c r="J412" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K412" s="2" t="inlineStr">
@@ -24403,7 +24405,7 @@
           <t>De opmerking gaat over de prijs van gezondere dranken ten opzichte van ongezonde dranken, wat direct verband houdt met de mate waarin gezond eten en drinken gemakkelijk verkrijgbaar en toegankelijk is op school. Dit sluit aan bij de code 'Toegankelijkheid gezond voedingsaanbod' die de beschikbaarheid en bereikbaarheid van gezond voedsel binnen of nabij de school beschrijft.</t>
         </is>
       </c>
-      <c r="J413" s="2" t="n">
+      <c r="J413" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K413" s="2" t="inlineStr">
@@ -24461,7 +24463,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak daadwerkelijk effect heeft op school, wat aansluit bij het concept van een 'Effectief ingebed kader' dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert. Dit is de beste match binnen de beschikbare codes.</t>
         </is>
       </c>
-      <c r="J414" s="2" t="n">
+      <c r="J414" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K414" s="2" t="inlineStr">
@@ -24519,7 +24521,7 @@
           <t>De opmerking dat er meer aandacht mag zijn binnen de onderwijsteams wijst op een behoefte aan blijvende uitvoering en brede betrokkenheid, wat aansluit bij de definitie van 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J415" s="2" t="n">
+      <c r="J415" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K415" s="2" t="inlineStr">
@@ -24577,7 +24579,7 @@
           <t>De idee benadrukt het belang van bewustwording over seksualiteit binnen de school, wat direct aansluit bij de code 'Seksualiteitsvoorlichting' die gaat over regelmatige lessen of activiteiten over seksualiteit die kennis en bewustzijn van leerlingen vergroten.</t>
         </is>
       </c>
-      <c r="J416" s="2" t="n">
+      <c r="J416" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K416" s="2" t="inlineStr">
@@ -24635,7 +24637,7 @@
           <t>De reactie benadrukt het belang van subsidie (financiering) die moet bijdragen aan bewustwording over seksualiteit. De code 'Seksualiteitsvoorlichting' sluit het beste aan omdat het gaat over lessen of activiteiten die kennis en bewustzijn over seksualiteit vergroten, wat overeenkomt met het doel van de subsidie-relaties in de reactie.</t>
         </is>
       </c>
-      <c r="J417" s="2" t="n">
+      <c r="J417" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K417" s="2" t="inlineStr">
@@ -24693,7 +24695,7 @@
           <t>De uitspraak 'maakt je bewust' sluit goed aan bij het concept van 'Handvatten voor gezonde leefstijl', omdat het gaat om concrete maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren. De andere codes richten zich meer op specifieke beleidsaspecten of organisatorische elementen, terwijl deze code het beste de kern van bewustwording vangt.</t>
         </is>
       </c>
-      <c r="J418" s="2" t="n">
+      <c r="J418" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K418" s="2" t="inlineStr">
@@ -24751,7 +24753,7 @@
           <t>De reactie geeft aan dat de Gezonde School-aanpak weinig effect heeft op het eetgedrag thuis, wat direct aansluit bij het thema 'Betrokkenheid thuis', dat gaat over de mate waarin adviezen uit school ook thuis worden toegepast door ouders.</t>
         </is>
       </c>
-      <c r="J419" s="2" t="n">
+      <c r="J419" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K419" s="2" t="inlineStr">
@@ -24809,7 +24811,7 @@
           <t>De reactie geeft aan dat de Gezonde School-aanpak weinig effect heeft op bewegen thuis, wat direct aansluit bij het thema 'Betrokkenheid thuis', dat gaat over de toepassing van adviezen uit school in de thuissituatie.</t>
         </is>
       </c>
-      <c r="J420" s="2" t="n">
+      <c r="J420" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K420" s="2" t="inlineStr">
@@ -24867,7 +24869,7 @@
           <t>De reactie geeft aan dat er meer aandacht moet zijn voor gezond eten binnen de Gezonde School-aanpak, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J421" s="2" t="n">
+      <c r="J421" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K421" s="2" t="inlineStr">
@@ -24925,7 +24927,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak moet geen snoep toestaan' sluit direct aan bij het code label 'Beperken van ongezonde producten', dat gaat over acties of beleid om het aanbod en de zichtbaarheid van snoep, snacks en frisdrank op school te verminderen. Dit is een duidelijke en directe match met de inhoud van de reactie.</t>
         </is>
       </c>
-      <c r="J422" s="2" t="n">
+      <c r="J422" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K422" s="2" t="inlineStr">
@@ -24983,7 +24985,7 @@
           <t>De uitspraak benadrukt het belang van stimuleren tot bewegen, wat direct aansluit bij het code label 'Ruim bewegingsaanbod', dat gaat over het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J423" s="2" t="n">
+      <c r="J423" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K423" s="2" t="inlineStr">
@@ -25041,7 +25043,7 @@
           <t>De opmerking geeft aan dat er een gebrek is aan aandacht en prioriteit vanuit het bestuur en de directie, wat duidt op een zwakke of ontbrekende verankering van de Gezonde School-aanpak in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J424" s="2" t="n">
+      <c r="J424" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K424" s="2" t="inlineStr">
@@ -25099,7 +25101,7 @@
           <t>De uitspraak 'Gezonde producten moeten beschikbaar zijn' sluit direct aan bij de code 'Toegankelijkheid gezond voedingsaanbod', die gaat over de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is. De focus ligt hier op de beschikbaarheid en toegankelijkheid van gezonde voedingsopties, wat precies wordt uitgedrukt in de idee-tekst.</t>
         </is>
       </c>
-      <c r="J425" s="2" t="n">
+      <c r="J425" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K425" s="2" t="inlineStr">
@@ -25157,7 +25159,7 @@
           <t>De uitspraak 'Leerlingen moeten minder snacken' sluit direct aan bij het verminderen van het aanbod en de zichtbaarheid van ongezonde producten zoals snacks op school, wat precies wordt beschreven in de code 'Beperken van ongezonde producten'.</t>
         </is>
       </c>
-      <c r="J426" s="2" t="n">
+      <c r="J426" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K426" s="2" t="inlineStr">
@@ -25215,7 +25217,7 @@
           <t>De uitspraak 'Leerlingen moeten gezonder drinken' sluit direct aan bij het codebegrip 'Verbeterd gezondheidsgedrag', dat verwijst naar een waargenomen toename van gezond gedrag zoals vaker water drinken. Dit is een duidelijke en directe match met de codeomschrijving.</t>
         </is>
       </c>
-      <c r="J427" s="2" t="n">
+      <c r="J427" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K427" s="2" t="inlineStr">
@@ -25273,7 +25275,7 @@
           <t>De uitspraak benadrukt het belang van blijvende aandacht en continuïteit voor de Gezonde School-aanpak, wat direct aansluit bij het concept van duurzame verankering zoals omschreven: blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J428" s="2" t="n">
+      <c r="J428" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K428" s="2" t="inlineStr">
@@ -25331,7 +25333,7 @@
           <t>De uitdrukking 'verdwijnt af en toe in de waan van de dag' duidt op een gebrek aan blijvende en consistente aanwezigheid van de Gezonde School-aanpak in de schoolpraktijk, wat overeenkomt met de code 'Onvoldoende verankering' die verwijst naar een zwakke of ontbrekende verankering van de aanpak.</t>
         </is>
       </c>
-      <c r="J429" s="2" t="n">
+      <c r="J429" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K429" s="2" t="inlineStr">
@@ -25389,7 +25391,7 @@
           <t>De uitspraak 'Er moet aandacht besteed worden aan de Gezonde School-aanpak' duidt op het belang van blijvende aandacht en ondersteuning voor de aanpak, wat aansluit bij het concept van 'Duurzame verankering' dat gaat over blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J430" s="2" t="n">
+      <c r="J430" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K430" s="2" t="inlineStr">
@@ -25447,7 +25449,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak de gestelde doelen op school behaalt, wat duidt op een blijvende en succesvolle uitvoering van de aanpak. Dit sluit het beste aan bij 'Duurzame verankering', dat verwijst naar de blijvende uitvoering van de aanpak door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J431" s="2" t="n">
+      <c r="J431" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K431" s="2" t="inlineStr">
@@ -25505,7 +25507,7 @@
           <t>De uitspraak benadrukt de rol van ouders in het voortzetten van de Gezonde School-aanpak, wat direct aansluit bij de code 'Ouderlijke betrokkenheid' die gaat over het informeren en betrekken van ouders bij gezondheidsthema's ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J432" s="2" t="n">
+      <c r="J432" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K432" s="2" t="inlineStr">
@@ -25563,7 +25565,7 @@
           <t>De idee benadrukt het belang van ouders die betrokken zijn bij de Gezonde School-aanpak, wat direct aansluit bij de code 'Ouderlijke betrokkenheid' die gaat over het informeren en betrekken van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J433" s="2" t="n">
+      <c r="J433" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K433" s="2" t="inlineStr">
@@ -25621,7 +25623,7 @@
           <t>De suggestie om gezonde producten vaker te bespreken sluit aan bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, wat past binnen de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J434" s="2" t="n">
+      <c r="J434" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K434" s="2" t="inlineStr">
@@ -25679,7 +25681,7 @@
           <t>De opmerking 'Een gezonde muffin is een discussiepunt' duidt op onduidelijkheid of discussie over wat als gezonde traktatie wordt gezien, wat aansluit bij het ontbreken van duidelijke traktatieregels en communicatie zoals beschreven in de code 'Onvoldoende beleidsduidelijkheid traktaties'.</t>
         </is>
       </c>
-      <c r="J435" s="2" t="n">
+      <c r="J435" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K435" s="2" t="inlineStr">
@@ -25737,7 +25739,7 @@
           <t>De uitdrukking 'Een pizza punt is een discussiepunt' suggereert dat er onduidelijkheid of discussie is over traktatieregels, wat aansluit bij het code label 'Onvoldoende beleidsduidelijkheid traktaties' dat gaat over afwezigheid van duidelijke traktatieregels en communicatie.</t>
         </is>
       </c>
-      <c r="J436" s="2" t="n">
+      <c r="J436" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K436" s="2" t="inlineStr">
@@ -25795,7 +25797,7 @@
           <t>De reactie gaat over het beter definiëren van wat ongezonde producten zijn, wat direct verband houdt met het beleid of acties om het aanbod en de zichtbaarheid van ongezonde producten op school te beperken. Dit sluit goed aan bij de code 'Beperken van ongezonde producten'.</t>
         </is>
       </c>
-      <c r="J437" s="2" t="n">
+      <c r="J437" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K437" s="2" t="inlineStr">
@@ -25853,7 +25855,7 @@
           <t>De term 'aangescherpt' suggereert een verbetering of versterking van de aanpak, wat aansluit bij het concept van 'Duurzame verankering' waarbij blijvende uitvoering en brede betrokkenheid centraal staan.</t>
         </is>
       </c>
-      <c r="J438" s="2" t="n">
+      <c r="J438" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K438" s="2" t="inlineStr">
@@ -25911,7 +25913,7 @@
           <t>De term 'gruitdagen' lijkt een typefout of verbastering van 'fruitdagen', wat duidt op het verstrekken van fruit op school. Dit sluit direct aan bij de code 'Structurele gratis fruitvoorziening', die gaat over consistente gratis dagelijkse verstrekking van fruit op school. Daarom is deze code de beste match.</t>
         </is>
       </c>
-      <c r="J439" s="2" t="n">
+      <c r="J439" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K439" s="2" t="inlineStr">
@@ -25969,7 +25971,7 @@
           <t>De vermelding van fruitkisten op school sluit direct aan bij het concept van een consistente gratis dagelijkse verstrekking van fruit op school, wat precies wordt beschreven onder 'Structurele gratis fruitvoorziening'.</t>
         </is>
       </c>
-      <c r="J440" s="2" t="n">
+      <c r="J440" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K440" s="2" t="inlineStr">
@@ -26027,7 +26029,7 @@
           <t>De reactie verwijst expliciet naar initiatieven rondom seksualiteit binnen de Gezonde School-aanpak, wat direct aansluit bij de code 'Seksualiteitsvoorlichting' die gaat over lessen of activiteiten over seksualiteit om kennis en bewustzijn te vergroten.</t>
         </is>
       </c>
-      <c r="J441" s="2" t="n">
+      <c r="J441" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K441" s="2" t="inlineStr">
@@ -26085,7 +26087,7 @@
           <t>De reactie geeft aan dat er veel initiatieven zijn genomen rondom leefstijl, wat direct aansluit bij de definitie van 'Brede implementatie van gezondheidsthema's' die verwijst naar zichtbare invoering van concrete initiatieven rond leefstijl op school.</t>
         </is>
       </c>
-      <c r="J442" s="2" t="n">
+      <c r="J442" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K442" s="2" t="inlineStr">
@@ -26143,7 +26145,7 @@
           <t>De reactie benadrukt dat er veel initiatieven zijn genomen rondom voeding, wat past bij de brede invoering van concrete initiatieven rond leefstijl en voeding op school, zoals beschreven in de code 'Brede implementatie van gezondheidsthema's'.</t>
         </is>
       </c>
-      <c r="J443" s="2" t="n">
+      <c r="J443" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K443" s="2" t="inlineStr">
@@ -26201,7 +26203,7 @@
           <t>De reactie geeft aan dat er veel initiatieven zijn genomen rondom het thema gewicht, wat direct aansluit bij de definitie van 'Brede implementatie van gezondheidsthema's' die verwijst naar zichtbare invoering van initiatieven rond leefstijl, voeding en gewicht op school.</t>
         </is>
       </c>
-      <c r="J444" s="2" t="n">
+      <c r="J444" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K444" s="2" t="inlineStr">
@@ -26259,7 +26261,7 @@
           <t>De reactie benadrukt initiatieven rond rookpreventie, wat valt onder de zichtbare invoering van concrete gezondheidsthema's zoals leefstijl en rookpreventie op school, precies zoals beschreven in de code 'Brede implementatie van gezondheidsthema's'.</t>
         </is>
       </c>
-      <c r="J445" s="2" t="n">
+      <c r="J445" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K445" s="2" t="inlineStr">
@@ -26317,7 +26319,7 @@
           <t>De reactie geeft aan dat er veel initiatieven zijn genomen rondom vapen, wat valt onder de zichtbare invoering van gezondheidsthema's zoals rookpreventie op school. Dit sluit direct aan bij de code 'Brede implementatie van gezondheidsthema's' die gaat over concrete initiatieven rond leefstijl en rookpreventie.</t>
         </is>
       </c>
-      <c r="J446" s="2" t="n">
+      <c r="J446" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K446" s="2" t="inlineStr">
@@ -26375,7 +26377,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak samenwerkt met de GGD, wat precies aansluit bij de code 'Ondersteunende samenwerking GGD' die beschrijft dat GGD-regisseurs de school ondersteunen bij de uitvoering van Gezonde School-activiteiten.</t>
         </is>
       </c>
-      <c r="J447" s="2" t="n">
+      <c r="J447" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K447" s="2" t="inlineStr">
@@ -26433,7 +26435,7 @@
           <t>De uitdrukking 'doorgaande lijn door de hele school' duidt op een blijvende en brede implementatie van de Gezonde School-aanpak, wat aansluit bij de definitie van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J448" s="2" t="n">
+      <c r="J448" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K448" s="2" t="inlineStr">
@@ -26491,7 +26493,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak meerdere gezondheidsthema's omvat en niet beperkt is tot alleen gezond eten. Dit sluit goed aan bij de code 'Brede implementatie van gezondheidsthema's', die verwijst naar de invoering van diverse leefstijl- en gezondheidsthema's op school.</t>
         </is>
       </c>
-      <c r="J449" s="2" t="n">
+      <c r="J449" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K449" s="2" t="inlineStr">
@@ -26549,7 +26551,7 @@
           <t>De vermelding van 'andere onderwerpen zoals paarse vrijdag' duidt op een brede integratie van diverse gezondheidsthema's binnen de Gezonde School-aanpak, wat aansluit bij de code 'Aandacht voor brede gezondheidsthema's' die milieu, seksuele relaties en sociaal-emotionele onderwerpen omvat.</t>
         </is>
       </c>
-      <c r="J450" s="2" t="n">
+      <c r="J450" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K450" s="2" t="inlineStr">
@@ -26607,7 +26609,7 @@
           <t>De opmerking dat de Gezonde School-aanpak meer tijd kost voor leerkrachten wijst op een mogelijke belemmering in de verankering van de aanpak binnen de schoolpraktijk, wat aansluit bij de code 'Onvoldoende verankering' die zwakke of ontbrekende verankering beschrijft, zichtbaar in lage prioriteit of tijd.</t>
         </is>
       </c>
-      <c r="J451" s="2" t="n">
+      <c r="J451" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K451" s="2" t="inlineStr">
@@ -26665,7 +26667,7 @@
           <t>De opmerking dat de Gezonde School-aanpak leerkrachten meer energie kost, duidt op een mogelijke zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk, wat leidt tot extra belasting voor leerkrachten. Dit sluit aan bij de code 'Onvoldoende verankering' die wijst op lage herkenning, prioriteit, tijd of handhaving.</t>
         </is>
       </c>
-      <c r="J452" s="2" t="n">
+      <c r="J452" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K452" s="2" t="inlineStr">
@@ -26723,7 +26725,7 @@
           <t>De uitspraak benadrukt de rol van ouders in gezond opvoeden, wat aansluit bij het code label 'Ouderlijke betrokkenheid' dat gaat over het informeren van ouders ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J453" s="2" t="n">
+      <c r="J453" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K453" s="2" t="inlineStr">
@@ -26781,7 +26783,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak moet meer aandacht krijgen' duidt op een behoefte aan blijvende en bredere betrokkenheid en ondersteuning, wat aansluit bij het concept van 'Duurzame verankering' als blijvende uitvoering door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J454" s="2" t="n">
+      <c r="J454" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K454" s="2" t="inlineStr">
@@ -26839,7 +26841,7 @@
           <t>De uitdrukking 'Er komt veel op het bordje onderwijs' suggereert dat er een overbelasting of onvoldoende ondersteuning is binnen het onderwijs om de Gezonde School-aanpak goed te implementeren. Dit sluit aan bij 'Onvoldoende verankering', waar sprake is van een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk, wat kan leiden tot lage herkenning, prioriteit of tijd voor de uitvoering.</t>
         </is>
       </c>
-      <c r="J455" s="2" t="n">
+      <c r="J455" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K455" s="2" t="inlineStr">
@@ -26897,7 +26899,7 @@
           <t>De suggestie om meer lesuren biologie en verzorging aan te bieden sluit direct aan bij het vergroten van het aantal lesuren voor gezondheidseducatie, wat precies wordt beschreven in de code 'Meer lestijd voor gezondheidseducatie'.</t>
         </is>
       </c>
-      <c r="J456" s="2" t="n">
+      <c r="J456" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K456" s="2" t="inlineStr">
@@ -26955,7 +26957,7 @@
           <t>De reactie benadrukt het belang van het behouden van lesuren biologie en verzorging, wat aansluit bij de code 'Meer lestijd voor gezondheidseducatie' die vraagt om een toename van lesuren voor gezondheidseducatie.</t>
         </is>
       </c>
-      <c r="J457" s="2" t="n">
+      <c r="J457" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K457" s="2" t="inlineStr">
@@ -27013,7 +27015,7 @@
           <t>De opmerking suggereert dat de Gezonde School-aanpak niet goed geïntegreerd is binnen de schoolpraktijk, doordat onderwerpen onder mentoraat worden weggeschoven. Dit duidt op een zwakke of ontbrekende verankering van de aanpak in de school, wat overeenkomt met de code 'Onvoldoende verankering'.</t>
         </is>
       </c>
-      <c r="J458" s="2" t="n">
+      <c r="J458" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K458" s="2" t="inlineStr">
@@ -27071,7 +27073,7 @@
           <t>De opmerking gaat over het gebrek aan professionele kennis van mentoren op een specifiek gebied (biologie en verzorging), wat kan duiden op een tekort aan duidelijke beleidslijnen of richtlijnen omtrent wie verantwoordelijk is voor bepaalde gezondheidsthema's. Hoewel de code 'Onvoldoende beleidsduidelijkheid traktaties' specifiek over traktatieregels gaat, is dit de meest nabije code die wijst op een gebrek aan duidelijke beleidsvoering binnen de Gezonde School-aanpak.</t>
         </is>
       </c>
-      <c r="J459" s="2" t="n">
+      <c r="J459" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="K459" s="2" t="inlineStr">
@@ -27129,7 +27131,7 @@
           <t>De reactie benadrukt het belang van het betrekken van leerlingen ('creëren en volgen van leerlingen'), wat aansluit bij de code 'Leerlinginspraak' die gaat over het betrekken van leerlingen bij besluitvorming en activiteiten om hun welbevinden te verbeteren.</t>
         </is>
       </c>
-      <c r="J460" s="2" t="n">
+      <c r="J460" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K460" s="2" t="inlineStr">
@@ -27187,7 +27189,7 @@
           <t>De reactie benadrukt de noodzaak van meer bewustzijn en voorlichting, wat aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J461" s="2" t="n">
+      <c r="J461" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K461" s="2" t="inlineStr">
@@ -27245,7 +27247,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak gericht is op het ondersteunen van leerlingen bij het maken van gezondere keuzes, wat direct aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J462" s="2" t="n">
+      <c r="J462" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K462" s="2" t="inlineStr">
@@ -27303,7 +27305,7 @@
           <t>De uiting 'Mentale welzijn moet meer op de voorgrond staan' sluit aan bij het code-label 'Aandacht voor brede gezondheidsthema's', omdat dit code-label de integratie van sociaal-emotionele onderwerpen (waaronder mentale gezondheid) in het schoolbeleid en onderwijs beschrijft. Dit is een sterke match omdat mentale welzijn een onderdeel is van brede gezondheidsthema's.</t>
         </is>
       </c>
-      <c r="J463" s="2" t="n">
+      <c r="J463" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K463" s="2" t="inlineStr">
@@ -27361,7 +27363,7 @@
           <t>De reactie benadrukt een positieve uitkomst van de Gezonde School-aanpak op de mentaliteit rondom gezondheid, wat aansluit bij het concept van waargenomen toename van gezond gedrag bij leerlingen.</t>
         </is>
       </c>
-      <c r="J464" s="2" t="n">
+      <c r="J464" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K464" s="2" t="inlineStr">
@@ -27419,7 +27421,7 @@
           <t>De uitspraak 'zorgt voor een fijne leeromgeving' duidt op een positieve invloed van de Gezonde School-aanpak op de schoolcultuur en het welzijn, wat aansluit bij het concept van een 'Effectief ingebed kader' dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert.</t>
         </is>
       </c>
-      <c r="J465" s="2" t="n">
+      <c r="J465" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K465" s="2" t="inlineStr">
@@ -27477,7 +27479,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak veel oplevert voor het sporten, wat direct aansluit bij het concept van een ruim bewegingsaanbod, namelijk frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J466" s="2" t="n">
+      <c r="J466" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K466" s="2" t="inlineStr">
@@ -27535,7 +27537,7 @@
           <t>De reactie vraagt om duidelijkheid over het voedingsbeleid rondom lunch, wat direct aansluit bij het concept van 'Structureel voedingsbeleid' dat gaat over blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J467" s="2" t="n">
+      <c r="J467" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K467" s="2" t="inlineStr">
@@ -27593,7 +27595,7 @@
           <t>De reactie vraagt om duidelijkheid over het voedingsbeleid rondom pauzehap, wat direct aansluit bij het concept van 'Structureel voedingsbeleid' dat gaat over blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J468" s="2" t="n">
+      <c r="J468" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K468" s="2" t="inlineStr">
@@ -27651,7 +27653,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak moet beter worden' duidt op ontevredenheid over de huidige uitvoering en verankering van de aanpak. Dit sluit aan bij 'Onvoldoende verankering', wat verwijst naar een zwakke of ontbrekende verankering van de aanpak in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J469" s="2" t="n">
+      <c r="J469" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K469" s="2" t="inlineStr">
@@ -27709,7 +27711,7 @@
           <t>De opmerking geeft aan dat de Gezonde School-aanpak actief is tijdens feesten, wat duidt op zichtbare en concrete initiatieven rond gezondheidsthema's binnen de schoolcontext. Dit sluit het beste aan bij 'Brede implementatie van gezondheidsthema's', omdat het gaat om de invoering van gezondheid gerelateerde activiteiten op school.</t>
         </is>
       </c>
-      <c r="J470" s="2" t="n">
+      <c r="J470" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K470" s="2" t="inlineStr">
@@ -27767,7 +27769,7 @@
           <t>De opmerking dat de Gezonde School-aanpak veel doet op evenementen duidt op zichtbare en concrete initiatieven rond gezondheidsthema's op school, wat aansluit bij de code 'Brede implementatie van gezondheidsthema's'. Het gaat om activiteiten die breed en zichtbaar zijn, wat past bij de definitie van deze code.</t>
         </is>
       </c>
-      <c r="J471" s="2" t="n">
+      <c r="J471" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K471" s="2" t="inlineStr">
@@ -27825,7 +27827,7 @@
           <t>De reactie geeft aan dat de Gezonde School-aanpak actief is op bijzondere schooldagen, wat duidt op zichtbare en concrete initiatieven binnen de school. Dit sluit het beste aan bij 'Brede implementatie van gezondheidsthema's', omdat het wijst op een brede en zichtbare invoering van gezondheidsthema's op school, ook al is het specifiek gericht op bijzondere dagen.</t>
         </is>
       </c>
-      <c r="J472" s="2" t="n">
+      <c r="J472" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K472" s="2" t="inlineStr">
@@ -27883,7 +27885,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak zich richt op voeding, wat aansluit bij het code label 'Structureel voedingsbeleid' dat gaat over blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J473" s="2" t="n">
+      <c r="J473" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K473" s="2" t="inlineStr">
@@ -27941,7 +27943,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak zich richt op beweging, wat direct aansluit bij het code label 'Ruim bewegingsaanbod', dat gaat over het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J474" s="2" t="n">
+      <c r="J474" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K474" s="2" t="inlineStr">
@@ -27999,7 +28001,7 @@
           <t>De uitspraak 'doet veel dingen' suggereert een brede aanpak met meerdere initiatieven en thema's, wat het beste aansluit bij 'Brede implementatie van gezondheidsthema's' die verwijst naar zichtbare terreinoverstijgende invoering van diverse gezondheidsthema's op school.</t>
         </is>
       </c>
-      <c r="J475" s="2" t="n">
+      <c r="J475" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K475" s="2" t="inlineStr">
@@ -28057,7 +28059,7 @@
           <t>De aanwezigheid van een coördinator duidt op een structurele en blijvende uitvoering van de Gezonde School-aanpak, wat aansluit bij het concept van duurzame verankering door bestuurlijke steun en betrokkenheid.</t>
         </is>
       </c>
-      <c r="J476" s="2" t="n">
+      <c r="J476" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K476" s="2" t="inlineStr">
@@ -28115,7 +28117,7 @@
           <t>Een werkgroep binnen de Gezonde School-aanpak duidt op een georganiseerde en structurele aanpak met betrokkenheid, wat past bij het concept van duurzame verankering van de aanpak in de school.</t>
         </is>
       </c>
-      <c r="J477" s="2" t="n">
+      <c r="J477" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K477" s="2" t="inlineStr">
@@ -28173,7 +28175,7 @@
           <t>De idee beschrijft het organiseren van activiteiten tijdens pauzes, wat aansluit bij het concept van een ruim bewegingsaanbod: frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J478" s="2" t="n">
+      <c r="J478" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K478" s="2" t="inlineStr">
@@ -28231,7 +28233,7 @@
           <t>De vermelding van activiteiten in de kantine verwijst naar de beschikbaarheid en toegankelijkheid van gezond eten binnen de schoolomgeving, wat aansluit bij de code 'Toegankelijkheid gezond voedingsaanbod' die gaat over de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is.</t>
         </is>
       </c>
-      <c r="J479" s="2" t="n">
+      <c r="J479" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K479" s="2" t="inlineStr">
@@ -28289,7 +28291,7 @@
           <t>De opmerking dat de Gezonde School-aanpak gericht is op docenten suggereert een focus op de betrokkenheid en verankering binnen de schoolorganisatie, wat aansluit bij het concept van duurzame verankering, namelijk blijvende uitvoering door brede betrokkenheid. Hoewel het niet expliciet over bestuurlijke steun gaat, is de focus op docenten een aspect van verankering in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J480" s="2" t="n">
+      <c r="J480" s="3" t="n">
         <v>0.6</v>
       </c>
       <c r="K480" s="2" t="inlineStr">
@@ -28347,7 +28349,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak zich richt op leerlingen, wat aansluit bij het concept van brede implementatie van gezondheidsthema's die zichtbaar en concreet zijn binnen de schoolcontext.</t>
         </is>
       </c>
-      <c r="J481" s="2" t="n">
+      <c r="J481" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K481" s="2" t="inlineStr">
@@ -28405,7 +28407,7 @@
           <t>De idee beschrijft een structurele voorziening van gezonde voeding (warme lunch) op school, wat direct aansluit bij de definitie van 'Structureel voedingsbeleid' als blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J482" s="2" t="n">
+      <c r="J482" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K482" s="2" t="inlineStr">
@@ -28463,7 +28465,7 @@
           <t>De idee beschrijft expliciet het gratis aanbieden van fruit aan alle kinderen gedurende een groot deel van het schooljaar, wat precies overeenkomt met de definitie van 'Structurele gratis fruitvoorziening' als consistente gratis dagelijkse verstrekking van fruit op school.</t>
         </is>
       </c>
-      <c r="J483" s="2" t="n">
+      <c r="J483" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K483" s="2" t="inlineStr">
@@ -28521,7 +28523,7 @@
           <t>De vermelding van een waterfles op tafel en een kraan in de klas duidt op blijvende voorzieningen gericht op gezond drinken, wat past binnen het concept van structureel voedingsbeleid zoals beschreven.</t>
         </is>
       </c>
-      <c r="J484" s="2" t="n">
+      <c r="J484" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K484" s="2" t="inlineStr">
@@ -28579,7 +28581,7 @@
           <t>De deelname aan nationale kraanwaterdag suggereert een initiatief dat gericht is op het stimuleren van gezond gedrag, zoals het vaker drinken van water, wat aansluit bij de code 'Verbeterd gezondheidsgedrag'.</t>
         </is>
       </c>
-      <c r="J485" s="2" t="n">
+      <c r="J485" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K485" s="2" t="inlineStr">
@@ -28637,7 +28639,7 @@
           <t>De reactie verwijst expliciet naar een nieuwe methode voor sociale emotionele ontwikkeling binnen de Gezonde School-aanpak, wat direct aansluit bij de code 'Methodische verankering van sociaal-emotionele ontwikkeling' die gaat over de invoering van een vaste methode voor registratie van sociale emotionele ontwikkeling op school.</t>
         </is>
       </c>
-      <c r="J486" s="2" t="n">
+      <c r="J486" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K486" s="2" t="inlineStr">
@@ -28695,7 +28697,7 @@
           <t>De reactie beschrijft het in kaart brengen van sociale emotionele ontwikkeling met een methode ('iep hart en handen'), wat direct aansluit bij de code 'Methodische verankering van sociaal-emotionele ontwikkeling' die verwijst naar een vaste methode voor registratie van deze ontwikkeling op school.</t>
         </is>
       </c>
-      <c r="J487" s="2" t="n">
+      <c r="J487" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K487" s="2" t="inlineStr">
@@ -28753,7 +28755,7 @@
           <t>De idee beschrijft het organiseren van activiteiten met een externe instantie, wat past bij het concept van samenwerking met externe partijen zoals de GGD ter ondersteuning van Gezonde School-activiteiten.</t>
         </is>
       </c>
-      <c r="J488" s="2" t="n">
+      <c r="J488" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K488" s="2" t="inlineStr">
@@ -28811,7 +28813,7 @@
           <t>De vermelding van twee keer per week gym duidt op een frequente en toegankelijke bewegingsactiviteit gedurende de schooldag, wat precies past bij de definitie van 'Ruim bewegingsaanbod'.</t>
         </is>
       </c>
-      <c r="J489" s="2" t="n">
+      <c r="J489" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K489" s="2" t="inlineStr">
@@ -28869,7 +28871,7 @@
           <t>De uitspraak 'maakt de school meer alert' duidt op een zichtbare verbetering in de schoolcultuur of het welzijn, wat aansluit bij de definitie van 'Effectief ingebed kader' als een raamwerk dat zichtbare verbeteringen bevordert.</t>
         </is>
       </c>
-      <c r="J490" s="2" t="n">
+      <c r="J490" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K490" s="2" t="inlineStr">
@@ -28927,7 +28929,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak leidt tot meer tijdsbesteding aan gezondheid, wat direct aansluit bij het code label 'Meer lestijd voor gezondheidseducatie', dat verwijst naar het vergroten van het aantal lesuren voor gezondheidseducatie.</t>
         </is>
       </c>
-      <c r="J491" s="2" t="n">
+      <c r="J491" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K491" s="2" t="inlineStr">
@@ -28985,7 +28987,7 @@
           <t>De uitspraak benadrukt het stimuleren van bewustwording van gezondheid, wat direct aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die gezond gedrag stimuleren, zoals beschreven in de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J492" s="2" t="n">
+      <c r="J492" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K492" s="2" t="inlineStr">
@@ -29043,7 +29045,7 @@
           <t>De uitspraak benadrukt het belang van gezondheid in de maatschappij, wat aansluit bij het concept van brede implementatie van gezondheidsthema's op school, waarbij diverse leefstijl- en gezondheidsonderwerpen worden geïntegreerd.</t>
         </is>
       </c>
-      <c r="J493" s="2" t="n">
+      <c r="J493" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K493" s="2" t="inlineStr">
@@ -29101,7 +29103,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak concrete hulpmiddelen ('handvatten') biedt voor het programma gezonde en veilige school, wat precies aansluit bij de code 'Handvatten voor gezonde leefstijl' die gaat over uitvoerbare maatregelen en hulpmiddelen die gezond gedrag stimuleren.</t>
         </is>
       </c>
-      <c r="J494" s="2" t="n">
+      <c r="J494" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K494" s="2" t="inlineStr">
@@ -29159,7 +29161,7 @@
           <t>De term 'handvatten' verwijst naar concrete uitvoerbare maatregelen en hulpmiddelen die de school helpen bij het stimuleren van een gezonde leefstijl, wat precies aansluit bij de definitie van de code 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J495" s="2" t="n">
+      <c r="J495" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K495" s="2" t="inlineStr">
@@ -29217,7 +29219,7 @@
           <t>De uitspraak 'De aanpak geeft een boost aan bepaalde programma's op school' duidt op een versterking of uitbreiding van initiatieven binnen de Gezonde School-aanpak. Dit sluit het beste aan bij 'Brede implementatie van gezondheidsthema's', omdat dit code-label verwijst naar de zichtbare invoering van concrete initiatieven rond gezondheidsthema's op school, wat overeenkomt met het versterken van programma's.</t>
         </is>
       </c>
-      <c r="J496" s="2" t="n">
+      <c r="J496" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K496" s="2" t="inlineStr">
@@ -29275,7 +29277,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak zorgt voor dagelijkse fruitverstrekking aan kinderen, wat precies aansluit bij de code 'Structurele gratis fruitvoorziening' die verwijst naar consistente gratis dagelijkse verstrekking van fruit op school.</t>
         </is>
       </c>
-      <c r="J497" s="2" t="n">
+      <c r="J497" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K497" s="2" t="inlineStr">
@@ -29333,7 +29335,7 @@
           <t>De reactie beschrijft dat melk meerdere keren per week wordt geschonken, wat direct betrekking heeft op de mate waarin gezond eten (in dit geval melk als gezond voedingsaanbod) binnen de school gemakkelijk te verkrijgen is. Dit sluit nauw aan bij de code 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J498" s="2" t="n">
+      <c r="J498" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K498" s="2" t="inlineStr">
@@ -29391,7 +29393,7 @@
           <t>De vermelding van het regelmatig eten van verse soep binnen de Gezonde School-aanpak duidt op een blijvende voorziening of beleid gericht op gezond eten op school, wat precies valt onder 'Structureel voedingsbeleid'.</t>
         </is>
       </c>
-      <c r="J499" s="2" t="n">
+      <c r="J499" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K499" s="2" t="inlineStr">
@@ -29449,7 +29451,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak zorgt voor frequente bewegingsmomenten (twee keer per week gym), wat direct aansluit bij de definitie van 'Ruim bewegingsaanbod' als een aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J500" s="2" t="n">
+      <c r="J500" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K500" s="2" t="inlineStr">
@@ -29507,7 +29509,7 @@
           <t>De vermelding dat kinderen twee keer per dag pauze hebben, duidt op het aanbieden van frequente en toegankelijke bewegingsmomenten gedurende de schooldag, wat precies past bij de definitie van 'Ruim bewegingsaanbod'.</t>
         </is>
       </c>
-      <c r="J501" s="2" t="n">
+      <c r="J501" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K501" s="2" t="inlineStr">
@@ -29565,7 +29567,7 @@
           <t>De uitspraak richt zich op het verminderen van de verkoop van snoepgoed, wat direct aansluit bij het beleid om het aanbod en de zichtbaarheid van ongezonde producten zoals snoep op school te beperken.</t>
         </is>
       </c>
-      <c r="J502" s="2" t="n">
+      <c r="J502" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K502" s="2" t="inlineStr">
@@ -29623,7 +29625,7 @@
           <t>De opmerking benadrukt het belang van welzijn van leerlingen, wat past binnen het bredere gezondheidsthema dat ook sociaal-emotionele aspecten omvat, zoals beschreven in de code 'Aandacht voor brede gezondheidsthema's'.</t>
         </is>
       </c>
-      <c r="J503" s="2" t="n">
+      <c r="J503" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K503" s="2" t="inlineStr">
@@ -29681,7 +29683,7 @@
           <t>De suggestie om voorlichting te geven over criminaliteit en mobieltjes valt onder de integratie van brede gezondheidsthema's zoals milieu, sociale en emotionele onderwerpen, wat aansluit bij de code 'Aandacht voor brede gezondheidsthema's'.</t>
         </is>
       </c>
-      <c r="J504" s="2" t="n">
+      <c r="J504" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K504" s="2" t="inlineStr">
@@ -29739,7 +29741,7 @@
           <t>De suggestie om voorlichting te geven over het voorkomen van pestgedrag valt onder de integratie van sociaal-emotionele onderwerpen in het schoolbeleid, wat past binnen 'Aandacht voor brede gezondheidsthema's'.</t>
         </is>
       </c>
-      <c r="J505" s="2" t="n">
+      <c r="J505" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K505" s="2" t="inlineStr">
@@ -29797,7 +29799,7 @@
           <t>De idee benadrukt het leren herkennen en voorkomen van ongewenste situaties, wat aansluit bij het bieden van concrete uitvoerbare maatregelen en hulpmiddelen die bewustwording en gezond gedrag stimuleren, zoals beschreven in 'Handvatten voor gezonde leefstijl'.</t>
         </is>
       </c>
-      <c r="J506" s="2" t="n">
+      <c r="J506" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K506" s="2" t="inlineStr">
@@ -29855,7 +29857,7 @@
           <t>De reactie 'Kinderen nemen ongezonde dingen' verwijst direct naar het probleem van ongezonde producten die door kinderen worden genomen. Dit sluit nauw aan bij de code 'Beperken van ongezonde producten', die gaat over acties of beleid om het aanbod en de zichtbaarheid van snoep, snacks en frisdrank op school te verminderen. De reactie geeft impliciet aan dat er een probleem is met ongezonde producten, wat precies het onderwerp van deze code is.</t>
         </is>
       </c>
-      <c r="J507" s="2" t="n">
+      <c r="J507" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K507" s="2" t="inlineStr">
@@ -29913,7 +29915,7 @@
           <t>De uitspraak 'Er is geen beleid voor gezonde voeding op school' sluit direct aan bij het ontbreken van een 'Structureel voedingsbeleid', dat volgens de definitie verwijst naar blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J508" s="2" t="n">
+      <c r="J508" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K508" s="2" t="inlineStr">
@@ -29971,7 +29973,7 @@
           <t>De uitspraak 'Er is geen structuur voor gezonde voeding op school' verwijst direct naar het ontbreken van een blijvend beleid of voorzieningen gericht op gezond eten, wat precies valt onder de definitie van 'Structureel voedingsbeleid'.</t>
         </is>
       </c>
-      <c r="J509" s="2" t="n">
+      <c r="J509" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K509" s="2" t="inlineStr">
@@ -30029,7 +30031,7 @@
           <t>De opmerking dat lessen over gezonde voeding niet worden gegeven, duidt op een tekort aan lestijd of aandacht voor gezondheidseducatie. Dit sluit goed aan bij de code 'Meer lestijd voor gezondheidseducatie', die verwijst naar uitingen die vragen om meer lesuren voor gezondheidseducatie.</t>
         </is>
       </c>
-      <c r="J510" s="2" t="n">
+      <c r="J510" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K510" s="2" t="inlineStr">
@@ -30087,7 +30089,7 @@
           <t>De opmerking dat traktaties op school niet gezond zijn, wijst op een probleem met het beleid of de regels rondom traktaties. Dit sluit aan bij de code 'Onvoldoende beleidsduidelijkheid traktaties', die verwijst naar het ontbreken van duidelijke traktatieregels en communicatie, wat leidt tot weerstand of problemen bij handhaving.</t>
         </is>
       </c>
-      <c r="J511" s="2" t="n">
+      <c r="J511" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K511" s="2" t="inlineStr">
@@ -30145,7 +30147,7 @@
           <t>De reactie benadrukt dat de Gezonde School-aanpak zich richt op sport, bewegen en bewegend leren, wat direct aansluit bij het code-label 'Ruim bewegingsaanbod', dat gaat over het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J512" s="2" t="n">
+      <c r="J512" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K512" s="2" t="inlineStr">
@@ -30203,7 +30205,7 @@
           <t>De reactie geeft aan dat de leerresultaten zijn verbeterd door deelname aan een groot onderzoek, wat wijst op een zichtbaar en effectief raamwerk dat verbetering in schoolresultaten bevordert. Dit sluit het beste aan bij 'Effectief ingebed kader', dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert.</t>
         </is>
       </c>
-      <c r="J513" s="2" t="n">
+      <c r="J513" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K513" s="2" t="inlineStr">
@@ -30261,7 +30263,7 @@
           <t>De term 'vignet' verwijst naar een soort certificaat of erkenning die scholen kunnen behalen. Dit sluit aan bij de code 'Certificaten als vrijwillige erkenning', die optionele erkenningen beschrijft zonder verplichte opvolging. De keuzevrijheid van scholen om hier naartoe te werken benadrukt het vrijwillige karakter.</t>
         </is>
       </c>
-      <c r="J514" s="2" t="n">
+      <c r="J514" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K514" s="2" t="inlineStr">
@@ -30319,7 +30321,7 @@
           <t>De idee beschrijft expliciet dat scholen ondersteuning ontvangen van GGD en regisseurs, wat direct aansluit bij de code 'Ondersteunende samenwerking GGD' die gaat over GGD-regisseurs die scholen ondersteunen bij de uitvoering van Gezonde School-activiteiten.</t>
         </is>
       </c>
-      <c r="J515" s="2" t="n">
+      <c r="J515" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K515" s="2" t="inlineStr">
@@ -30377,7 +30379,7 @@
           <t>De uitspraak geeft aan dat scholen zelf kunnen kiezen welke vignetten (certificaten) bij hen passen, wat aansluit bij het concept van certificaten als optionele erkenning zonder verplichte opvolging.</t>
         </is>
       </c>
-      <c r="J516" s="2" t="n">
+      <c r="J516" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K516" s="2" t="inlineStr">
@@ -30435,7 +30437,7 @@
           <t>De idee beschrijft expliciet de dagelijkse gratis verstrekking van fruit aan leerlingen en personeel, wat precies overeenkomt met de definitie van 'Structurele gratis fruitvoorziening' als consistente gratis dagelijkse verstrekking van fruit op school.</t>
         </is>
       </c>
-      <c r="J517" s="2" t="n">
+      <c r="J517" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K517" s="2" t="inlineStr">
@@ -30493,7 +30495,7 @@
           <t>De vermelding dat leerlingen en personeel elke dag schoolmelk krijgen, duidt op een blijvende voorziening gericht op gezond eten binnen de school. Dit sluit direct aan bij de definitie van 'Structureel voedingsbeleid', dat gaat over blijvende voorzieningen of beleid gericht op gezond eten op school.</t>
         </is>
       </c>
-      <c r="J518" s="2" t="n">
+      <c r="J518" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K518" s="2" t="inlineStr">
@@ -30551,7 +30553,7 @@
           <t>De uitspraak 'Er mogen alleen gezonde traktaties uitgedeeld worden' sluit direct aan bij het concept van het verminderen van het aanbod en de zichtbaarheid van ongezonde producten zoals snoep en snacks op school. Dit valt binnen de definitie van 'Beperken van ongezonde producten', omdat het gaat om het beperken van ongezonde traktaties.</t>
         </is>
       </c>
-      <c r="J519" s="2" t="n">
+      <c r="J519" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K519" s="2" t="inlineStr">
@@ -30609,7 +30611,7 @@
           <t>De uitspraak 'Er wordt voldoende bewogen' sluit direct aan bij het code label 'Ruim bewegingsaanbod', dat verwijst naar het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag. Dit is een uitstekende match omdat de focus ligt op voldoende beweging binnen de schoolcontext.</t>
         </is>
       </c>
-      <c r="J520" s="2" t="n">
+      <c r="J520" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K520" s="2" t="inlineStr">
@@ -30667,7 +30669,7 @@
           <t>De reactie geeft aan dat er aandacht is voor het milieu, wat past binnen de code 'Aandacht voor brede gezondheidsthema's' die integratie van milieu en andere brede gezondheidsthema's in het schoolbeleid beschrijft.</t>
         </is>
       </c>
-      <c r="J521" s="2" t="n">
+      <c r="J521" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K521" s="2" t="inlineStr">
@@ -30725,7 +30727,7 @@
           <t>De idee beschrijft expliciet aandacht voor (seksuele) relaties, wat direct aansluit bij de code 'Seksualiteitsvoorlichting' die gaat over lessen of activiteiten over seksualiteit die kennis en bewustzijn vergroten.</t>
         </is>
       </c>
-      <c r="J522" s="2" t="n">
+      <c r="J522" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K522" s="2" t="inlineStr">
@@ -30783,7 +30785,7 @@
           <t>Een veilig pedagogisch klimaat duidt op een positieve schoolcultuur en welzijn, wat aansluit bij het code label 'Effectief ingebed kader' dat een raamwerk beschrijft dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert.</t>
         </is>
       </c>
-      <c r="J523" s="2" t="n">
+      <c r="J523" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K523" s="2" t="inlineStr">
@@ -30841,7 +30843,7 @@
           <t>De reactie benadrukt het effect van de Gezonde School-aanpak op ouders en kinderen, wat aansluit bij het concept van 'Ouderlijke betrokkenheid', waarbij ouders geïnformeerd worden en betrokken zijn bij gezondheidsthema's ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J524" s="2" t="n">
+      <c r="J524" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K524" s="2" t="inlineStr">
@@ -30899,7 +30901,7 @@
           <t>De uitspraak benadrukt dat de Gezonde School-aanpak een positieve invloed heeft op de schoolcultuur, wat aansluit bij het concept van een raamwerk dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert, zoals beschreven in 'Effectief ingebed kader'.</t>
         </is>
       </c>
-      <c r="J525" s="2" t="n">
+      <c r="J525" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K525" s="2" t="inlineStr">
@@ -30957,7 +30959,7 @@
           <t>De reactie benadrukt de verbetering van het gedrag van ouders en kinderen, wat aansluit bij het concept van 'Ouderlijke betrokkenheid', waarbij ouders geïnformeerd worden en betrokken zijn bij gezondheidsthema's ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J526" s="2" t="n">
+      <c r="J526" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K526" s="2" t="inlineStr">
@@ -31015,7 +31017,7 @@
           <t>De uitspraak benadrukt het bevorderen van het welbevinden van ouders en kinderen door de Gezonde School-aanpak, wat aansluit bij een raamwerk dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert. Dit is de beste match binnen de beschikbare codes.</t>
         </is>
       </c>
-      <c r="J527" s="2" t="n">
+      <c r="J527" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K527" s="2" t="inlineStr">
@@ -31073,7 +31075,7 @@
           <t>De reactie benadrukt het aanbieden van materialen om te bewegen, wat direct aansluit bij het code-label 'Ruim bewegingsaanbod', dat verwijst naar het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten en materialen gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J528" s="2" t="n">
+      <c r="J528" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K528" s="2" t="inlineStr">
@@ -31131,7 +31133,7 @@
           <t>De idee beschrijft het aanbieden van gymlessen door vakdocenten aan alle groepen, wat direct aansluit bij het concept van een ruim bewegingsaanbod met frequente en gevarieerde bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J529" s="2" t="n">
+      <c r="J529" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K529" s="2" t="inlineStr">
@@ -31189,7 +31191,7 @@
           <t>De reactie beschrijft expliciet het aanbieden van schoolfruit, wat direct aansluit bij de code 'Structurele gratis fruitvoorziening' die staat voor consistente gratis dagelijkse verstrekking van fruit op school.</t>
         </is>
       </c>
-      <c r="J530" s="2" t="n">
+      <c r="J530" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K530" s="2" t="inlineStr">
@@ -31247,7 +31249,7 @@
           <t>De uitspraak benadrukt dat kinderen iets gezonds krijgen op school, wat direct aansluit bij de mate waarin gezond eten binnen of nabij school gemakkelijk te verkrijgen is, zoals beschreven in 'Toegankelijkheid gezond voedingsaanbod'.</t>
         </is>
       </c>
-      <c r="J531" s="2" t="n">
+      <c r="J531" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K531" s="2" t="inlineStr">
@@ -31305,7 +31307,7 @@
           <t>De reactie benoemt specifiek nadelen van de aanpak in relatie tot het bemoeien met eetgedrag en voedselkeuzes van ouders, wat direct aansluit bij het code-label 'Ouderlijke betrokkenheid' dat gaat over het informeren en betrekken van ouders bij gezondheidsthema's ter ondersteuning van schoolinterventies.</t>
         </is>
       </c>
-      <c r="J532" s="2" t="n">
+      <c r="J532" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K532" s="2" t="inlineStr">
@@ -31363,7 +31365,7 @@
           <t>De term 'voorlichting' verwijst naar het geven van informatie en bewustwording, wat aansluit bij 'Handvatten voor gezonde leefstijl' die concrete maatregelen en hulpmiddelen omvatten om gezond gedrag te stimuleren. Dit is de beste match binnen de gegeven codes, omdat het direct gaat over het belang van educatie en ondersteuning binnen de Gezonde School-aanpak.</t>
         </is>
       </c>
-      <c r="J533" s="2" t="n">
+      <c r="J533" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K533" s="2" t="inlineStr">
@@ -31421,7 +31423,7 @@
           <t>De uitspraak benadrukt het belang van bewegen binnen de Gezonde School-aanpak, wat direct aansluit bij het code label 'Ruim bewegingsaanbod' dat gaat over het aanbod van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J534" s="2" t="n">
+      <c r="J534" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K534" s="2" t="inlineStr">
@@ -31479,7 +31481,7 @@
           <t>De idee benadrukt het belang van een gevarieerd en toegankelijk aanbod van bewegingsvormen en materialen, wat precies aansluit bij de definitie van 'Ruim bewegingsaanbod' als frequente, gevarieerde en toegankelijke bewegingsmomenten en materialen gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J535" s="2" t="n">
+      <c r="J535" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K535" s="2" t="inlineStr">
@@ -31537,7 +31539,7 @@
           <t>De opmerking gaat over de dunne scheidslijn tussen voorlichting geven en betutteling, wat duidt op de noodzaak van duidelijke, consistente en heldere communicatie binnen de Gezonde School-aanpak om dit onderscheid goed te maken.</t>
         </is>
       </c>
-      <c r="J536" s="2" t="n">
+      <c r="J536" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K536" s="2" t="inlineStr">
@@ -31595,7 +31597,7 @@
           <t>De uitspraak 'De Gezonde School-aanpak werkt' impliceert dat de aanpak succesvol en blijvend is, wat aansluit bij het concept van 'Duurzame verankering' waarbij de aanpak blijvend wordt uitgevoerd door bestuurlijke steun en brede betrokkenheid.</t>
         </is>
       </c>
-      <c r="J537" s="2" t="n">
+      <c r="J537" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K537" s="2" t="inlineStr">
@@ -31653,7 +31655,7 @@
           <t>De uitspraak benadrukt de noodzaak van voortdurende aandacht voor de Gezonde School-aanpak, wat aansluit bij het concept van 'Duurzame verankering' waarbij blijvende uitvoering en brede betrokkenheid centraal staan.</t>
         </is>
       </c>
-      <c r="J538" s="2" t="n">
+      <c r="J538" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K538" s="2" t="inlineStr">
@@ -31711,7 +31713,7 @@
           <t>De uitspraak benadrukt dat de werkwijze helpt om continu met de Gezonde School-aanpak bezig te blijven, wat aansluit bij het concept van blijvende uitvoering en verankering van de aanpak in de schoolpraktijk.</t>
         </is>
       </c>
-      <c r="J539" s="2" t="n">
+      <c r="J539" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K539" s="2" t="inlineStr">
@@ -31769,7 +31771,7 @@
           <t>De uitspraak benadrukt dat certificaten niet het primaire doel zijn, wat aansluit bij het concept van certificaten als optionele erkenning zonder verplichte opvolging.</t>
         </is>
       </c>
-      <c r="J540" s="2" t="n">
+      <c r="J540" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K540" s="2" t="inlineStr">
@@ -31827,7 +31829,7 @@
           <t>De uitdrukking 'slagroom op het toetje' suggereert dat certificaten een extra, niet noodzakelijke erkenning zijn. Dit sluit goed aan bij de code 'Certificaten als vrijwillige erkenning', die certificaten beschrijft als optionele erkenning zonder verplichte opvolging.</t>
         </is>
       </c>
-      <c r="J541" s="2" t="n">
+      <c r="J541" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K541" s="2" t="inlineStr">
@@ -31885,7 +31887,7 @@
           <t>De uitspraak benadrukt het belang van de Gezonde School-aanpak voor het welzijn van kinderen, wat aansluit bij het concept van een raamwerk dat zichtbare verbeteringen in schoolcultuur of welzijn bevordert. Dit is een sterke match met 'Effectief ingebed kader' omdat het idee de positieve impact van de aanpak op welzijn onderstreept.</t>
         </is>
       </c>
-      <c r="J542" s="2" t="n">
+      <c r="J542" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K542" s="2" t="inlineStr">
@@ -31943,7 +31945,7 @@
           <t>De uitspraak benadrukt het algemene belang van de Gezonde School-aanpak voor de gezondheid van kinderen, wat aansluit bij de brede invoering van gezondheidsthema's op school. Hoewel het niet specifiek ingaat op concrete initiatieven, past het conceptueel het beste bij de brede implementatie van gezondheidsthema's.</t>
         </is>
       </c>
-      <c r="J543" s="2" t="n">
+      <c r="J543" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K543" s="2" t="inlineStr">
@@ -32001,7 +32003,7 @@
           <t>De reactie benadrukt de heldere en duidelijke communicatie naar ouders, wat precies aansluit bij de code 'Consistente heldere communicatie' die staat voor regelmatige, eenduidige en verzorgde informatievoorziening aan alle betrokkenen.</t>
         </is>
       </c>
-      <c r="J544" s="2" t="n">
+      <c r="J544" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K544" s="2" t="inlineStr">
@@ -32059,7 +32061,7 @@
           <t>De reactie benadrukt de heldere en duidelijke communicatie binnen het team over de Gezonde School-aanpak, wat precies aansluit bij de definitie van 'Consistente heldere communicatie' als regelmatige, eenduidige en verzorgde informatievoorziening aan alle betrokkenen.</t>
         </is>
       </c>
-      <c r="J545" s="2" t="n">
+      <c r="J545" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K545" s="2" t="inlineStr">
@@ -32117,7 +32119,7 @@
           <t>De reactie benadrukt de heldere en duidelijke communicatie naar leerlingen, wat direct aansluit bij de code 'Consistente heldere communicatie' die staat voor regelmatige, eenduidige en verzorgde informatievoorziening aan alle betrokkenen.</t>
         </is>
       </c>
-      <c r="J546" s="2" t="n">
+      <c r="J546" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K546" s="2" t="inlineStr">
@@ -32175,7 +32177,7 @@
           <t>De uitspraak benadrukt dat de doelen van de Gezonde School-aanpak helder en duidelijk zijn, wat aansluit bij het concept van consistente en heldere communicatie over de aanpak en voortgang.</t>
         </is>
       </c>
-      <c r="J547" s="2" t="n">
+      <c r="J547" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K547" s="2" t="inlineStr">
@@ -32233,7 +32235,7 @@
           <t>De uitspraak geeft aan dat er voldoende aandacht is voor de doelen van de Gezonde School-aanpak, wat duidt op een blijvende uitvoering en betrokkenheid, passend bij de definitie van 'Duurzame verankering'.</t>
         </is>
       </c>
-      <c r="J548" s="2" t="n">
+      <c r="J548" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K548" s="2" t="inlineStr">
@@ -32291,7 +32293,7 @@
           <t>De uitspraak geeft aan dat de Gezonde School-aanpak voldoet aan verplichte kerndoelen, wat duidt op een blijvende en structurele uitvoering van de aanpak binnen de school, passend bij het concept van duurzame verankering.</t>
         </is>
       </c>
-      <c r="J549" s="2" t="n">
+      <c r="J549" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K549" s="2" t="inlineStr">
@@ -32349,7 +32351,7 @@
           <t>De reactie benadrukt het frequente en gevarieerde bewegingsmoment (drie keer per week gym en fietsen), wat direct aansluit bij de definitie van 'Ruim bewegingsaanbod' als het aanbieden van frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J550" s="2" t="n">
+      <c r="J550" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K550" s="2" t="inlineStr">
@@ -32407,7 +32409,7 @@
           <t>De uitspraak benadrukt het ruime aanbod van buitenspelen, wat direct aansluit bij de definitie van 'Ruim bewegingsaanbod' als frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J551" s="2" t="n">
+      <c r="J551" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K551" s="2" t="inlineStr">
@@ -32465,7 +32467,7 @@
           <t>De aanwezigheid van een voetbalkooi duidt op een concreet en toegankelijk bewegingsaanbod binnen de school, wat direct aansluit bij de definitie van 'Ruim bewegingsaanbod' als het aanbieden van frequente, gevarieerde en toegankelijke bewegingsmomenten en materialen gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J552" s="2" t="n">
+      <c r="J552" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K552" s="2" t="inlineStr">
@@ -32523,7 +32525,7 @@
           <t>De vermelding van tafeltennis binnen de Gezonde School-aanpak duidt op een concreet sport- of bewegingsaanbod. Dit sluit goed aan bij de code 'Ruim bewegingsaanbod', die verwijst naar een gevarieerd en toegankelijk aanbod van bewegingsmomenten en materialen gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J553" s="2" t="n">
+      <c r="J553" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K553" s="2" t="inlineStr">
@@ -32581,7 +32583,7 @@
           <t>De term 'stoepranden' suggereert fysieke structuren die uitnodigen tot bewegen of spelen, wat past bij het concept van een ruim bewegingsaanbod met toegankelijke bewegingsmomenten en materialen gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J554" s="2" t="n">
+      <c r="J554" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="K554" s="2" t="inlineStr">
@@ -32639,7 +32641,7 @@
           <t>De vermelding van basketbal binnen de Gezonde School-aanpak duidt op een aanbod van sportactiviteiten en bewegingsmogelijkheden, wat aansluit bij de definitie van 'Ruim bewegingsaanbod' als gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J555" s="2" t="n">
+      <c r="J555" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K555" s="2" t="inlineStr">
@@ -32697,7 +32699,7 @@
           <t>De opmerking dat de Gezonde School-aanpak geen schoolkantine heeft, raakt direct aan de toegankelijkheid van gezond voedingsaanbod binnen de schoolomgeving. Het ontbreken van een kantine kan de beschikbaarheid en het gemakkelijk verkrijgen van gezond eten beperken, wat precies valt onder de definitie van deze code.</t>
         </is>
       </c>
-      <c r="J556" s="2" t="n">
+      <c r="J556" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
@@ -32755,7 +32757,7 @@
           <t>De opmerking dat leerlingen zelf brood en drinken meenemen, duidt op een situatie rondom het voedingsaanbod op school. 'Structureel voedingsbeleid' betreft blijvende voorzieningen of beleid gericht op gezond eten op school, wat hier het beste aansluit bij het feit dat leerlingen zelf voor hun voeding zorgen, mogelijk vanwege het ontbreken van een schoolvoorziening.</t>
         </is>
       </c>
-      <c r="J557" s="2" t="n">
+      <c r="J557" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K557" s="2" t="inlineStr">
@@ -32813,7 +32815,7 @@
           <t>De uitspraak geeft duidelijk aan dat ongezonde producten zoals frisdrank, koek, snoep en chips niet zijn toegestaan, wat direct aansluit bij het beleid om het aanbod en de zichtbaarheid van deze ongezonde producten op school te verminderen.</t>
         </is>
       </c>
-      <c r="J558" s="2" t="n">
+      <c r="J558" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
@@ -32871,7 +32873,7 @@
           <t>De reactie benadrukt het dagelijkse aanbod van vrije bewegingsactiviteiten, wat direct aansluit bij de definitie van 'Ruim bewegingsaanbod' als frequente, gevarieerde en toegankelijke bewegingsmomenten gedurende de schooldag.</t>
         </is>
       </c>
-      <c r="J559" s="2" t="n">
+      <c r="J559" s="3" t="n">
         <v>0.95</v>
       </c>
       <c r="K559" s="2" t="inlineStr">
@@ -32929,7 +32931,7 @@
           <t>Het idee verwijst naar een 'circuit aanbod', wat duidt op een gevarieerd en toegankelijk bewegingsmomentenaanbod binnen de schooldag. Dit sluit goed aan bij de definitie van 'Ruim bewegingsaanbod', dat gaat over frequente, gevarieerde en toegankelijke bewegingsmomenten en materialen.</t>
         </is>
       </c>
-      <c r="J560" s="2" t="n">
+      <c r="J560" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="K560" s="2" t="inlineStr">
@@ -32987,7 +32989,7 @@
           <t>De opmerking 'De Gezonde School-aanpak is rookvrij' verwijst naar een concreet initiatief rond rookpreventie, wat valt onder de brede implementatie van gezondheidsthema's zoals leefstijl en rookpreventie op school.</t>
         </is>
       </c>
-      <c r="J561" s="2" t="n">
+      <c r="J561" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="K561" s="2" t="inlineStr">
@@ -33020,19 +33022,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Summary Statistics</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr"/>
+      <c r="B1" s="4" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Total Assignments</t>
         </is>
@@ -33042,7 +33044,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Unique Respondents</t>
         </is>
@@ -33052,7 +33054,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Unique Ideas</t>
         </is>
@@ -33062,7 +33064,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Unique Codes</t>
         </is>
@@ -33072,7 +33074,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Unique Themes</t>
         </is>
@@ -33086,7 +33088,7 @@
       <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Code Frequency</t>
         </is>
